--- a/scripts/gbrt_standard/performance.xlsx
+++ b/scripts/gbrt_standard/performance.xlsx
@@ -9,13 +9,18 @@
   <sheets>
     <sheet name="Models" sheetId="1" r:id="rId1"/>
     <sheet name="Ensemble" sheetId="2" r:id="rId2"/>
+    <sheet name="Ensemble optspreads" sheetId="3" r:id="rId3"/>
+    <sheet name="Ensemble opt-undspreads" sheetId="4" r:id="rId4"/>
+    <sheet name="Returns Long-Short 30-min" sheetId="5" r:id="rId5"/>
+    <sheet name="Returns Long-Short Daily" sheetId="6" r:id="rId6"/>
+    <sheet name="Returns Long-Short Weekly" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="490">
   <si>
     <t>Model</t>
   </si>
@@ -238,7 +243,1288 @@
     <t>H-L 10 portfolios, 0 turnover</t>
   </si>
   <si>
-    <t>[nan, nan]</t>
+    <t>[np.float64(0.0006117655596526198), np.float64(6.648290307913089e-61)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0015920372764433397), np.float64(0.4491402880064453)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.7553843360900186), np.float64(0.45023612022055176)]</t>
+  </si>
+  <si>
+    <t>delta_change_mean</t>
+  </si>
+  <si>
+    <t>delta_change_std</t>
+  </si>
+  <si>
+    <t>turnover_mean</t>
+  </si>
+  <si>
+    <t>turnover_std</t>
+  </si>
+  <si>
+    <t>H-L 3 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 4 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 5 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 10 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 20 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 40 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 100 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 200 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 500 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 1000 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 3 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 4 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 5 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 10 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 20 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 40 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 100 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 200 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 500 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 1000 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 3 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 4 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 5 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 10 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 20 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 40 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 100 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 200 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 500 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 1000 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 3 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 4 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 5 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 10 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 20 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 40 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 100 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 200 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 500 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 1000 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 3 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 4 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 5 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 10 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 20 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 40 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 100 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 200 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 500 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 1000 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 3 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 4 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 5 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 20 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 40 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 100 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 200 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 500 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 1000 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>inf</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0028145106469345113), np.float64(0.07091679980016778)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0032082401261016137), np.float64(0.12245124001849195)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0010855260131773191), np.float64(0.35273755240205645)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0010469979174990802), np.float64(0.6537801105244825)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.003674659871171172), np.float64(7.704292722642614e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.007240574802215668), np.float64(0.00010112641121993734)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.017444885246933668), np.float64(0.0001732151301543866)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.034424368109083676), np.float64(0.0002115273367370503)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.08532657132858636), np.float64(0.00029982085077828415)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.1657735946415912), np.float64(0.0001496797474862028)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-7.389552118358248e-05), np.float64(0.8593662083973966)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0005271798546212915), np.float64(0.33176947696591536)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.001146840729826348), np.float64(0.0754800535083276)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.003044545405010196), np.float64(0.018417020531972157)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.006455723031539631), np.float64(0.012355643909606775)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.01272836579945151), np.float64(0.013264692814258265)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.031188108874328747), np.float64(0.01549848475923338)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.060999359980245825), np.float64(0.015808056681071533)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.15230932188434962), np.float64(0.017882564341228906)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.29502659360099187), np.float64(0.012998863936675752)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00032483663171629847), np.float64(4.1748195250134603e-07)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-3.331488627798027e-05), np.float64(0.6665018376999469)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00021778432415626086), np.float64(0.015256386699074132)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0009499587909215627), np.float64(3.620054395247036e-08)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0019597790311410616), np.float64(9.721508846536516e-09)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0036550329179522623), np.float64(7.718302324576563e-08)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.008375088190130092), np.float64(7.725702958720772e-07)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.01662218339095679), np.float64(7.79623489878143e-07)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.03994028982889551), np.float64(1.269864698057875e-06)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.07748505612002826), np.float64(2.1047505096492e-06)]</t>
+  </si>
+  <si>
+    <t>[np.float64(8.627576420616154e-06), np.float64(0.9431045584237883)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00022015848793111102), np.float64(0.1411971029580317)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0004339731237990975), np.float64(0.019310843233956754)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0011080520738897981), np.float64(0.002672994927816649)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0022418620495661835), np.float64(0.002110616249485383)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.004116915800503944), np.float64(0.004711399318368551)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.009380242230680057), np.float64(0.009954192401798215)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0180211883429474), np.float64(0.01331131529598282)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.042792364117061124), np.float64(0.015949753594709452)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.08811398286724063), np.float64(0.024263550309331066)]</t>
+  </si>
+  <si>
+    <t>[np.float64(6.331569643584056e-05), np.float64(0.09867474758033747)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00016068021364207234), np.float64(7.408299327286583e-07)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0002558016298810388), np.float64(4.112882645594598e-12)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0005304467970145386), np.float64(1.5892955378804697e-22)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0008243588781533342), np.float64(1.8222965383673736e-19)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0011863413103499693), np.float64(7.979115451139763e-13)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0019368333501449805), np.float64(7.339254337841818e-07)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0029975873920481543), np.float64(6.87143513793735e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0059838402349033275), np.float64(0.001880373176903835)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.01033100186322306), np.float64(0.004238131573479859)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00031244784395448717), np.float64(9.279739565583579e-33)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0003758872631540577), np.float64(2.9055779454249765e-39)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00043082573557756573), np.float64(4.4498048485146555e-45)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.000611772133495693), np.float64(6.622877165655811e-61)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0008061109564408985), np.float64(7.101865849057359e-68)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0009858472085302675), np.float64(2.5020049675690492e-61)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0012249882278466684), np.float64(4.281986643098708e-43)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0014116754783498543), np.float64(9.663831763493785e-30)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0017600106444586156), np.float64(4.5554769218086146e-18)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.002012176422201506), np.float64(1.386006411228308e-13)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.23906680560988797), np.float64(0.01397640301339538)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.3347611019709865), np.float64(0.009747342684849444)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.20815822806214357), np.float64(0.004273834406216405)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.417445355652617), np.float64(0.004039472367073718)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.06609791539561903), np.float64(0.24313429834872907)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.09889204152623278), np.float64(0.379272840410416)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.2668090717138282), np.float64(0.3418756352313518)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.3950881617077744), np.float64(0.4781288600746821)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.0727552454626303), np.float64(0.4397175314830496)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.5272828514199066), np.float64(0.31297706143987414)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.002909564180043592), np.float64(0.9108919289165662)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.004138127921869984), np.float64(0.9025010525432297)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0018280681634179497), np.float64(0.9636304238813331)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.006034610031558068), np.float64(0.939774032737142)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.02180650321034484), np.float64(0.8898043506115402)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0472793114156039), np.float64(0.8789134859191973)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.13699005043046208), np.float64(0.8605924049304858)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.46317445067264423), np.float64(0.7606639954140507)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.0872681228484213), np.float64(0.7737063789289595)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.757791412924157), np.float64(0.5816455168233318)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.004823316560331387), np.float64(0.22442921784188746)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.006668033367351449), np.float64(0.16643149104997834)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.010356520868395044), np.float64(0.06371511845438861)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.019444352500837918), np.float64(0.06636599161520261)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.038971495839573274), np.float64(0.05924875208219774)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.07374809353694767), np.float64(0.07056917583814737)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.19443804010499346), np.float64(0.05670604472474839)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.27371167791004575), np.float64(0.17349590318078556)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.7497214399440376), np.float64(0.12031262322278245)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.578152140057066), np.float64(0.08996812244721897)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.001341767008186592), np.float64(0.8585736996451333)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0015115268526774547), np.float64(0.8710111333817211)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0031051022728032737), np.float64(0.7879811865160381)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.006642361615780987), np.float64(0.7703225377516608)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.025060479704684113), np.float64(0.5721196675250263)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.04518325550071086), np.float64(0.607040776673125)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.09419187841205887), np.float64(0.6682070648250508)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.2082235865284422), np.float64(0.6339853577431981)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.2497723137227879), np.float64(0.810770226366213)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.5625440272895096), np.float64(0.8006675801673216)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0036241833311435943), np.float64(0.12816059135756588)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0007155987604542732), np.float64(0.7205903357008161)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00044791175165866045), np.float64(0.84267969733557)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0005598800837809507), np.float64(0.8635548075118579)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00099327004053728), np.float64(0.8550346902534306)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0038987613129659888), np.float64(0.6933689645439051)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.008461572842416307), np.float64(0.7192875790480269)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.014064981355840906), np.float64(0.755220622179188)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0027286405233613465), np.float64(0.9807010202571579)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.016069106199699278), np.float64(0.9380258476614558)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0005084579896084576), np.float64(0.7439208126586073)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00047355672510872293), np.float64(0.7788043817528436)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0006589190381372326), np.float64(0.711396592091288)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0015929333072644916), np.float64(0.4488910154767773)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.002950316299992358), np.float64(0.2501481010754609)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.005086379591533188), np.float64(0.1276858199118491)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.009580923046541193), np.float64(0.058930974506783085)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.01183466017800786), np.float64(0.09796715184559038)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.01720569301234028), np.float64(0.13984299611831527)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.02138072729654887), np.float64(0.16295434355888483)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.2766703731364086), np.float64(0.023063766362276847)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.8801834261428487), np.float64(0.06043865551912793)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.5648672758514135), np.float64(0.11800126200587803)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.695298444018081), np.float64(0.48706599582789056)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.5838844351117185), np.float64(0.00994198905893985)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.3101174066050163), np.float64(0.0009734458831901265)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.620798628845102), np.float64(0.00031179719227774076)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.6635242188079244), np.float64(0.00026480836588583514)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.6434783984611974), np.float64(0.00028595908528008195)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.8500424726993074), np.float64(0.00012732382894272177)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.7142830318756723), np.float64(0.08685602405486144)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.7590980064661833), np.float64(0.4480128798019012)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0711035479261651), np.float64(0.9433327455075572)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.4393320790065023), np.float64(0.15043947236115005)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.0757627324872283), np.float64(0.038228180882053)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.2888115971330905), np.float64(0.022344715705453884)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.367019128966752), np.float64(0.01816421733135822)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.403220670174118), np.float64(0.016473340803077614)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.3802551944817854), np.float64(0.017529110699028766)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.516402318112253), np.float64(0.012046514503271346)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.5624723788985446), np.float64(0.010571159337458337)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.050731107894961), np.float64(0.04061165907109596)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.5229841862015767), np.float64(0.12814961257607183)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.15451478977985098), np.float64(0.8772420119770192)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.5142827584149352), np.float64(0.13034089101850285)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.181194679793428), np.float64(0.0015220839882237214)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.377596970757083), np.float64(1.3556807547358484e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.736719562669465), np.float64(2.5606717080854497e-06)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.860263191221733), np.float64(1.4056740198305813e-06)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.822222914715942), np.float64(1.6932039311917055e-06)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.9260157575942163), np.float64(0.054449099513370125)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.5311717679788324), np.float64(0.1261140400039378)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.0830318526355565), np.float64(0.2791138114415807)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.08513606392610645), np.float64(0.9321740772487965)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.2659939096736208), np.float64(0.20587613051840062)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.939553561177967), np.float64(0.05277787352298614)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.2708919075080676), np.float64(0.023413003903887078)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.308633208835002), np.float64(0.02121273761586637)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.3401488689806578), np.float64(0.019515896632946478)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.2225908913241126), np.float64(0.026516432091182162)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.788428817103637), np.float64(0.0740772925709651)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.6591547102463493), np.float64(0.09746841233066474)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.4437899168119903), np.float64(0.14918141672939567)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.971867599293833), np.float64(0.3314040592870664)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.41745726320943033), np.float64(0.6764536554653352)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.1975285093376238), np.float64(0.8434631062770708)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.2911856228409067), np.float64(0.19700452386021644)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.062288079268831), np.float64(0.039495976616424545)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.3916412578075863), np.float64(0.016998463410668053)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.564496415474091), np.float64(0.010510202580217521)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.3395503702035965), np.float64(0.18076406338618511)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.226586433539589), np.float64(0.22033144564790338)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.1247989216901921), np.float64(0.2610045937262532)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.7553677249105637), np.float64(0.450246078781788)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.3679744435898268), np.float64(0.7129876027531832)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.06306726046337283), np.float64(0.9497283708235824)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.39347213543581006), np.float64(0.694073458310646)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.6815887175930511), np.float64(0.49569220832780175)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.9752460262614068), np.float64(0.32972690017234885)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.2506200239283056), np.float64(0.21143118716844958)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0029088007473024105), np.float64(0.06487629357247439)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00417064997820183), np.float64(0.09987122012333617)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.002157302204833479), np.float64(0.27964229699220206)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0018497961259477732), np.float64(0.5135134367544988)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0033169175099131), np.float64(3.066153884619201e-07)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.006506240626486262), np.float64(2.9164715544879654e-07)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.015717425238098062), np.float64(6.169494770324503e-07)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.03096968798677963), np.float64(9.501408310964873e-07)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.07748843415796457), np.float64(2.826143121191309e-06)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.15542406750637539), np.float64(1.2171801655759823e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0001898594622131064), np.float64(0.5513569798450804)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00033892356814280405), np.float64(0.38007484199390373)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0009152031151652568), np.float64(0.03243600612746896)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0028774108163690973), np.float64(0.013086738900914312)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00521568610077558), np.float64(0.0010853336671907306)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.009624624769518645), np.float64(0.00014586157363222213)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.023022637128855824), np.float64(0.00018912808149629829)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.04307391067389383), np.float64(0.0001083936531070091)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.10422636304739222), np.float64(0.00010290384749431717)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.20582481828973584), np.float64(6.62370907093747e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00036767156743929436), np.float64(1.658340337351035e-07)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-7.484970002424865e-05), np.float64(0.38564690841988786)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0001417749066579407), np.float64(0.17631210744938217)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0009241236576351435), np.float64(3.282633307705462e-08)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0019152294882191574), np.float64(4.1058190830483345e-09)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.003556392899413191), np.float64(3.019419309571721e-08)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.008087328444824491), np.float64(3.1195266109274307e-07)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.015534970830074652), np.float64(9.92655256022145e-07)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0373627688148158), np.float64(1.69052940413138e-06)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.07304891161291698), np.float64(4.410181806978265e-06)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-4.465008689010477e-05), np.float64(0.6941441203773983)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00019986557668777295), np.float64(0.17392066482744833)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0004179480335397618), np.float64(0.022412572490753895)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0010737643371422476), np.float64(0.0029497369660431787)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0021565663432190642), np.float64(0.002136424492148143)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.003857655353643189), np.float64(0.004383362873530194)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.008230796522113492), np.float64(0.005384165071325668)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.015333795925879249), np.float64(0.005476163245065052)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.03887192280248597), np.float64(0.009577379649554097)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.07908090564225628), np.float64(0.014239846693218653)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-4.277829583684948e-05), np.float64(0.6884984104671772)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.291425011339145e-05), np.float64(0.8679203393273438)]</t>
+  </si>
+  <si>
+    <t>[np.float64(8.836889949431724e-05), np.float64(0.5995452519441348)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00023725586173950442), np.float64(0.4289561925051573)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0001806584285136011), np.float64(0.7850664270259745)]</t>
+  </si>
+  <si>
+    <t>[np.float64(7.94374187909383e-06), np.float64(0.9947630904381872)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0010511910475918932), np.float64(0.7324621536959289)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.002962656601325373), np.float64(0.6288220176623224)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.008897340003519534), np.float64(0.5584795419282)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.019130534362274642), np.float64(0.5189659627791757)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00030770465666311473), np.float64(4.987801935219264e-32)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0003716048928714127), np.float64(1.2331215400838067e-38)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0004265431852263902), np.float64(1.6472939314630336e-44)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0006060666678240922), np.float64(2.090579024332089e-60)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0007989956286347735), np.float64(2.5357647133596767e-67)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0009756039199836571), np.float64(8.936735484898636e-61)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00121723957970414), np.float64(1.0142613881693652e-42)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0014056279744632336), np.float64(1.3126513477235944e-29)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0017479945996944754), np.float64(7.096881586128794e-18)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0019947534691298636), np.float64(2.054107899773933e-13)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.24279519948435963), np.float64(0.013425001654842282)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.44677765847789), np.float64(0.0046024771331725405)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.3476889941388529), np.float64(0.0051325165730088385)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.5045751389524846), np.float64(0.00410192949431298)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.037038088052204696), np.float64(0.3460282541184976)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0510898475900136), np.float64(0.5034899001385353)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.129996335270306), np.float64(0.4940549383388208)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.18052551080909823), np.float64(0.6331645553599693)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.5239517561353071), np.float64(0.5894919897865394)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.002890528095322), np.float64(0.3236610377014402)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0037334102458838722), np.float64(0.85076505718796)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.003950119465061473), np.float64(0.8692643016903289)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.008669765385814187), np.float64(0.7441274695848599)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0033643817355564964), np.float64(0.9625598799885761)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.032299891700950094), np.float64(0.7391833024749307)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.05478948009321984), np.float64(0.7196248464591734)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.11533083394352263), np.float64(0.7567857012215372)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0783035177874397), np.float64(0.9066363739636766)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.005580203336968567), np.float64(0.9971719697419782)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.8392961999730537), np.float64(0.7761682799161115)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0038601014050797383), np.float64(0.3740647354736334)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.004026587441014687), np.float64(0.45388965565318007)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0070798986082840805), np.float64(0.27800142855670656)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.018071495420512618), np.float64(0.07844816001287969)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.037272734944506156), np.float64(0.05835335088801156)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.06999446738077567), np.float64(0.06880377861454813)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.18705516987647677), np.float64(0.049229094416732296)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.35163372969559625), np.float64(0.06453324937766225)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.8512514129419204), np.float64(0.06258800522772992)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.9466959640360846), np.float64(0.031440909458292615)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0010693490638554498), np.float64(0.8800990460587851)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0011156498788172885), np.float64(0.9030869268832037)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0033911460727495276), np.float64(0.7662060351307752)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.005042237050526818), np.float64(0.8212524859705277)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.021546480985877026), np.float64(0.6143998562295404)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.03795350389033134), np.float64(0.642301352837968)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.08027430162881004), np.float64(0.6533811756417934)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.19374825153398817), np.float64(0.5585762276091336)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.2829055990252863), np.float64(0.7491148078305051)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.558714730685318), np.float64(0.761444264218921)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0003475318137276955), np.float64(0.958261971910215)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0029909028952524595), np.float64(0.7270609635579086)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.004103900037273485), np.float64(0.6948041817187182)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.007230751270845209), np.float64(0.6961139256778447)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.016629984661731687), np.float64(0.6806852955961622)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.03596079069088129), np.float64(0.6238553050344802)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.10369782029864191), np.float64(0.5779133614445315)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.18835896847959974), np.float64(0.6085210535489504)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.279349618866277), np.float64(0.7545762976892005)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.18951147224390244), np.float64(0.9109420430325614)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0006660717753708438), np.float64(0.6679627278457853)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0005296689215611365), np.float64(0.752967973251796)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0007075510057631539), np.float64(0.6903739073320825)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00158596372503507), np.float64(0.4486356206247009)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0028641772231589287), np.float64(0.26210545356012455)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.004994932675869057), np.float64(0.13252468190593583)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.009631691351819505), np.float64(0.05690775456614334)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.01192294103735937), np.float64(0.09441350725585013)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.016290972430243845), np.float64(0.1602984429913022)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.02005775103870783), np.float64(0.19310264771226512)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.3122905065871415), np.float64(0.021009435389492546)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.8852348134470045), np.float64(0.059752780338076045)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.4199233114555072), np.float64(0.15601146717426068)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.8338602272669262), np.float64(0.4046034770929268)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.767212269394502), np.float64(0.005781605776700601)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.0774132286201805), np.float64(4.999365726048341e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.721511336473866), np.float64(2.7543097307373616e-06)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.811102737651354), np.float64(1.787440889834683e-06)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.697209051384477), np.float64(3.0932728442366215e-06)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.437120565593736), np.float64(1.0366423057739159e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.0523111239337006), np.float64(0.04045756605240981)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.1670398629132916), np.float64(0.2435347793649524)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.28136986569827843), np.float64(0.7784979749689624)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.421523159772229), np.float64(0.15554632157356446)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.453496663498044), np.float64(0.014355342093149865)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.3155016735975242), np.float64(0.0009551320905403846)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.567836400640597), np.float64(0.00038090915510589744)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.7984986496807487), np.float64(0.00015636854887606178)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.871681134595233), np.float64(0.00011671792692644878)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.015701354279134), np.float64(6.47285450947798e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.630533499781979), np.float64(0.008685622886330084)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.0932616622262046), np.float64(0.036633626859865216)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.647513514350101), np.float64(0.09983705483447941)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.19439572573821884), np.float64(0.8459143623332357)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.441190859895549), np.float64(0.14991392046030444)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.1539343558818467), np.float64(0.001669769298339811)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.478023782893435), np.float64(8.605173185462234e-06)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.700048971823165), np.float64(3.0516846492475454e-06)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.814242953159267), np.float64(1.760329714467349e-06)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.6899899353356505), np.float64(3.201457126806848e-06)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.019431205891956), np.float64(0.04376849488174244)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.560797602414402), np.float64(0.11895876451591296)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.114845730701007), np.float64(0.2652443667308496)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0018333716420673991), np.float64(0.9985376294432368)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.1834107289803775), np.float64(0.23699062952589753)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.8909119898953433), np.float64(0.0589896680409692)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.394157791331997), np.float64(0.016883104129073758)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.554140005050847), np.float64(0.01082543158660504)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.5040344850428817), np.float64(0.012472513997697542)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.4128491632133304), np.float64(0.01604761682154162)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.965234518891574), np.float64(0.04972551957902438)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.8621384208097918), np.float64(0.06294239666257087)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.646971645722007), np.float64(0.09994841974774958)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.3373568900778725), np.float64(0.1814783639683098)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.0202395213066155), np.float64(0.307916886482754)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.809866397995212), np.float64(0.41825277745897294)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.7000694988788293), np.float64(0.4840831948236833)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.677056050931647), np.float64(0.498562047442674)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.6872098586577858), np.float64(0.4921455140829271)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.6868582118979533), np.float64(0.4923669872133146)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.3522285358726358), np.float64(0.17667639235286445)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.2340717411787967), np.float64(0.2175310355001667)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.1287773273019073), np.float64(0.2593231133622933)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.7770867218682701), np.float64(0.4373325429922788)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.4061277048665911), np.float64(0.6847551188104861)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0985362412041609), np.float64(0.9215306655619052)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.39335866563333577), np.float64(0.6941572190313718)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.6195881495737218), np.float64(0.5357017172066432)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.9710920195327646), np.float64(0.33178986042902536)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.5543304480900124), np.float64(0.12049287904650982)]</t>
+  </si>
+  <si>
+    <t>Returns</t>
   </si>
 </sst>
 </file>
@@ -1697,10 +2983,6169 @@
         <v>62</v>
       </c>
       <c r="V12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="W12" t="s">
-        <v>62</v>
+        <v>64</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P61"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:16">
+      <c r="B1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J1" t="s">
+        <v>54</v>
+      </c>
+      <c r="K1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L1" t="s">
+        <v>56</v>
+      </c>
+      <c r="M1" t="s">
+        <v>57</v>
+      </c>
+      <c r="N1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O1" t="s">
+        <v>59</v>
+      </c>
+      <c r="P1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2">
+        <v>0.001057807401679532</v>
+      </c>
+      <c r="D2">
+        <v>-0.002547855954617262</v>
+      </c>
+      <c r="E2">
+        <v>0.04454321414232254</v>
+      </c>
+      <c r="F2">
+        <v>0.0008540613926015794</v>
+      </c>
+      <c r="G2">
+        <v>0.0008677298319526017</v>
+      </c>
+      <c r="H2">
+        <v>1.0005704815381</v>
+      </c>
+      <c r="I2">
+        <v>0.04898014277549018</v>
+      </c>
+      <c r="J2">
+        <v>-0.05719964206218719</v>
+      </c>
+      <c r="K2">
+        <v>-0.9997653365135193</v>
+      </c>
+      <c r="L2">
+        <v>2.549490928649902</v>
+      </c>
+      <c r="M2">
+        <v>-3.273898839950562</v>
+      </c>
+      <c r="N2" t="s">
+        <v>129</v>
+      </c>
+      <c r="O2" t="s">
+        <v>189</v>
+      </c>
+      <c r="P2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3">
+        <v>0.001407008946909041</v>
+      </c>
+      <c r="D3">
+        <v>-0.002833906793966889</v>
+      </c>
+      <c r="E3">
+        <v>0.05940783023834229</v>
+      </c>
+      <c r="F3">
+        <v>0.001011624350212514</v>
+      </c>
+      <c r="G3">
+        <v>0.0009687909623607993</v>
+      </c>
+      <c r="H3">
+        <v>1.00079886176607</v>
+      </c>
+      <c r="I3">
+        <v>0.04892841994748822</v>
+      </c>
+      <c r="J3">
+        <v>-0.04770258069038391</v>
+      </c>
+      <c r="K3">
+        <v>-0.9999083280563354</v>
+      </c>
+      <c r="L3">
+        <v>3.400287389755249</v>
+      </c>
+      <c r="M3">
+        <v>-2.730321645736694</v>
+      </c>
+      <c r="N3" t="s">
+        <v>130</v>
+      </c>
+      <c r="O3" t="s">
+        <v>190</v>
+      </c>
+      <c r="P3" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4">
+        <v>0.001754134150883748</v>
+      </c>
+      <c r="D4">
+        <v>-0.0008583601447753608</v>
+      </c>
+      <c r="E4">
+        <v>0.03345958143472672</v>
+      </c>
+      <c r="F4">
+        <v>0.001148651354014874</v>
+      </c>
+      <c r="G4">
+        <v>0.001097879954613745</v>
+      </c>
+      <c r="H4">
+        <v>1.000909835587544</v>
+      </c>
+      <c r="I4">
+        <v>0.048950399098979</v>
+      </c>
+      <c r="J4">
+        <v>-0.02565364353358746</v>
+      </c>
+      <c r="K4">
+        <v>-0.9399883151054382</v>
+      </c>
+      <c r="L4">
+        <v>1.915104389190674</v>
+      </c>
+      <c r="M4">
+        <v>-1.468320965766907</v>
+      </c>
+      <c r="N4" t="s">
+        <v>131</v>
+      </c>
+      <c r="O4" t="s">
+        <v>191</v>
+      </c>
+      <c r="P4" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5">
+        <v>0.003459777565252189</v>
+      </c>
+      <c r="D5">
+        <v>-0.0006261630915105343</v>
+      </c>
+      <c r="E5">
+        <v>0.06690638512372971</v>
+      </c>
+      <c r="F5">
+        <v>0.00165543903131038</v>
+      </c>
+      <c r="G5">
+        <v>0.001454378245398402</v>
+      </c>
+      <c r="H5">
+        <v>1.001084465681174</v>
+      </c>
+      <c r="I5">
+        <v>0.04895122638870369</v>
+      </c>
+      <c r="J5">
+        <v>-0.009358794428408146</v>
+      </c>
+      <c r="K5">
+        <v>-0.8715093731880188</v>
+      </c>
+      <c r="L5">
+        <v>3.829477310180664</v>
+      </c>
+      <c r="M5">
+        <v>-0.5356632471084595</v>
+      </c>
+      <c r="N5" t="s">
+        <v>132</v>
+      </c>
+      <c r="O5" t="s">
+        <v>192</v>
+      </c>
+      <c r="P5" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6">
+        <v>0</v>
+      </c>
+      <c r="B6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6">
+        <v>0.006791113013036696</v>
+      </c>
+      <c r="D6">
+        <v>0.003739902516826987</v>
+      </c>
+      <c r="E6">
+        <v>0.02640628069639206</v>
+      </c>
+      <c r="F6">
+        <v>0.002188879530876875</v>
+      </c>
+      <c r="G6">
+        <v>0.001782883307896554</v>
+      </c>
+      <c r="H6">
+        <v>1.001189335480276</v>
+      </c>
+      <c r="I6">
+        <v>0.04908305368506005</v>
+      </c>
+      <c r="J6">
+        <v>0.1416292786598206</v>
+      </c>
+      <c r="K6">
+        <v>204684.921875</v>
+      </c>
+      <c r="L6">
+        <v>1.511399149894714</v>
+      </c>
+      <c r="M6">
+        <v>8.106343269348145</v>
+      </c>
+      <c r="N6" t="s">
+        <v>133</v>
+      </c>
+      <c r="O6" t="s">
+        <v>193</v>
+      </c>
+      <c r="P6" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7">
+        <v>0</v>
+      </c>
+      <c r="B7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7">
+        <v>0.01335503143223508</v>
+      </c>
+      <c r="D7">
+        <v>0.007337661925703287</v>
+      </c>
+      <c r="E7">
+        <v>0.05290023237466812</v>
+      </c>
+      <c r="F7">
+        <v>0.002652466064319015</v>
+      </c>
+      <c r="G7">
+        <v>0.002069624373689294</v>
+      </c>
+      <c r="H7">
+        <v>1.001037766869773</v>
+      </c>
+      <c r="I7">
+        <v>0.04918780670119183</v>
+      </c>
+      <c r="J7">
+        <v>0.1387075483798981</v>
+      </c>
+      <c r="K7">
+        <v>25210007552</v>
+      </c>
+      <c r="L7">
+        <v>3.027816295623779</v>
+      </c>
+      <c r="M7">
+        <v>7.939114093780518</v>
+      </c>
+      <c r="N7" t="s">
+        <v>134</v>
+      </c>
+      <c r="O7" t="s">
+        <v>194</v>
+      </c>
+      <c r="P7" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8">
+        <v>0</v>
+      </c>
+      <c r="B8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8">
+        <v>0.03273917991315294</v>
+      </c>
+      <c r="D8">
+        <v>0.01768802292644978</v>
+      </c>
+      <c r="E8">
+        <v>0.1320415139198303</v>
+      </c>
+      <c r="F8">
+        <v>0.00292159290984273</v>
+      </c>
+      <c r="G8">
+        <v>0.002230143407359719</v>
+      </c>
+      <c r="H8">
+        <v>1.000712748016749</v>
+      </c>
+      <c r="I8">
+        <v>0.05085982878199578</v>
+      </c>
+      <c r="J8">
+        <v>0.1339580416679382</v>
+      </c>
+      <c r="K8">
+        <v>8.823795960552649E+24</v>
+      </c>
+      <c r="L8">
+        <v>7.557574272155762</v>
+      </c>
+      <c r="M8">
+        <v>7.667269706726074</v>
+      </c>
+      <c r="N8" t="s">
+        <v>135</v>
+      </c>
+      <c r="O8" t="s">
+        <v>195</v>
+      </c>
+      <c r="P8" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9">
+        <v>0</v>
+      </c>
+      <c r="B9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C9">
+        <v>0.06481592995401972</v>
+      </c>
+      <c r="D9">
+        <v>0.03481140732765198</v>
+      </c>
+      <c r="E9">
+        <v>0.2640112936496735</v>
+      </c>
+      <c r="F9">
+        <v>0.002928420202806592</v>
+      </c>
+      <c r="G9">
+        <v>0.002262473804876208</v>
+      </c>
+      <c r="H9">
+        <v>1.000407100285757</v>
+      </c>
+      <c r="I9">
+        <v>0.05230209125491456</v>
+      </c>
+      <c r="J9">
+        <v>0.1318557560443878</v>
+      </c>
+      <c r="K9" t="s">
+        <v>128</v>
+      </c>
+      <c r="L9">
+        <v>15.11104297637939</v>
+      </c>
+      <c r="M9">
+        <v>7.546942234039307</v>
+      </c>
+      <c r="N9" t="s">
+        <v>136</v>
+      </c>
+      <c r="O9" t="s">
+        <v>196</v>
+      </c>
+      <c r="P9" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10">
+        <v>0</v>
+      </c>
+      <c r="B10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10">
+        <v>0.1616860480437905</v>
+      </c>
+      <c r="D10">
+        <v>0.08644607663154602</v>
+      </c>
+      <c r="E10">
+        <v>0.67063969373703</v>
+      </c>
+      <c r="F10">
+        <v>0.002724152058362961</v>
+      </c>
+      <c r="G10">
+        <v>0.002362794009968638</v>
+      </c>
+      <c r="H10">
+        <v>1.000916138125441</v>
+      </c>
+      <c r="I10">
+        <v>0.05820111326850902</v>
+      </c>
+      <c r="J10">
+        <v>0.1289009302854538</v>
+      </c>
+      <c r="K10" t="s">
+        <v>128</v>
+      </c>
+      <c r="L10">
+        <v>38.38496780395508</v>
+      </c>
+      <c r="M10">
+        <v>7.377819061279297</v>
+      </c>
+      <c r="N10" t="s">
+        <v>137</v>
+      </c>
+      <c r="O10" t="s">
+        <v>197</v>
+      </c>
+      <c r="P10" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11">
+        <v>0</v>
+      </c>
+      <c r="B11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11">
+        <v>0.3151190553593516</v>
+      </c>
+      <c r="D11">
+        <v>0.1681708842515945</v>
+      </c>
+      <c r="E11">
+        <v>1.242731809616089</v>
+      </c>
+      <c r="F11">
+        <v>0.002639228478074074</v>
+      </c>
+      <c r="G11">
+        <v>0.002468330087140203</v>
+      </c>
+      <c r="H11">
+        <v>1.002172582619339</v>
+      </c>
+      <c r="I11">
+        <v>0.06761948594284269</v>
+      </c>
+      <c r="J11">
+        <v>0.13532355427742</v>
+      </c>
+      <c r="K11" t="s">
+        <v>128</v>
+      </c>
+      <c r="L11">
+        <v>71.12943267822266</v>
+      </c>
+      <c r="M11">
+        <v>7.745426654815674</v>
+      </c>
+      <c r="N11" t="s">
+        <v>138</v>
+      </c>
+      <c r="O11" t="s">
+        <v>198</v>
+      </c>
+      <c r="P11" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12">
+        <v>0</v>
+      </c>
+      <c r="B12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12">
+        <v>0.001737581919777997</v>
+      </c>
+      <c r="D12">
+        <v>-7.062957593007013E-05</v>
+      </c>
+      <c r="E12">
+        <v>0.01188808679580688</v>
+      </c>
+      <c r="F12">
+        <v>0.0008704078500159085</v>
+      </c>
+      <c r="G12">
+        <v>0.0008708203677088022</v>
+      </c>
+      <c r="H12">
+        <v>1.000527335679428</v>
+      </c>
+      <c r="I12">
+        <v>0.04897053144965573</v>
+      </c>
+      <c r="J12">
+        <v>-0.005941206123679876</v>
+      </c>
+      <c r="K12">
+        <v>-0.2065755724906921</v>
+      </c>
+      <c r="L12">
+        <v>0.6804307103157043</v>
+      </c>
+      <c r="M12">
+        <v>-0.3400529623031616</v>
+      </c>
+      <c r="N12" t="s">
+        <v>139</v>
+      </c>
+      <c r="O12" t="s">
+        <v>199</v>
+      </c>
+      <c r="P12" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13">
+        <v>0</v>
+      </c>
+      <c r="B13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13">
+        <v>0.002312476812473673</v>
+      </c>
+      <c r="D13">
+        <v>0.0005318239564076066</v>
+      </c>
+      <c r="E13">
+        <v>0.01547866500914097</v>
+      </c>
+      <c r="F13">
+        <v>0.001036970177665353</v>
+      </c>
+      <c r="G13">
+        <v>0.0009981356561183929</v>
+      </c>
+      <c r="H13">
+        <v>1.000747598081996</v>
+      </c>
+      <c r="I13">
+        <v>0.04892037852402119</v>
+      </c>
+      <c r="J13">
+        <v>0.03435851633548737</v>
+      </c>
+      <c r="K13">
+        <v>4.706977844238281</v>
+      </c>
+      <c r="L13">
+        <v>0.885942280292511</v>
+      </c>
+      <c r="M13">
+        <v>1.966556072235107</v>
+      </c>
+      <c r="N13" t="s">
+        <v>140</v>
+      </c>
+      <c r="O13" t="s">
+        <v>200</v>
+      </c>
+      <c r="P13" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14">
+        <v>0</v>
+      </c>
+      <c r="B14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C14">
+        <v>0.002884534028919651</v>
+      </c>
+      <c r="D14">
+        <v>0.001148830051533878</v>
+      </c>
+      <c r="E14">
+        <v>0.01837574504315853</v>
+      </c>
+      <c r="F14">
+        <v>0.001180731458589435</v>
+      </c>
+      <c r="G14">
+        <v>0.00112479121889919</v>
+      </c>
+      <c r="H14">
+        <v>1.000870554311253</v>
+      </c>
+      <c r="I14">
+        <v>0.04890813860002634</v>
+      </c>
+      <c r="J14">
+        <v>0.06251882761716843</v>
+      </c>
+      <c r="K14">
+        <v>42.00747299194336</v>
+      </c>
+      <c r="L14">
+        <v>1.05176055431366</v>
+      </c>
+      <c r="M14">
+        <v>3.578349590301514</v>
+      </c>
+      <c r="N14" t="s">
+        <v>141</v>
+      </c>
+      <c r="O14" t="s">
+        <v>201</v>
+      </c>
+      <c r="P14" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15">
+        <v>0</v>
+      </c>
+      <c r="B15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C15">
+        <v>0.005716169557169079</v>
+      </c>
+      <c r="D15">
+        <v>0.003050775034353137</v>
+      </c>
+      <c r="E15">
+        <v>0.03676962479948997</v>
+      </c>
+      <c r="F15">
+        <v>0.001702866400592029</v>
+      </c>
+      <c r="G15">
+        <v>0.00147887715138495</v>
+      </c>
+      <c r="H15">
+        <v>1.001075365546918</v>
+      </c>
+      <c r="I15">
+        <v>0.04894739586259389</v>
+      </c>
+      <c r="J15">
+        <v>0.08296997845172882</v>
+      </c>
+      <c r="K15">
+        <v>21572.47265625</v>
+      </c>
+      <c r="L15">
+        <v>2.104559183120728</v>
+      </c>
+      <c r="M15">
+        <v>4.748898983001709</v>
+      </c>
+      <c r="N15" t="s">
+        <v>142</v>
+      </c>
+      <c r="O15" t="s">
+        <v>202</v>
+      </c>
+      <c r="P15" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16">
+        <v>0</v>
+      </c>
+      <c r="B16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16">
+        <v>0.01129076146046355</v>
+      </c>
+      <c r="D16">
+        <v>0.006478020921349525</v>
+      </c>
+      <c r="E16">
+        <v>0.07344938069581985</v>
+      </c>
+      <c r="F16">
+        <v>0.002239353489130735</v>
+      </c>
+      <c r="G16">
+        <v>0.001826581661589444</v>
+      </c>
+      <c r="H16">
+        <v>1.001193974093663</v>
+      </c>
+      <c r="I16">
+        <v>0.04910199244091504</v>
+      </c>
+      <c r="J16">
+        <v>0.08819708228111267</v>
+      </c>
+      <c r="K16">
+        <v>1537951872</v>
+      </c>
+      <c r="L16">
+        <v>4.203974723815918</v>
+      </c>
+      <c r="M16">
+        <v>5.048079013824463</v>
+      </c>
+      <c r="N16" t="s">
+        <v>143</v>
+      </c>
+      <c r="O16" t="s">
+        <v>203</v>
+      </c>
+      <c r="P16" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17">
+        <v>0</v>
+      </c>
+      <c r="B17" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17">
+        <v>0.02228170564741719</v>
+      </c>
+      <c r="D17">
+        <v>0.0127756055444479</v>
+      </c>
+      <c r="E17">
+        <v>0.1463159918785095</v>
+      </c>
+      <c r="F17">
+        <v>0.002706993836909533</v>
+      </c>
+      <c r="G17">
+        <v>0.002105645602568984</v>
+      </c>
+      <c r="H17">
+        <v>1.001031060821363</v>
+      </c>
+      <c r="I17">
+        <v>0.04919508857680562</v>
+      </c>
+      <c r="J17">
+        <v>0.08731517195701599</v>
+      </c>
+      <c r="K17">
+        <v>1.151924797316268E+18</v>
+      </c>
+      <c r="L17">
+        <v>8.374593734741211</v>
+      </c>
+      <c r="M17">
+        <v>4.997601985931396</v>
+      </c>
+      <c r="N17" t="s">
+        <v>144</v>
+      </c>
+      <c r="O17" t="s">
+        <v>204</v>
+      </c>
+      <c r="P17" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18">
+        <v>0</v>
+      </c>
+      <c r="B18" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18">
+        <v>0.0551058856843063</v>
+      </c>
+      <c r="D18">
+        <v>0.03131461516022682</v>
+      </c>
+      <c r="E18">
+        <v>0.3669477701187134</v>
+      </c>
+      <c r="F18">
+        <v>0.002956733107566833</v>
+      </c>
+      <c r="G18">
+        <v>0.002247866010293365</v>
+      </c>
+      <c r="H18">
+        <v>1.000768643781311</v>
+      </c>
+      <c r="I18">
+        <v>0.05079026784994584</v>
+      </c>
+      <c r="J18">
+        <v>0.08533807098865509</v>
+      </c>
+      <c r="K18" t="s">
+        <v>128</v>
+      </c>
+      <c r="L18">
+        <v>21.00275230407715</v>
+      </c>
+      <c r="M18">
+        <v>4.884439945220947</v>
+      </c>
+      <c r="N18" t="s">
+        <v>145</v>
+      </c>
+      <c r="O18" t="s">
+        <v>205</v>
+      </c>
+      <c r="P18" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19">
+        <v>0</v>
+      </c>
+      <c r="B19" t="s">
+        <v>86</v>
+      </c>
+      <c r="C19">
+        <v>0.1085479290086356</v>
+      </c>
+      <c r="D19">
+        <v>0.06144512817263603</v>
+      </c>
+      <c r="E19">
+        <v>0.7197899222373962</v>
+      </c>
+      <c r="F19">
+        <v>0.002947431290522218</v>
+      </c>
+      <c r="G19">
+        <v>0.002278057392686605</v>
+      </c>
+      <c r="H19">
+        <v>1.000433708768542</v>
+      </c>
+      <c r="I19">
+        <v>0.05229634017223155</v>
+      </c>
+      <c r="J19">
+        <v>0.08536536246538162</v>
+      </c>
+      <c r="K19" t="s">
+        <v>128</v>
+      </c>
+      <c r="L19">
+        <v>41.19814682006836</v>
+      </c>
+      <c r="M19">
+        <v>4.886002063751221</v>
+      </c>
+      <c r="N19" t="s">
+        <v>146</v>
+      </c>
+      <c r="O19" t="s">
+        <v>206</v>
+      </c>
+      <c r="P19" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20">
+        <v>0</v>
+      </c>
+      <c r="B20" t="s">
+        <v>87</v>
+      </c>
+      <c r="C20">
+        <v>0.2719841224614625</v>
+      </c>
+      <c r="D20">
+        <v>0.1534482538700104</v>
+      </c>
+      <c r="E20">
+        <v>1.831310868263245</v>
+      </c>
+      <c r="F20">
+        <v>0.002713247667998075</v>
+      </c>
+      <c r="G20">
+        <v>0.002356237266212702</v>
+      </c>
+      <c r="H20">
+        <v>1.000620340491821</v>
+      </c>
+      <c r="I20">
+        <v>0.057978030362671</v>
+      </c>
+      <c r="J20">
+        <v>0.08379148691892624</v>
+      </c>
+      <c r="K20" t="s">
+        <v>128</v>
+      </c>
+      <c r="L20">
+        <v>104.8175506591797</v>
+      </c>
+      <c r="M20">
+        <v>4.795918941497803</v>
+      </c>
+      <c r="N20" t="s">
+        <v>147</v>
+      </c>
+      <c r="O20" t="s">
+        <v>207</v>
+      </c>
+      <c r="P20" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21">
+        <v>0</v>
+      </c>
+      <c r="B21" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21">
+        <v>0.5279354684991531</v>
+      </c>
+      <c r="D21">
+        <v>0.2985944747924805</v>
+      </c>
+      <c r="E21">
+        <v>3.383237600326538</v>
+      </c>
+      <c r="F21">
+        <v>0.002658195793628693</v>
+      </c>
+      <c r="G21">
+        <v>0.002489544916898012</v>
+      </c>
+      <c r="H21">
+        <v>1.002050183598531</v>
+      </c>
+      <c r="I21">
+        <v>0.06771386325557802</v>
+      </c>
+      <c r="J21">
+        <v>0.08825702220201492</v>
+      </c>
+      <c r="K21" t="s">
+        <v>128</v>
+      </c>
+      <c r="L21">
+        <v>193.6441802978516</v>
+      </c>
+      <c r="M21">
+        <v>5.051509857177734</v>
+      </c>
+      <c r="N21" t="s">
+        <v>148</v>
+      </c>
+      <c r="O21" t="s">
+        <v>208</v>
+      </c>
+      <c r="P21" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22">
+        <v>0</v>
+      </c>
+      <c r="B22" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22">
+        <v>0.0005682496230976891</v>
+      </c>
+      <c r="D22">
+        <v>-0.0003194442833773792</v>
+      </c>
+      <c r="E22">
+        <v>0.001816940493881702</v>
+      </c>
+      <c r="F22">
+        <v>0.0009020473808050156</v>
+      </c>
+      <c r="G22">
+        <v>0.0008954944205470383</v>
+      </c>
+      <c r="H22">
+        <v>1.000474231506427</v>
+      </c>
+      <c r="I22">
+        <v>0.04900057282465634</v>
+      </c>
+      <c r="J22">
+        <v>-0.1758143901824951</v>
+      </c>
+      <c r="K22">
+        <v>-0.6488673686981201</v>
+      </c>
+      <c r="L22">
+        <v>0.1039950475096703</v>
+      </c>
+      <c r="M22">
+        <v>-10.06297397613525</v>
+      </c>
+      <c r="N22" t="s">
+        <v>149</v>
+      </c>
+      <c r="O22" t="s">
+        <v>209</v>
+      </c>
+      <c r="P22" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23">
+        <v>0</v>
+      </c>
+      <c r="B23" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23">
+        <v>0.0007522056475362466</v>
+      </c>
+      <c r="D23">
+        <v>-2.58055097219767E-05</v>
+      </c>
+      <c r="E23">
+        <v>0.002205965109169483</v>
+      </c>
+      <c r="F23">
+        <v>0.0010743752354756</v>
+      </c>
+      <c r="G23">
+        <v>0.00104357348755002</v>
+      </c>
+      <c r="H23">
+        <v>1.000662844280686</v>
+      </c>
+      <c r="I23">
+        <v>0.04897090182221258</v>
+      </c>
+      <c r="J23">
+        <v>-0.01169805880635977</v>
+      </c>
+      <c r="K23">
+        <v>-0.08107501268386841</v>
+      </c>
+      <c r="L23">
+        <v>0.1262613981962204</v>
+      </c>
+      <c r="M23">
+        <v>-0.6695541739463806</v>
+      </c>
+      <c r="N23" t="s">
+        <v>150</v>
+      </c>
+      <c r="O23" t="s">
+        <v>210</v>
+      </c>
+      <c r="P23" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="A24">
+        <v>0</v>
+      </c>
+      <c r="B24" t="s">
+        <v>91</v>
+      </c>
+      <c r="C24">
+        <v>0.0009327141461277556</v>
+      </c>
+      <c r="D24">
+        <v>0.000229018391110003</v>
+      </c>
+      <c r="E24">
+        <v>0.002559821121394634</v>
+      </c>
+      <c r="F24">
+        <v>0.001236661104485393</v>
+      </c>
+      <c r="G24">
+        <v>0.001166622154414654</v>
+      </c>
+      <c r="H24">
+        <v>1.000768617716909</v>
+      </c>
+      <c r="I24">
+        <v>0.04896826937381646</v>
+      </c>
+      <c r="J24">
+        <v>0.08946655690670013</v>
+      </c>
+      <c r="K24">
+        <v>1.117257356643677</v>
+      </c>
+      <c r="L24">
+        <v>0.146514818072319</v>
+      </c>
+      <c r="M24">
+        <v>5.120739459991455</v>
+      </c>
+      <c r="N24" t="s">
+        <v>151</v>
+      </c>
+      <c r="O24" t="s">
+        <v>211</v>
+      </c>
+      <c r="P24" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
+      <c r="A25">
+        <v>0</v>
+      </c>
+      <c r="B25" t="s">
+        <v>92</v>
+      </c>
+      <c r="C25">
+        <v>0.001799890225091363</v>
+      </c>
+      <c r="D25">
+        <v>0.0009705687989480793</v>
+      </c>
+      <c r="E25">
+        <v>0.004881586879491806</v>
+      </c>
+      <c r="F25">
+        <v>0.001753253862261772</v>
+      </c>
+      <c r="G25">
+        <v>0.001510809175670147</v>
+      </c>
+      <c r="H25">
+        <v>1.001037494465747</v>
+      </c>
+      <c r="I25">
+        <v>0.04895971797374894</v>
+      </c>
+      <c r="J25">
+        <v>0.1988223940134048</v>
+      </c>
+      <c r="K25">
+        <v>23.00231170654297</v>
+      </c>
+      <c r="L25">
+        <v>0.2794042229652405</v>
+      </c>
+      <c r="M25">
+        <v>11.37986850738525</v>
+      </c>
+      <c r="N25" t="s">
+        <v>152</v>
+      </c>
+      <c r="O25" t="s">
+        <v>212</v>
+      </c>
+      <c r="P25" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="A26">
+        <v>0</v>
+      </c>
+      <c r="B26" t="s">
+        <v>93</v>
+      </c>
+      <c r="C26">
+        <v>0.003443460975979279</v>
+      </c>
+      <c r="D26">
+        <v>0.001999632688239217</v>
+      </c>
+      <c r="E26">
+        <v>0.009667600505053997</v>
+      </c>
+      <c r="F26">
+        <v>0.002310250652953982</v>
+      </c>
+      <c r="G26">
+        <v>0.001870410516858101</v>
+      </c>
+      <c r="H26">
+        <v>1.001121761683086</v>
+      </c>
+      <c r="I26">
+        <v>0.04914733183340182</v>
+      </c>
+      <c r="J26">
+        <v>0.2068385779857635</v>
+      </c>
+      <c r="K26">
+        <v>694.2025756835938</v>
+      </c>
+      <c r="L26">
+        <v>0.5533381700515747</v>
+      </c>
+      <c r="M26">
+        <v>11.83868503570557</v>
+      </c>
+      <c r="N26" t="s">
+        <v>153</v>
+      </c>
+      <c r="O26" t="s">
+        <v>213</v>
+      </c>
+      <c r="P26" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
+      <c r="A27">
+        <v>0</v>
+      </c>
+      <c r="B27" t="s">
+        <v>94</v>
+      </c>
+      <c r="C27">
+        <v>0.006605556740544347</v>
+      </c>
+      <c r="D27">
+        <v>0.003728380426764488</v>
+      </c>
+      <c r="E27">
+        <v>0.019267862662673</v>
+      </c>
+      <c r="F27">
+        <v>0.002770982449874282</v>
+      </c>
+      <c r="G27">
+        <v>0.002139504998922348</v>
+      </c>
+      <c r="H27">
+        <v>1.00099879417467</v>
+      </c>
+      <c r="I27">
+        <v>0.04920728730670573</v>
+      </c>
+      <c r="J27">
+        <v>0.1935025453567505</v>
+      </c>
+      <c r="K27">
+        <v>197103.9375</v>
+      </c>
+      <c r="L27">
+        <v>1.102822184562683</v>
+      </c>
+      <c r="M27">
+        <v>11.07537937164307</v>
+      </c>
+      <c r="N27" t="s">
+        <v>154</v>
+      </c>
+      <c r="O27" t="s">
+        <v>214</v>
+      </c>
+      <c r="P27" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16">
+      <c r="A28">
+        <v>0</v>
+      </c>
+      <c r="B28" t="s">
+        <v>95</v>
+      </c>
+      <c r="C28">
+        <v>0.01585778497349501</v>
+      </c>
+      <c r="D28">
+        <v>0.008557260036468506</v>
+      </c>
+      <c r="E28">
+        <v>0.04809005931019783</v>
+      </c>
+      <c r="F28">
+        <v>0.003003209130838513</v>
+      </c>
+      <c r="G28">
+        <v>0.002269354881718755</v>
+      </c>
+      <c r="H28">
+        <v>1.000797712533746</v>
+      </c>
+      <c r="I28">
+        <v>0.05076091911624914</v>
+      </c>
+      <c r="J28">
+        <v>0.1779423952102661</v>
+      </c>
+      <c r="K28">
+        <v>1327756869632</v>
+      </c>
+      <c r="L28">
+        <v>2.752499580383301</v>
+      </c>
+      <c r="M28">
+        <v>10.18477344512939</v>
+      </c>
+      <c r="N28" t="s">
+        <v>155</v>
+      </c>
+      <c r="O28" t="s">
+        <v>215</v>
+      </c>
+      <c r="P28" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
+      <c r="A29">
+        <v>0</v>
+      </c>
+      <c r="B29" t="s">
+        <v>96</v>
+      </c>
+      <c r="C29">
+        <v>0.03105950285957571</v>
+      </c>
+      <c r="D29">
+        <v>0.01689404062926769</v>
+      </c>
+      <c r="E29">
+        <v>0.09535910189151764</v>
+      </c>
+      <c r="F29">
+        <v>0.00294859055429697</v>
+      </c>
+      <c r="G29">
+        <v>0.002289955737069249</v>
+      </c>
+      <c r="H29">
+        <v>1.000431174627324</v>
+      </c>
+      <c r="I29">
+        <v>0.05227973425799742</v>
+      </c>
+      <c r="J29">
+        <v>0.1771623343229294</v>
+      </c>
+      <c r="K29">
+        <v>6.841001701044981E+23</v>
+      </c>
+      <c r="L29">
+        <v>5.458006858825684</v>
+      </c>
+      <c r="M29">
+        <v>10.1401252746582</v>
+      </c>
+      <c r="N29" t="s">
+        <v>156</v>
+      </c>
+      <c r="O29" t="s">
+        <v>216</v>
+      </c>
+      <c r="P29" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
+      <c r="A30">
+        <v>0</v>
+      </c>
+      <c r="B30" t="s">
+        <v>97</v>
+      </c>
+      <c r="C30">
+        <v>0.07589592235577694</v>
+      </c>
+      <c r="D30">
+        <v>0.04073144868016243</v>
+      </c>
+      <c r="E30">
+        <v>0.2337855100631714</v>
+      </c>
+      <c r="F30">
+        <v>0.00271491426974535</v>
+      </c>
+      <c r="G30">
+        <v>0.002361643826588988</v>
+      </c>
+      <c r="H30">
+        <v>1.000764839335831</v>
+      </c>
+      <c r="I30">
+        <v>0.05791969908583712</v>
+      </c>
+      <c r="J30">
+        <v>0.1742257177829742</v>
+      </c>
+      <c r="K30" t="s">
+        <v>128</v>
+      </c>
+      <c r="L30">
+        <v>13.38102912902832</v>
+      </c>
+      <c r="M30">
+        <v>9.972043991088867</v>
+      </c>
+      <c r="N30" t="s">
+        <v>157</v>
+      </c>
+      <c r="O30" t="s">
+        <v>217</v>
+      </c>
+      <c r="P30" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16">
+      <c r="A31">
+        <v>0</v>
+      </c>
+      <c r="B31" t="s">
+        <v>98</v>
+      </c>
+      <c r="C31">
+        <v>0.148343252384992</v>
+      </c>
+      <c r="D31">
+        <v>0.07904426753520966</v>
+      </c>
+      <c r="E31">
+        <v>0.4636601805686951</v>
+      </c>
+      <c r="F31">
+        <v>0.002682717284187675</v>
+      </c>
+      <c r="G31">
+        <v>0.002548201708123088</v>
+      </c>
+      <c r="H31">
+        <v>1.001897184822521</v>
+      </c>
+      <c r="I31">
+        <v>0.06814115359016776</v>
+      </c>
+      <c r="J31">
+        <v>0.170478880405426</v>
+      </c>
+      <c r="K31" t="s">
+        <v>128</v>
+      </c>
+      <c r="L31">
+        <v>26.53821754455566</v>
+      </c>
+      <c r="M31">
+        <v>9.757589340209961</v>
+      </c>
+      <c r="N31" t="s">
+        <v>158</v>
+      </c>
+      <c r="O31" t="s">
+        <v>218</v>
+      </c>
+      <c r="P31" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16">
+      <c r="A32">
+        <v>0</v>
+      </c>
+      <c r="B32" t="s">
+        <v>99</v>
+      </c>
+      <c r="C32">
+        <v>0.0006126567297814038</v>
+      </c>
+      <c r="D32">
+        <v>1.012037500913721E-05</v>
+      </c>
+      <c r="E32">
+        <v>0.003446060698479414</v>
+      </c>
+      <c r="F32">
+        <v>0.0009346152655780315</v>
+      </c>
+      <c r="G32">
+        <v>0.0009256696794182062</v>
+      </c>
+      <c r="H32">
+        <v>1.000412861982143</v>
+      </c>
+      <c r="I32">
+        <v>0.04899336500979768</v>
+      </c>
+      <c r="J32">
+        <v>0.002936795353889465</v>
+      </c>
+      <c r="K32">
+        <v>0.0337519645690918</v>
+      </c>
+      <c r="L32">
+        <v>0.1972399353981018</v>
+      </c>
+      <c r="M32">
+        <v>0.1680914461612701</v>
+      </c>
+      <c r="N32" t="s">
+        <v>159</v>
+      </c>
+      <c r="O32" t="s">
+        <v>219</v>
+      </c>
+      <c r="P32" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16">
+      <c r="A33">
+        <v>0</v>
+      </c>
+      <c r="B33" t="s">
+        <v>100</v>
+      </c>
+      <c r="C33">
+        <v>0.0008090147693939576</v>
+      </c>
+      <c r="D33">
+        <v>0.0002184837067034096</v>
+      </c>
+      <c r="E33">
+        <v>0.004262662027031183</v>
+      </c>
+      <c r="F33">
+        <v>0.001123863970860839</v>
+      </c>
+      <c r="G33">
+        <v>0.001082480535842478</v>
+      </c>
+      <c r="H33">
+        <v>1.000612611819603</v>
+      </c>
+      <c r="I33">
+        <v>0.04898529370523502</v>
+      </c>
+      <c r="J33">
+        <v>0.05125522613525391</v>
+      </c>
+      <c r="K33">
+        <v>1.045746326446533</v>
+      </c>
+      <c r="L33">
+        <v>0.2439792156219482</v>
+      </c>
+      <c r="M33">
+        <v>2.933662176132202</v>
+      </c>
+      <c r="N33" t="s">
+        <v>160</v>
+      </c>
+      <c r="O33" t="s">
+        <v>220</v>
+      </c>
+      <c r="P33" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16">
+      <c r="A34">
+        <v>0</v>
+      </c>
+      <c r="B34" t="s">
+        <v>101</v>
+      </c>
+      <c r="C34">
+        <v>0.001001185507763471</v>
+      </c>
+      <c r="D34">
+        <v>0.000430647749453783</v>
+      </c>
+      <c r="E34">
+        <v>0.005280098412185907</v>
+      </c>
+      <c r="F34">
+        <v>0.001293390756472945</v>
+      </c>
+      <c r="G34">
+        <v>0.00122196355368942</v>
+      </c>
+      <c r="H34">
+        <v>1.000736691146194</v>
+      </c>
+      <c r="I34">
+        <v>0.04897006050282642</v>
+      </c>
+      <c r="J34">
+        <v>0.08156055212020874</v>
+      </c>
+      <c r="K34">
+        <v>3.098740577697754</v>
+      </c>
+      <c r="L34">
+        <v>0.302213579416275</v>
+      </c>
+      <c r="M34">
+        <v>4.668228626251221</v>
+      </c>
+      <c r="N34" t="s">
+        <v>161</v>
+      </c>
+      <c r="O34" t="s">
+        <v>221</v>
+      </c>
+      <c r="P34" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16">
+      <c r="A35">
+        <v>0</v>
+      </c>
+      <c r="B35" t="s">
+        <v>102</v>
+      </c>
+      <c r="C35">
+        <v>0.001922103583513203</v>
+      </c>
+      <c r="D35">
+        <v>0.001101120607927442</v>
+      </c>
+      <c r="E35">
+        <v>0.01049282029271126</v>
+      </c>
+      <c r="F35">
+        <v>0.001832049572840333</v>
+      </c>
+      <c r="G35">
+        <v>0.001565634622238576</v>
+      </c>
+      <c r="H35">
+        <v>1.00092809335166</v>
+      </c>
+      <c r="I35">
+        <v>0.04902088669240681</v>
+      </c>
+      <c r="J35">
+        <v>0.1049403846263885</v>
+      </c>
+      <c r="K35">
+        <v>35.79410171508789</v>
+      </c>
+      <c r="L35">
+        <v>0.6005707383155823</v>
+      </c>
+      <c r="M35">
+        <v>6.006404876708984</v>
+      </c>
+      <c r="N35" t="s">
+        <v>162</v>
+      </c>
+      <c r="O35" t="s">
+        <v>222</v>
+      </c>
+      <c r="P35" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16">
+      <c r="A36">
+        <v>0</v>
+      </c>
+      <c r="B36" t="s">
+        <v>103</v>
+      </c>
+      <c r="C36">
+        <v>0.003669872079588998</v>
+      </c>
+      <c r="D36">
+        <v>0.002215920714661479</v>
+      </c>
+      <c r="E36">
+        <v>0.02074011974036694</v>
+      </c>
+      <c r="F36">
+        <v>0.002410599030554295</v>
+      </c>
+      <c r="G36">
+        <v>0.001919927773997188</v>
+      </c>
+      <c r="H36">
+        <v>1.001046906272016</v>
+      </c>
+      <c r="I36">
+        <v>0.04918600431617405</v>
+      </c>
+      <c r="J36">
+        <v>0.1068422347307205</v>
+      </c>
+      <c r="K36">
+        <v>1408.702514648438</v>
+      </c>
+      <c r="L36">
+        <v>1.18708872795105</v>
+      </c>
+      <c r="M36">
+        <v>6.115259647369385</v>
+      </c>
+      <c r="N36" t="s">
+        <v>163</v>
+      </c>
+      <c r="O36" t="s">
+        <v>223</v>
+      </c>
+      <c r="P36" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16">
+      <c r="A37">
+        <v>0</v>
+      </c>
+      <c r="B37" t="s">
+        <v>104</v>
+      </c>
+      <c r="C37">
+        <v>0.007031972060043069</v>
+      </c>
+      <c r="D37">
+        <v>0.004070562310516834</v>
+      </c>
+      <c r="E37">
+        <v>0.04145022109150887</v>
+      </c>
+      <c r="F37">
+        <v>0.002858104882761836</v>
+      </c>
+      <c r="G37">
+        <v>0.002180309733375907</v>
+      </c>
+      <c r="H37">
+        <v>1.000875929139819</v>
+      </c>
+      <c r="I37">
+        <v>0.04930001534221296</v>
+      </c>
+      <c r="J37">
+        <v>0.0982036367058754</v>
+      </c>
+      <c r="K37">
+        <v>601966.0625</v>
+      </c>
+      <c r="L37">
+        <v>2.372459411621094</v>
+      </c>
+      <c r="M37">
+        <v>5.6208176612854</v>
+      </c>
+      <c r="N37" t="s">
+        <v>164</v>
+      </c>
+      <c r="O37" t="s">
+        <v>224</v>
+      </c>
+      <c r="P37" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16">
+      <c r="A38">
+        <v>0</v>
+      </c>
+      <c r="B38" t="s">
+        <v>105</v>
+      </c>
+      <c r="C38">
+        <v>0.0168818822829842</v>
+      </c>
+      <c r="D38">
+        <v>0.00929164607077837</v>
+      </c>
+      <c r="E38">
+        <v>0.1036254987120628</v>
+      </c>
+      <c r="F38">
+        <v>0.003020872361958027</v>
+      </c>
+      <c r="G38">
+        <v>0.002290122909471393</v>
+      </c>
+      <c r="H38">
+        <v>1.000752040265706</v>
+      </c>
+      <c r="I38">
+        <v>0.05075417209386936</v>
+      </c>
+      <c r="J38">
+        <v>0.08966563642024994</v>
+      </c>
+      <c r="K38">
+        <v>14409304899584</v>
+      </c>
+      <c r="L38">
+        <v>5.931145191192627</v>
+      </c>
+      <c r="M38">
+        <v>5.132133960723877</v>
+      </c>
+      <c r="N38" t="s">
+        <v>165</v>
+      </c>
+      <c r="O38" t="s">
+        <v>225</v>
+      </c>
+      <c r="P38" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16">
+      <c r="A39">
+        <v>0</v>
+      </c>
+      <c r="B39" t="s">
+        <v>106</v>
+      </c>
+      <c r="C39">
+        <v>0.0330878571060246</v>
+      </c>
+      <c r="D39">
+        <v>0.01781212911009789</v>
+      </c>
+      <c r="E39">
+        <v>0.2072898149490356</v>
+      </c>
+      <c r="F39">
+        <v>0.002970208181068301</v>
+      </c>
+      <c r="G39">
+        <v>0.002317919628694654</v>
+      </c>
+      <c r="H39">
+        <v>1.000460317251326</v>
+      </c>
+      <c r="I39">
+        <v>0.05224625336010784</v>
+      </c>
+      <c r="J39">
+        <v>0.08592862635850906</v>
+      </c>
+      <c r="K39">
+        <v>1.315633201259861E+25</v>
+      </c>
+      <c r="L39">
+        <v>11.86451244354248</v>
+      </c>
+      <c r="M39">
+        <v>4.918241024017334</v>
+      </c>
+      <c r="N39" t="s">
+        <v>166</v>
+      </c>
+      <c r="O39" t="s">
+        <v>226</v>
+      </c>
+      <c r="P39" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16">
+      <c r="A40">
+        <v>0</v>
+      </c>
+      <c r="B40" t="s">
+        <v>107</v>
+      </c>
+      <c r="C40">
+        <v>0.0800603205165072</v>
+      </c>
+      <c r="D40">
+        <v>0.04251091182231903</v>
+      </c>
+      <c r="E40">
+        <v>0.5053588151931763</v>
+      </c>
+      <c r="F40">
+        <v>0.002741548465564847</v>
+      </c>
+      <c r="G40">
+        <v>0.002427542582154274</v>
+      </c>
+      <c r="H40">
+        <v>1.000637340355823</v>
+      </c>
+      <c r="I40">
+        <v>0.05830312487006046</v>
+      </c>
+      <c r="J40">
+        <v>0.0841202512383461</v>
+      </c>
+      <c r="K40" t="s">
+        <v>128</v>
+      </c>
+      <c r="L40">
+        <v>28.92489433288574</v>
+      </c>
+      <c r="M40">
+        <v>4.814736366271973</v>
+      </c>
+      <c r="N40" t="s">
+        <v>167</v>
+      </c>
+      <c r="O40" t="s">
+        <v>227</v>
+      </c>
+      <c r="P40" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16">
+      <c r="A41">
+        <v>0</v>
+      </c>
+      <c r="B41" t="s">
+        <v>108</v>
+      </c>
+      <c r="C41">
+        <v>0.1663654852617165</v>
+      </c>
+      <c r="D41">
+        <v>0.08757153153419495</v>
+      </c>
+      <c r="E41">
+        <v>1.114185214042664</v>
+      </c>
+      <c r="F41">
+        <v>0.002709541469812393</v>
+      </c>
+      <c r="G41">
+        <v>0.002682714723050594</v>
+      </c>
+      <c r="H41">
+        <v>1.001774785801714</v>
+      </c>
+      <c r="I41">
+        <v>0.06841367929647706</v>
+      </c>
+      <c r="J41">
+        <v>0.07859692722558975</v>
+      </c>
+      <c r="K41" t="s">
+        <v>128</v>
+      </c>
+      <c r="L41">
+        <v>63.77189636230469</v>
+      </c>
+      <c r="M41">
+        <v>4.49860143661499</v>
+      </c>
+      <c r="N41" t="s">
+        <v>168</v>
+      </c>
+      <c r="O41" t="s">
+        <v>228</v>
+      </c>
+      <c r="P41" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
+      <c r="A42">
+        <v>0</v>
+      </c>
+      <c r="B42" t="s">
+        <v>109</v>
+      </c>
+      <c r="C42">
+        <v>0.0002086793378413935</v>
+      </c>
+      <c r="D42">
+        <v>6.719584052916616E-05</v>
+      </c>
+      <c r="E42">
+        <v>0.001093829981982708</v>
+      </c>
+      <c r="F42">
+        <v>0.0009730003075674176</v>
+      </c>
+      <c r="G42">
+        <v>0.0009493340039625764</v>
+      </c>
+      <c r="H42">
+        <v>1.000235711036398</v>
+      </c>
+      <c r="I42">
+        <v>0.04917041226780874</v>
+      </c>
+      <c r="J42">
+        <v>0.06143170595169067</v>
+      </c>
+      <c r="K42">
+        <v>0.2463898658752441</v>
+      </c>
+      <c r="L42">
+        <v>0.06260683387517929</v>
+      </c>
+      <c r="M42">
+        <v>3.51612663269043</v>
+      </c>
+      <c r="N42" t="s">
+        <v>169</v>
+      </c>
+      <c r="O42" t="s">
+        <v>229</v>
+      </c>
+      <c r="P42" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
+      <c r="A43">
+        <v>0</v>
+      </c>
+      <c r="B43" t="s">
+        <v>110</v>
+      </c>
+      <c r="C43">
+        <v>0.0002661064506041268</v>
+      </c>
+      <c r="D43">
+        <v>0.0001614636566955596</v>
+      </c>
+      <c r="E43">
+        <v>0.0009184640948660672</v>
+      </c>
+      <c r="F43">
+        <v>0.001177300466224551</v>
+      </c>
+      <c r="G43">
+        <v>0.001115265535190701</v>
+      </c>
+      <c r="H43">
+        <v>1.000430032687526</v>
+      </c>
+      <c r="I43">
+        <v>0.04909850572108727</v>
+      </c>
+      <c r="J43">
+        <v>0.1757974624633789</v>
+      </c>
+      <c r="K43">
+        <v>0.6967835426330566</v>
+      </c>
+      <c r="L43">
+        <v>0.05256953462958336</v>
+      </c>
+      <c r="M43">
+        <v>10.06200504302979</v>
+      </c>
+      <c r="N43" t="s">
+        <v>170</v>
+      </c>
+      <c r="O43" t="s">
+        <v>230</v>
+      </c>
+      <c r="P43" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
+      <c r="A44">
+        <v>0</v>
+      </c>
+      <c r="B44" t="s">
+        <v>111</v>
+      </c>
+      <c r="C44">
+        <v>0.0003182727971897425</v>
+      </c>
+      <c r="D44">
+        <v>0.0002562806766945869</v>
+      </c>
+      <c r="E44">
+        <v>0.001036489265970886</v>
+      </c>
+      <c r="F44">
+        <v>0.001358953304588795</v>
+      </c>
+      <c r="G44">
+        <v>0.001258920878171921</v>
+      </c>
+      <c r="H44">
+        <v>1.00055479965047</v>
+      </c>
+      <c r="I44">
+        <v>0.04908118703365784</v>
+      </c>
+      <c r="J44">
+        <v>0.2472583949565887</v>
+      </c>
+      <c r="K44">
+        <v>1.31528115272522</v>
+      </c>
+      <c r="L44">
+        <v>0.05932486429810524</v>
+      </c>
+      <c r="M44">
+        <v>14.15216827392578</v>
+      </c>
+      <c r="N44" t="s">
+        <v>171</v>
+      </c>
+      <c r="O44" t="s">
+        <v>231</v>
+      </c>
+      <c r="P44" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="A45">
+        <v>0</v>
+      </c>
+      <c r="B45" t="s">
+        <v>112</v>
+      </c>
+      <c r="C45">
+        <v>0.0005319477635731633</v>
+      </c>
+      <c r="D45">
+        <v>0.0005310527631081641</v>
+      </c>
+      <c r="E45">
+        <v>0.001503692823462188</v>
+      </c>
+      <c r="F45">
+        <v>0.001939662033692002</v>
+      </c>
+      <c r="G45">
+        <v>0.001618414418771863</v>
+      </c>
+      <c r="H45">
+        <v>1.000837811578165</v>
+      </c>
+      <c r="I45">
+        <v>0.04903374430406098</v>
+      </c>
+      <c r="J45">
+        <v>0.3531657159328461</v>
+      </c>
+      <c r="K45">
+        <v>4.693628311157227</v>
+      </c>
+      <c r="L45">
+        <v>0.08606588840484619</v>
+      </c>
+      <c r="M45">
+        <v>20.21391677856445</v>
+      </c>
+      <c r="N45" t="s">
+        <v>172</v>
+      </c>
+      <c r="O45" t="s">
+        <v>232</v>
+      </c>
+      <c r="P45" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="A46">
+        <v>0</v>
+      </c>
+      <c r="B46" t="s">
+        <v>113</v>
+      </c>
+      <c r="C46">
+        <v>0.0008515995860059494</v>
+      </c>
+      <c r="D46">
+        <v>0.0008233009139075875</v>
+      </c>
+      <c r="E46">
+        <v>0.002540273126214743</v>
+      </c>
+      <c r="F46">
+        <v>0.002541185356676579</v>
+      </c>
+      <c r="G46">
+        <v>0.001984677510336041</v>
+      </c>
+      <c r="H46">
+        <v>1.000922678002484</v>
+      </c>
+      <c r="I46">
+        <v>0.04923756278668312</v>
+      </c>
+      <c r="J46">
+        <v>0.3240993618965149</v>
+      </c>
+      <c r="K46">
+        <v>13.8186731338501</v>
+      </c>
+      <c r="L46">
+        <v>0.145395964384079</v>
+      </c>
+      <c r="M46">
+        <v>18.55026435852051</v>
+      </c>
+      <c r="N46" t="s">
+        <v>173</v>
+      </c>
+      <c r="O46" t="s">
+        <v>233</v>
+      </c>
+      <c r="P46" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="A47">
+        <v>0</v>
+      </c>
+      <c r="B47" t="s">
+        <v>114</v>
+      </c>
+      <c r="C47">
+        <v>0.00135953532595703</v>
+      </c>
+      <c r="D47">
+        <v>0.001182194682769477</v>
+      </c>
+      <c r="E47">
+        <v>0.004650026559829712</v>
+      </c>
+      <c r="F47">
+        <v>0.002934838179498911</v>
+      </c>
+      <c r="G47">
+        <v>0.002240686910226941</v>
+      </c>
+      <c r="H47">
+        <v>1.00079779042958</v>
+      </c>
+      <c r="I47">
+        <v>0.04935383558943489</v>
+      </c>
+      <c r="J47">
+        <v>0.2542339563369751</v>
+      </c>
+      <c r="K47">
+        <v>46.97091674804688</v>
+      </c>
+      <c r="L47">
+        <v>0.266150563955307</v>
+      </c>
+      <c r="M47">
+        <v>14.55142402648926</v>
+      </c>
+      <c r="N47" t="s">
+        <v>174</v>
+      </c>
+      <c r="O47" t="s">
+        <v>234</v>
+      </c>
+      <c r="P47" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16">
+      <c r="A48">
+        <v>0</v>
+      </c>
+      <c r="B48" t="s">
+        <v>115</v>
+      </c>
+      <c r="C48">
+        <v>0.002632937581033637</v>
+      </c>
+      <c r="D48">
+        <v>0.001928141922689974</v>
+      </c>
+      <c r="E48">
+        <v>0.01107113249599934</v>
+      </c>
+      <c r="F48">
+        <v>0.003038807073608041</v>
+      </c>
+      <c r="G48">
+        <v>0.002312160329893231</v>
+      </c>
+      <c r="H48">
+        <v>1.000540849622436</v>
+      </c>
+      <c r="I48">
+        <v>0.05089264448937743</v>
+      </c>
+      <c r="J48">
+        <v>0.1741594076156616</v>
+      </c>
+      <c r="K48">
+        <v>549.234619140625</v>
+      </c>
+      <c r="L48">
+        <v>0.6336712241172791</v>
+      </c>
+      <c r="M48">
+        <v>9.968249320983887</v>
+      </c>
+      <c r="N48" t="s">
+        <v>175</v>
+      </c>
+      <c r="O48" t="s">
+        <v>235</v>
+      </c>
+      <c r="P48" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16">
+      <c r="A49">
+        <v>0</v>
+      </c>
+      <c r="B49" t="s">
+        <v>116</v>
+      </c>
+      <c r="C49">
+        <v>0.004528551251715486</v>
+      </c>
+      <c r="D49">
+        <v>0.002983213402330875</v>
+      </c>
+      <c r="E49">
+        <v>0.02137372456490993</v>
+      </c>
+      <c r="F49">
+        <v>0.002959772478789091</v>
+      </c>
+      <c r="G49">
+        <v>0.002370779169723392</v>
+      </c>
+      <c r="H49">
+        <v>1.000295369615515</v>
+      </c>
+      <c r="I49">
+        <v>0.05251602469116587</v>
+      </c>
+      <c r="J49">
+        <v>0.139573872089386</v>
+      </c>
+      <c r="K49">
+        <v>17298.890625</v>
+      </c>
+      <c r="L49">
+        <v>1.223353981971741</v>
+      </c>
+      <c r="M49">
+        <v>7.988698959350586</v>
+      </c>
+      <c r="N49" t="s">
+        <v>176</v>
+      </c>
+      <c r="O49" t="s">
+        <v>236</v>
+      </c>
+      <c r="P49" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16">
+      <c r="A50">
+        <v>0</v>
+      </c>
+      <c r="B50" t="s">
+        <v>117</v>
+      </c>
+      <c r="C50">
+        <v>0.009998862674455905</v>
+      </c>
+      <c r="D50">
+        <v>0.005980595480650663</v>
+      </c>
+      <c r="E50">
+        <v>0.0547085739672184</v>
+      </c>
+      <c r="F50">
+        <v>0.002744779223576188</v>
+      </c>
+      <c r="G50">
+        <v>0.002508056117221713</v>
+      </c>
+      <c r="H50">
+        <v>1.000560840967818</v>
+      </c>
+      <c r="I50">
+        <v>0.05834495019415879</v>
+      </c>
+      <c r="J50">
+        <v>0.1093173325061798</v>
+      </c>
+      <c r="K50">
+        <v>304483104</v>
+      </c>
+      <c r="L50">
+        <v>3.131319046020508</v>
+      </c>
+      <c r="M50">
+        <v>6.256925106048584</v>
+      </c>
+      <c r="N50" t="s">
+        <v>177</v>
+      </c>
+      <c r="O50" t="s">
+        <v>237</v>
+      </c>
+      <c r="P50" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16">
+      <c r="A51">
+        <v>0</v>
+      </c>
+      <c r="B51" t="s">
+        <v>118</v>
+      </c>
+      <c r="C51">
+        <v>0.01830275512651549</v>
+      </c>
+      <c r="D51">
+        <v>0.01034711673855782</v>
+      </c>
+      <c r="E51">
+        <v>0.1027935445308685</v>
+      </c>
+      <c r="F51">
+        <v>0.002728314138948917</v>
+      </c>
+      <c r="G51">
+        <v>0.002711737062782049</v>
+      </c>
+      <c r="H51">
+        <v>1.001499388004896</v>
+      </c>
+      <c r="I51">
+        <v>0.0686493809617631</v>
+      </c>
+      <c r="J51">
+        <v>0.1006592065095901</v>
+      </c>
+      <c r="K51">
+        <v>442305597145088</v>
+      </c>
+      <c r="L51">
+        <v>5.883527278900146</v>
+      </c>
+      <c r="M51">
+        <v>5.76136589050293</v>
+      </c>
+      <c r="N51" t="s">
+        <v>178</v>
+      </c>
+      <c r="O51" t="s">
+        <v>238</v>
+      </c>
+      <c r="P51" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16">
+      <c r="A52">
+        <v>0</v>
+      </c>
+      <c r="B52" t="s">
+        <v>119</v>
+      </c>
+      <c r="C52">
+        <v>0.0002247565483057536</v>
+      </c>
+      <c r="D52">
+        <v>0.0003119055763818324</v>
+      </c>
+      <c r="E52">
+        <v>0.0007150778546929359</v>
+      </c>
+      <c r="F52">
+        <v>0.001118181273341179</v>
+      </c>
+      <c r="G52">
+        <v>0.00107943790499121</v>
+      </c>
+      <c r="H52">
+        <v>0.9996907682212378</v>
+      </c>
+      <c r="I52">
+        <v>0.04969636010959013</v>
+      </c>
+      <c r="J52">
+        <v>0.4361840784549713</v>
+      </c>
+      <c r="K52">
+        <v>1.777263879776001</v>
+      </c>
+      <c r="L52">
+        <v>0.04092844575643539</v>
+      </c>
+      <c r="M52">
+        <v>24.96558570861816</v>
+      </c>
+      <c r="N52" t="s">
+        <v>179</v>
+      </c>
+      <c r="O52" t="s">
+        <v>239</v>
+      </c>
+      <c r="P52" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16">
+      <c r="A53">
+        <v>0</v>
+      </c>
+      <c r="B53" t="s">
+        <v>120</v>
+      </c>
+      <c r="C53">
+        <v>0.0002736887318614471</v>
+      </c>
+      <c r="D53">
+        <v>0.0003753821074496955</v>
+      </c>
+      <c r="E53">
+        <v>0.0007748856442049146</v>
+      </c>
+      <c r="F53">
+        <v>0.001298942253924906</v>
+      </c>
+      <c r="G53">
+        <v>0.001228062901645899</v>
+      </c>
+      <c r="H53">
+        <v>0.9999586610795502</v>
+      </c>
+      <c r="I53">
+        <v>0.04954705613378152</v>
+      </c>
+      <c r="J53">
+        <v>0.484435498714447</v>
+      </c>
+      <c r="K53">
+        <v>2.419680118560791</v>
+      </c>
+      <c r="L53">
+        <v>0.04435162618756294</v>
+      </c>
+      <c r="M53">
+        <v>27.72731971740723</v>
+      </c>
+      <c r="N53" t="s">
+        <v>180</v>
+      </c>
+      <c r="O53" t="s">
+        <v>240</v>
+      </c>
+      <c r="P53" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16">
+      <c r="A54">
+        <v>0</v>
+      </c>
+      <c r="B54" t="s">
+        <v>121</v>
+      </c>
+      <c r="C54">
+        <v>0.0003139503708554754</v>
+      </c>
+      <c r="D54">
+        <v>0.0004301239969208837</v>
+      </c>
+      <c r="E54">
+        <v>0.0008194711990654469</v>
+      </c>
+      <c r="F54">
+        <v>0.001465844339691103</v>
+      </c>
+      <c r="G54">
+        <v>0.001330886385403574</v>
+      </c>
+      <c r="H54">
+        <v>1.000171688601776</v>
+      </c>
+      <c r="I54">
+        <v>0.04945741493801473</v>
+      </c>
+      <c r="J54">
+        <v>0.5248799324035645</v>
+      </c>
+      <c r="K54">
+        <v>3.09074878692627</v>
+      </c>
+      <c r="L54">
+        <v>0.04690353944897652</v>
+      </c>
+      <c r="M54">
+        <v>30.04221153259277</v>
+      </c>
+      <c r="N54" t="s">
+        <v>181</v>
+      </c>
+      <c r="O54" t="s">
+        <v>241</v>
+      </c>
+      <c r="P54" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16">
+      <c r="A55">
+        <v>0</v>
+      </c>
+      <c r="B55" t="s">
+        <v>61</v>
+      </c>
+      <c r="C55">
+        <v>0.0004517172770068056</v>
+      </c>
+      <c r="D55">
+        <v>0.0006101165199652314</v>
+      </c>
+      <c r="E55">
+        <v>0.0009731933241710067</v>
+      </c>
+      <c r="F55">
+        <v>0.002091016387566924</v>
+      </c>
+      <c r="G55">
+        <v>0.001720696338452399</v>
+      </c>
+      <c r="H55">
+        <v>1.000601366207502</v>
+      </c>
+      <c r="I55">
+        <v>0.04925663153802683</v>
+      </c>
+      <c r="J55">
+        <v>0.6269222497940063</v>
+      </c>
+      <c r="K55">
+        <v>6.375186443328857</v>
+      </c>
+      <c r="L55">
+        <v>0.05570203438401222</v>
+      </c>
+      <c r="M55">
+        <v>35.88274383544922</v>
+      </c>
+      <c r="N55" t="s">
+        <v>182</v>
+      </c>
+      <c r="O55" t="s">
+        <v>242</v>
+      </c>
+      <c r="P55" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16">
+      <c r="A56">
+        <v>0</v>
+      </c>
+      <c r="B56" t="s">
+        <v>122</v>
+      </c>
+      <c r="C56">
+        <v>0.0006035961824179331</v>
+      </c>
+      <c r="D56">
+        <v>0.0008031160687096417</v>
+      </c>
+      <c r="E56">
+        <v>0.001200982602313161</v>
+      </c>
+      <c r="F56">
+        <v>0.002678824588656425</v>
+      </c>
+      <c r="G56">
+        <v>0.002076019765809178</v>
+      </c>
+      <c r="H56">
+        <v>1.000640768603257</v>
+      </c>
+      <c r="I56">
+        <v>0.04957762583377028</v>
+      </c>
+      <c r="J56">
+        <v>0.6687158346176147</v>
+      </c>
+      <c r="K56">
+        <v>12.87296772003174</v>
+      </c>
+      <c r="L56">
+        <v>0.06873986124992371</v>
+      </c>
+      <c r="M56">
+        <v>38.27485275268555</v>
+      </c>
+      <c r="N56" t="s">
+        <v>183</v>
+      </c>
+      <c r="O56" t="s">
+        <v>243</v>
+      </c>
+      <c r="P56" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16">
+      <c r="A57">
+        <v>0</v>
+      </c>
+      <c r="B57" t="s">
+        <v>123</v>
+      </c>
+      <c r="C57">
+        <v>0.0007721227792913817</v>
+      </c>
+      <c r="D57">
+        <v>0.0009806735906749964</v>
+      </c>
+      <c r="E57">
+        <v>0.001563581405207515</v>
+      </c>
+      <c r="F57">
+        <v>0.002978114644065499</v>
+      </c>
+      <c r="G57">
+        <v>0.002250515157356858</v>
+      </c>
+      <c r="H57">
+        <v>1.000650101605531</v>
+      </c>
+      <c r="I57">
+        <v>0.04959134431491563</v>
+      </c>
+      <c r="J57">
+        <v>0.6271970272064209</v>
+      </c>
+      <c r="K57">
+        <v>23.80195999145508</v>
+      </c>
+      <c r="L57">
+        <v>0.08949369192123413</v>
+      </c>
+      <c r="M57">
+        <v>35.89846801757812</v>
+      </c>
+      <c r="N57" t="s">
+        <v>184</v>
+      </c>
+      <c r="O57" t="s">
+        <v>244</v>
+      </c>
+      <c r="P57" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16">
+      <c r="A58">
+        <v>0</v>
+      </c>
+      <c r="B58" t="s">
+        <v>124</v>
+      </c>
+      <c r="C58">
+        <v>0.001036909058136108</v>
+      </c>
+      <c r="D58">
+        <v>0.001215565134771168</v>
+      </c>
+      <c r="E58">
+        <v>0.002398230135440826</v>
+      </c>
+      <c r="F58">
+        <v>0.003037377027794719</v>
+      </c>
+      <c r="G58">
+        <v>0.002438005525618792</v>
+      </c>
+      <c r="H58">
+        <v>1.000213997222606</v>
+      </c>
+      <c r="I58">
+        <v>0.05167567532025988</v>
+      </c>
+      <c r="J58">
+        <v>0.5068592429161072</v>
+      </c>
+      <c r="K58">
+        <v>52.50698852539062</v>
+      </c>
+      <c r="L58">
+        <v>0.1372659355401993</v>
+      </c>
+      <c r="M58">
+        <v>29.01077270507812</v>
+      </c>
+      <c r="N58" t="s">
+        <v>185</v>
+      </c>
+      <c r="O58" t="s">
+        <v>245</v>
+      </c>
+      <c r="P58" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16">
+      <c r="A59">
+        <v>0</v>
+      </c>
+      <c r="B59" t="s">
+        <v>125</v>
+      </c>
+      <c r="C59">
+        <v>0.001272746546252149</v>
+      </c>
+      <c r="D59">
+        <v>0.001399980741553009</v>
+      </c>
+      <c r="E59">
+        <v>0.00342195201665163</v>
+      </c>
+      <c r="F59">
+        <v>0.002908776514232159</v>
+      </c>
+      <c r="G59">
+        <v>0.002434280700981617</v>
+      </c>
+      <c r="H59">
+        <v>0.9997211748955712</v>
+      </c>
+      <c r="I59">
+        <v>0.05420679738738828</v>
+      </c>
+      <c r="J59">
+        <v>0.409117579460144</v>
+      </c>
+      <c r="K59">
+        <v>96.82425689697266</v>
+      </c>
+      <c r="L59">
+        <v>0.1958600431680679</v>
+      </c>
+      <c r="M59">
+        <v>23.41639709472656</v>
+      </c>
+      <c r="N59" t="s">
+        <v>186</v>
+      </c>
+      <c r="O59" t="s">
+        <v>246</v>
+      </c>
+      <c r="P59" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16">
+      <c r="A60">
+        <v>0</v>
+      </c>
+      <c r="B60" t="s">
+        <v>126</v>
+      </c>
+      <c r="C60">
+        <v>0.001605409878418132</v>
+      </c>
+      <c r="D60">
+        <v>0.001740744221024215</v>
+      </c>
+      <c r="E60">
+        <v>0.0056669139303267</v>
+      </c>
+      <c r="F60">
+        <v>0.002699287142604589</v>
+      </c>
+      <c r="G60">
+        <v>0.002524242969229817</v>
+      </c>
+      <c r="H60">
+        <v>0.9999318459997774</v>
+      </c>
+      <c r="I60">
+        <v>0.06092034829777291</v>
+      </c>
+      <c r="J60">
+        <v>0.3071767389774323</v>
+      </c>
+      <c r="K60">
+        <v>297.137939453125</v>
+      </c>
+      <c r="L60">
+        <v>0.3243534862995148</v>
+      </c>
+      <c r="M60">
+        <v>17.5816764831543</v>
+      </c>
+      <c r="N60" t="s">
+        <v>187</v>
+      </c>
+      <c r="O60" t="s">
+        <v>247</v>
+      </c>
+      <c r="P60" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16">
+      <c r="A61">
+        <v>0</v>
+      </c>
+      <c r="B61" t="s">
+        <v>127</v>
+      </c>
+      <c r="C61">
+        <v>0.001838736509442959</v>
+      </c>
+      <c r="D61">
+        <v>0.001987788360565901</v>
+      </c>
+      <c r="E61">
+        <v>0.007635069545358419</v>
+      </c>
+      <c r="F61">
+        <v>0.002674614544957876</v>
+      </c>
+      <c r="G61">
+        <v>0.002698813797906041</v>
+      </c>
+      <c r="H61">
+        <v>1.001346389228886</v>
+      </c>
+      <c r="I61">
+        <v>0.06932424638266356</v>
+      </c>
+      <c r="J61">
+        <v>0.2603497505187988</v>
+      </c>
+      <c r="K61">
+        <v>667.8887939453125</v>
+      </c>
+      <c r="L61">
+        <v>0.4370035231113434</v>
+      </c>
+      <c r="M61">
+        <v>14.90146923065186</v>
+      </c>
+      <c r="N61" t="s">
+        <v>188</v>
+      </c>
+      <c r="O61" t="s">
+        <v>248</v>
+      </c>
+      <c r="P61" t="s">
+        <v>308</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P61"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:16">
+      <c r="B1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J1" t="s">
+        <v>54</v>
+      </c>
+      <c r="K1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L1" t="s">
+        <v>56</v>
+      </c>
+      <c r="M1" t="s">
+        <v>57</v>
+      </c>
+      <c r="N1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O1" t="s">
+        <v>59</v>
+      </c>
+      <c r="P1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2">
+        <v>0.0009952024922401429</v>
+      </c>
+      <c r="D2">
+        <v>-0.002636610064655542</v>
+      </c>
+      <c r="E2">
+        <v>0.04503464698791504</v>
+      </c>
+      <c r="F2">
+        <v>0.0008554814849048853</v>
+      </c>
+      <c r="G2">
+        <v>0.0008663327316753566</v>
+      </c>
+      <c r="H2">
+        <v>1.000576009946482</v>
+      </c>
+      <c r="I2">
+        <v>0.04896137020148717</v>
+      </c>
+      <c r="J2">
+        <v>-0.05854625627398491</v>
+      </c>
+      <c r="K2">
+        <v>-0.9998247027397156</v>
+      </c>
+      <c r="L2">
+        <v>2.577618837356567</v>
+      </c>
+      <c r="M2">
+        <v>-3.350974082946777</v>
+      </c>
+      <c r="N2" t="s">
+        <v>309</v>
+      </c>
+      <c r="O2" t="s">
+        <v>369</v>
+      </c>
+      <c r="P2" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3">
+        <v>0.00132367153448009</v>
+      </c>
+      <c r="D3">
+        <v>-0.003667039563879371</v>
+      </c>
+      <c r="E3">
+        <v>0.07254373282194138</v>
+      </c>
+      <c r="F3">
+        <v>0.001012838794849813</v>
+      </c>
+      <c r="G3">
+        <v>0.0009692645398899913</v>
+      </c>
+      <c r="H3">
+        <v>1.000808515214522</v>
+      </c>
+      <c r="I3">
+        <v>0.0489080478999448</v>
+      </c>
+      <c r="J3">
+        <v>-0.05054936558008194</v>
+      </c>
+      <c r="K3">
+        <v>-0.9999940395355225</v>
+      </c>
+      <c r="L3">
+        <v>4.152138710021973</v>
+      </c>
+      <c r="M3">
+        <v>-2.893261194229126</v>
+      </c>
+      <c r="N3" t="s">
+        <v>310</v>
+      </c>
+      <c r="O3" t="s">
+        <v>370</v>
+      </c>
+      <c r="P3" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4">
+        <v>0.001650125375718094</v>
+      </c>
+      <c r="D4">
+        <v>-0.001777029829099774</v>
+      </c>
+      <c r="E4">
+        <v>0.05713972821831703</v>
+      </c>
+      <c r="F4">
+        <v>0.001154551398940384</v>
+      </c>
+      <c r="G4">
+        <v>0.001101662404835224</v>
+      </c>
+      <c r="H4">
+        <v>1.00092332439839</v>
+      </c>
+      <c r="I4">
+        <v>0.04893085488733089</v>
+      </c>
+      <c r="J4">
+        <v>-0.03109972551465034</v>
+      </c>
+      <c r="K4">
+        <v>-0.9970524907112122</v>
+      </c>
+      <c r="L4">
+        <v>3.270469427108765</v>
+      </c>
+      <c r="M4">
+        <v>-1.780034780502319</v>
+      </c>
+      <c r="N4" t="s">
+        <v>311</v>
+      </c>
+      <c r="O4" t="s">
+        <v>371</v>
+      </c>
+      <c r="P4" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5">
+        <v>0.003253394994747907</v>
+      </c>
+      <c r="D5">
+        <v>-0.001325192744843662</v>
+      </c>
+      <c r="E5">
+        <v>0.08112823963165283</v>
+      </c>
+      <c r="F5">
+        <v>0.001657702843658626</v>
+      </c>
+      <c r="G5">
+        <v>0.001459612743929029</v>
+      </c>
+      <c r="H5">
+        <v>1.00110577840894</v>
+      </c>
+      <c r="I5">
+        <v>0.04894885079303557</v>
+      </c>
+      <c r="J5">
+        <v>-0.016334543004632</v>
+      </c>
+      <c r="K5">
+        <v>-0.9870181083679199</v>
+      </c>
+      <c r="L5">
+        <v>4.643484592437744</v>
+      </c>
+      <c r="M5">
+        <v>-0.9349296092987061</v>
+      </c>
+      <c r="N5" t="s">
+        <v>312</v>
+      </c>
+      <c r="O5" t="s">
+        <v>372</v>
+      </c>
+      <c r="P5" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6">
+        <v>0</v>
+      </c>
+      <c r="B6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6">
+        <v>0.006381022137243401</v>
+      </c>
+      <c r="D6">
+        <v>0.003354608779773116</v>
+      </c>
+      <c r="E6">
+        <v>0.01833981089293957</v>
+      </c>
+      <c r="F6">
+        <v>0.00218567019328475</v>
+      </c>
+      <c r="G6">
+        <v>0.001784898340702057</v>
+      </c>
+      <c r="H6">
+        <v>1.00120127533848</v>
+      </c>
+      <c r="I6">
+        <v>0.04909729042476027</v>
+      </c>
+      <c r="J6">
+        <v>0.1829140335321426</v>
+      </c>
+      <c r="K6">
+        <v>58168.2734375</v>
+      </c>
+      <c r="L6">
+        <v>1.04970383644104</v>
+      </c>
+      <c r="M6">
+        <v>10.46933174133301</v>
+      </c>
+      <c r="N6" t="s">
+        <v>313</v>
+      </c>
+      <c r="O6" t="s">
+        <v>373</v>
+      </c>
+      <c r="P6" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7">
+        <v>0</v>
+      </c>
+      <c r="B7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7">
+        <v>0.01253506980631696</v>
+      </c>
+      <c r="D7">
+        <v>0.006556070875376463</v>
+      </c>
+      <c r="E7">
+        <v>0.03590384870767593</v>
+      </c>
+      <c r="F7">
+        <v>0.00264669512398541</v>
+      </c>
+      <c r="G7">
+        <v>0.002072105649858713</v>
+      </c>
+      <c r="H7">
+        <v>1.00104295002754</v>
+      </c>
+      <c r="I7">
+        <v>0.0491963498491934</v>
+      </c>
+      <c r="J7">
+        <v>0.1826007813215256</v>
+      </c>
+      <c r="K7">
+        <v>1982193792</v>
+      </c>
+      <c r="L7">
+        <v>2.055005311965942</v>
+      </c>
+      <c r="M7">
+        <v>10.45140266418457</v>
+      </c>
+      <c r="N7" t="s">
+        <v>314</v>
+      </c>
+      <c r="O7" t="s">
+        <v>374</v>
+      </c>
+      <c r="P7" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8">
+        <v>0</v>
+      </c>
+      <c r="B8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8">
+        <v>0.03069620600381771</v>
+      </c>
+      <c r="D8">
+        <v>0.01583617553114891</v>
+      </c>
+      <c r="E8">
+        <v>0.08928082883358002</v>
+      </c>
+      <c r="F8">
+        <v>0.002910170936957002</v>
+      </c>
+      <c r="G8">
+        <v>0.002228680765256286</v>
+      </c>
+      <c r="H8">
+        <v>1.000712748016749</v>
+      </c>
+      <c r="I8">
+        <v>0.05085982878199578</v>
+      </c>
+      <c r="J8">
+        <v>0.1773748695850372</v>
+      </c>
+      <c r="K8">
+        <v>2.26089280651289E+22</v>
+      </c>
+      <c r="L8">
+        <v>5.110108852386475</v>
+      </c>
+      <c r="M8">
+        <v>10.15229034423828</v>
+      </c>
+      <c r="N8" t="s">
+        <v>315</v>
+      </c>
+      <c r="O8" t="s">
+        <v>375</v>
+      </c>
+      <c r="P8" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9">
+        <v>0</v>
+      </c>
+      <c r="B9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C9">
+        <v>0.0607322064403467</v>
+      </c>
+      <c r="D9">
+        <v>0.03114325366914272</v>
+      </c>
+      <c r="E9">
+        <v>0.1789334118366241</v>
+      </c>
+      <c r="F9">
+        <v>0.002935540163889527</v>
+      </c>
+      <c r="G9">
+        <v>0.002263546921312809</v>
+      </c>
+      <c r="H9">
+        <v>1.000407100285757</v>
+      </c>
+      <c r="I9">
+        <v>0.05230209125491456</v>
+      </c>
+      <c r="J9">
+        <v>0.1740494072437286</v>
+      </c>
+      <c r="K9" t="s">
+        <v>128</v>
+      </c>
+      <c r="L9">
+        <v>10.24149513244629</v>
+      </c>
+      <c r="M9">
+        <v>9.961953163146973</v>
+      </c>
+      <c r="N9" t="s">
+        <v>316</v>
+      </c>
+      <c r="O9" t="s">
+        <v>376</v>
+      </c>
+      <c r="P9" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10">
+        <v>0</v>
+      </c>
+      <c r="B10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10">
+        <v>0.151328083931748</v>
+      </c>
+      <c r="D10">
+        <v>0.07802821695804596</v>
+      </c>
+      <c r="E10">
+        <v>0.4688454866409302</v>
+      </c>
+      <c r="F10">
+        <v>0.002732494380325079</v>
+      </c>
+      <c r="G10">
+        <v>0.002356800949200988</v>
+      </c>
+      <c r="H10">
+        <v>1.000916138125441</v>
+      </c>
+      <c r="I10">
+        <v>0.05820111326850902</v>
+      </c>
+      <c r="J10">
+        <v>0.1664263010025024</v>
+      </c>
+      <c r="K10" t="s">
+        <v>128</v>
+      </c>
+      <c r="L10">
+        <v>26.83500480651855</v>
+      </c>
+      <c r="M10">
+        <v>9.525633811950684</v>
+      </c>
+      <c r="N10" t="s">
+        <v>317</v>
+      </c>
+      <c r="O10" t="s">
+        <v>377</v>
+      </c>
+      <c r="P10" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11">
+        <v>0</v>
+      </c>
+      <c r="B11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11">
+        <v>0.295973574617074</v>
+      </c>
+      <c r="D11">
+        <v>0.1573200970888138</v>
+      </c>
+      <c r="E11">
+        <v>1.008399844169617</v>
+      </c>
+      <c r="F11">
+        <v>0.002641432918608189</v>
+      </c>
+      <c r="G11">
+        <v>0.002471783198416233</v>
+      </c>
+      <c r="H11">
+        <v>1.002172582619339</v>
+      </c>
+      <c r="I11">
+        <v>0.06761948594284269</v>
+      </c>
+      <c r="J11">
+        <v>0.1560096442699432</v>
+      </c>
+      <c r="K11" t="s">
+        <v>128</v>
+      </c>
+      <c r="L11">
+        <v>57.71712875366211</v>
+      </c>
+      <c r="M11">
+        <v>8.929422378540039</v>
+      </c>
+      <c r="N11" t="s">
+        <v>318</v>
+      </c>
+      <c r="O11" t="s">
+        <v>378</v>
+      </c>
+      <c r="P11" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12">
+        <v>0</v>
+      </c>
+      <c r="B12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12">
+        <v>0.001334911170163473</v>
+      </c>
+      <c r="D12">
+        <v>-0.0001940845249919221</v>
+      </c>
+      <c r="E12">
+        <v>0.009083286859095097</v>
+      </c>
+      <c r="F12">
+        <v>0.000877275422681123</v>
+      </c>
+      <c r="G12">
+        <v>0.0008741266210563481</v>
+      </c>
+      <c r="H12">
+        <v>1.000520758517882</v>
+      </c>
+      <c r="I12">
+        <v>0.0489854394738341</v>
+      </c>
+      <c r="J12">
+        <v>-0.02136721275746822</v>
+      </c>
+      <c r="K12">
+        <v>-0.4705115556716919</v>
+      </c>
+      <c r="L12">
+        <v>0.5198941826820374</v>
+      </c>
+      <c r="M12">
+        <v>-1.222981333732605</v>
+      </c>
+      <c r="N12" t="s">
+        <v>319</v>
+      </c>
+      <c r="O12" t="s">
+        <v>379</v>
+      </c>
+      <c r="P12" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13">
+        <v>0</v>
+      </c>
+      <c r="B13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13">
+        <v>0.001775842670467348</v>
+      </c>
+      <c r="D13">
+        <v>0.000334456650307402</v>
+      </c>
+      <c r="E13">
+        <v>0.01100355945527554</v>
+      </c>
+      <c r="F13">
+        <v>0.001039438066072762</v>
+      </c>
+      <c r="G13">
+        <v>0.0009955433197319508</v>
+      </c>
+      <c r="H13">
+        <v>1.00075735334101</v>
+      </c>
+      <c r="I13">
+        <v>0.04893143464002322</v>
+      </c>
+      <c r="J13">
+        <v>0.03039531409740448</v>
+      </c>
+      <c r="K13">
+        <v>1.991105079650879</v>
+      </c>
+      <c r="L13">
+        <v>0.6298035979270935</v>
+      </c>
+      <c r="M13">
+        <v>1.73971688747406</v>
+      </c>
+      <c r="N13" t="s">
+        <v>320</v>
+      </c>
+      <c r="O13" t="s">
+        <v>380</v>
+      </c>
+      <c r="P13" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14">
+        <v>0</v>
+      </c>
+      <c r="B14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C14">
+        <v>0.002214077962050144</v>
+      </c>
+      <c r="D14">
+        <v>0.0009056230774149299</v>
+      </c>
+      <c r="E14">
+        <v>0.01218083593994379</v>
+      </c>
+      <c r="F14">
+        <v>0.001182628911919892</v>
+      </c>
+      <c r="G14">
+        <v>0.001127204392105341</v>
+      </c>
+      <c r="H14">
+        <v>1.000866772079426</v>
+      </c>
+      <c r="I14">
+        <v>0.04895126915960361</v>
+      </c>
+      <c r="J14">
+        <v>0.07434818893671036</v>
+      </c>
+      <c r="K14">
+        <v>18.40461540222168</v>
+      </c>
+      <c r="L14">
+        <v>0.6971865892410278</v>
+      </c>
+      <c r="M14">
+        <v>4.255419254302979</v>
+      </c>
+      <c r="N14" t="s">
+        <v>321</v>
+      </c>
+      <c r="O14" t="s">
+        <v>381</v>
+      </c>
+      <c r="P14" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15">
+        <v>0</v>
+      </c>
+      <c r="B15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C15">
+        <v>0.004375690259212021</v>
+      </c>
+      <c r="D15">
+        <v>0.002873888239264488</v>
+      </c>
+      <c r="E15">
+        <v>0.03300260752439499</v>
+      </c>
+      <c r="F15">
+        <v>0.001703156041912735</v>
+      </c>
+      <c r="G15">
+        <v>0.001475862460210919</v>
+      </c>
+      <c r="H15">
+        <v>1.001070011924178</v>
+      </c>
+      <c r="I15">
+        <v>0.04896815512785127</v>
+      </c>
+      <c r="J15">
+        <v>0.08708064258098602</v>
+      </c>
+      <c r="K15">
+        <v>12104.1416015625</v>
+      </c>
+      <c r="L15">
+        <v>1.888948798179626</v>
+      </c>
+      <c r="M15">
+        <v>4.984178066253662</v>
+      </c>
+      <c r="N15" t="s">
+        <v>322</v>
+      </c>
+      <c r="O15" t="s">
+        <v>382</v>
+      </c>
+      <c r="P15" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16">
+        <v>0</v>
+      </c>
+      <c r="B16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16">
+        <v>0.008613097138896946</v>
+      </c>
+      <c r="D16">
+        <v>0.005182460881769657</v>
+      </c>
+      <c r="E16">
+        <v>0.04537694528698921</v>
+      </c>
+      <c r="F16">
+        <v>0.002240240108221769</v>
+      </c>
+      <c r="G16">
+        <v>0.001819791039451957</v>
+      </c>
+      <c r="H16">
+        <v>1.001183146523279</v>
+      </c>
+      <c r="I16">
+        <v>0.0491146357029742</v>
+      </c>
+      <c r="J16">
+        <v>0.1142091155052185</v>
+      </c>
+      <c r="K16">
+        <v>22613160</v>
+      </c>
+      <c r="L16">
+        <v>2.597210884094238</v>
+      </c>
+      <c r="M16">
+        <v>6.53691291809082</v>
+      </c>
+      <c r="N16" t="s">
+        <v>323</v>
+      </c>
+      <c r="O16" t="s">
+        <v>383</v>
+      </c>
+      <c r="P16" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17">
+        <v>0</v>
+      </c>
+      <c r="B17" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17">
+        <v>0.01694977277412797</v>
+      </c>
+      <c r="D17">
+        <v>0.009570516645908356</v>
+      </c>
+      <c r="E17">
+        <v>0.07196807861328125</v>
+      </c>
+      <c r="F17">
+        <v>0.002700681565329432</v>
+      </c>
+      <c r="G17">
+        <v>0.002107211388647556</v>
+      </c>
+      <c r="H17">
+        <v>1.001025176253054</v>
+      </c>
+      <c r="I17">
+        <v>0.0492012570787327</v>
+      </c>
+      <c r="J17">
+        <v>0.1329828053712845</v>
+      </c>
+      <c r="K17">
+        <v>35615777226752</v>
+      </c>
+      <c r="L17">
+        <v>4.119190216064453</v>
+      </c>
+      <c r="M17">
+        <v>7.611450672149658</v>
+      </c>
+      <c r="N17" t="s">
+        <v>324</v>
+      </c>
+      <c r="O17" t="s">
+        <v>384</v>
+      </c>
+      <c r="P17" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18">
+        <v>0</v>
+      </c>
+      <c r="B18" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18">
+        <v>0.04174134987933198</v>
+      </c>
+      <c r="D18">
+        <v>0.02291415631771088</v>
+      </c>
+      <c r="E18">
+        <v>0.1751949936151505</v>
+      </c>
+      <c r="F18">
+        <v>0.002946323715150356</v>
+      </c>
+      <c r="G18">
+        <v>0.002252720296382904</v>
+      </c>
+      <c r="H18">
+        <v>1.000755622608885</v>
+      </c>
+      <c r="I18">
+        <v>0.05079182880343619</v>
+      </c>
+      <c r="J18">
+        <v>0.1307923048734665</v>
+      </c>
+      <c r="K18">
+        <v>1.710817466613773E+32</v>
+      </c>
+      <c r="L18">
+        <v>10.02752208709717</v>
+      </c>
+      <c r="M18">
+        <v>7.486074447631836</v>
+      </c>
+      <c r="N18" t="s">
+        <v>325</v>
+      </c>
+      <c r="O18" t="s">
+        <v>385</v>
+      </c>
+      <c r="P18" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19">
+        <v>0</v>
+      </c>
+      <c r="B19" t="s">
+        <v>86</v>
+      </c>
+      <c r="C19">
+        <v>0.08231053309555586</v>
+      </c>
+      <c r="D19">
+        <v>0.04299810528755188</v>
+      </c>
+      <c r="E19">
+        <v>0.3159620761871338</v>
+      </c>
+      <c r="F19">
+        <v>0.002950792200863361</v>
+      </c>
+      <c r="G19">
+        <v>0.002280836226418614</v>
+      </c>
+      <c r="H19">
+        <v>1.000433708768542</v>
+      </c>
+      <c r="I19">
+        <v>0.05229634017223155</v>
+      </c>
+      <c r="J19">
+        <v>0.1360862851142883</v>
+      </c>
+      <c r="K19" t="s">
+        <v>128</v>
+      </c>
+      <c r="L19">
+        <v>18.08451652526855</v>
+      </c>
+      <c r="M19">
+        <v>7.789082527160645</v>
+      </c>
+      <c r="N19" t="s">
+        <v>326</v>
+      </c>
+      <c r="O19" t="s">
+        <v>386</v>
+      </c>
+      <c r="P19" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20">
+        <v>0</v>
+      </c>
+      <c r="B20" t="s">
+        <v>87</v>
+      </c>
+      <c r="C20">
+        <v>0.2053329306975024</v>
+      </c>
+      <c r="D20">
+        <v>0.1042203903198242</v>
+      </c>
+      <c r="E20">
+        <v>0.7617989182472229</v>
+      </c>
+      <c r="F20">
+        <v>0.002722728997468948</v>
+      </c>
+      <c r="G20">
+        <v>0.002354462863877416</v>
+      </c>
+      <c r="H20">
+        <v>1.000620340491821</v>
+      </c>
+      <c r="I20">
+        <v>0.057978030362671</v>
+      </c>
+      <c r="J20">
+        <v>0.1368082612752914</v>
+      </c>
+      <c r="K20" t="s">
+        <v>128</v>
+      </c>
+      <c r="L20">
+        <v>43.60258865356445</v>
+      </c>
+      <c r="M20">
+        <v>7.830405712127686</v>
+      </c>
+      <c r="N20" t="s">
+        <v>327</v>
+      </c>
+      <c r="O20" t="s">
+        <v>387</v>
+      </c>
+      <c r="P20" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21">
+        <v>0</v>
+      </c>
+      <c r="B21" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21">
+        <v>0.4041740075693175</v>
+      </c>
+      <c r="D21">
+        <v>0.2066266089677811</v>
+      </c>
+      <c r="E21">
+        <v>1.464905619621277</v>
+      </c>
+      <c r="F21">
+        <v>0.002661186503246427</v>
+      </c>
+      <c r="G21">
+        <v>0.002486685523763299</v>
+      </c>
+      <c r="H21">
+        <v>1.002050183598531</v>
+      </c>
+      <c r="I21">
+        <v>0.06771386325557802</v>
+      </c>
+      <c r="J21">
+        <v>0.1410511434078217</v>
+      </c>
+      <c r="K21" t="s">
+        <v>128</v>
+      </c>
+      <c r="L21">
+        <v>83.84585571289062</v>
+      </c>
+      <c r="M21">
+        <v>8.07325267791748</v>
+      </c>
+      <c r="N21" t="s">
+        <v>328</v>
+      </c>
+      <c r="O21" t="s">
+        <v>388</v>
+      </c>
+      <c r="P21" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22">
+        <v>0</v>
+      </c>
+      <c r="B22" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22">
+        <v>0.0005539719691378193</v>
+      </c>
+      <c r="D22">
+        <v>-0.0003633665619418025</v>
+      </c>
+      <c r="E22">
+        <v>0.001986557617783546</v>
+      </c>
+      <c r="F22">
+        <v>0.00090471759904176</v>
+      </c>
+      <c r="G22">
+        <v>0.0008933966746553779</v>
+      </c>
+      <c r="H22">
+        <v>1.000483097352556</v>
+      </c>
+      <c r="I22">
+        <v>0.04898233632775388</v>
+      </c>
+      <c r="J22">
+        <v>-0.182912677526474</v>
+      </c>
+      <c r="K22">
+        <v>-0.695946216583252</v>
+      </c>
+      <c r="L22">
+        <v>0.1137033104896545</v>
+      </c>
+      <c r="M22">
+        <v>-10.46925449371338</v>
+      </c>
+      <c r="N22" t="s">
+        <v>329</v>
+      </c>
+      <c r="O22" t="s">
+        <v>389</v>
+      </c>
+      <c r="P22" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23">
+        <v>0</v>
+      </c>
+      <c r="B23" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23">
+        <v>0.0007333917535779289</v>
+      </c>
+      <c r="D23">
+        <v>-7.037597242742777E-05</v>
+      </c>
+      <c r="E23">
+        <v>0.00245971349067986</v>
+      </c>
+      <c r="F23">
+        <v>0.00107857771217823</v>
+      </c>
+      <c r="G23">
+        <v>0.00104888912755996</v>
+      </c>
+      <c r="H23">
+        <v>1.000669295737782</v>
+      </c>
+      <c r="I23">
+        <v>0.04895181963655644</v>
+      </c>
+      <c r="J23">
+        <v>-0.0286114513874054</v>
+      </c>
+      <c r="K23">
+        <v>-0.2059555649757385</v>
+      </c>
+      <c r="L23">
+        <v>0.1407850235700607</v>
+      </c>
+      <c r="M23">
+        <v>-1.637615084648132</v>
+      </c>
+      <c r="N23" t="s">
+        <v>330</v>
+      </c>
+      <c r="O23" t="s">
+        <v>390</v>
+      </c>
+      <c r="P23" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="A24">
+        <v>0</v>
+      </c>
+      <c r="B24" t="s">
+        <v>91</v>
+      </c>
+      <c r="C24">
+        <v>0.0009095018823043042</v>
+      </c>
+      <c r="D24">
+        <v>0.0001494396710768342</v>
+      </c>
+      <c r="E24">
+        <v>0.002989634172990918</v>
+      </c>
+      <c r="F24">
+        <v>0.001236708019860089</v>
+      </c>
+      <c r="G24">
+        <v>0.001172923250123858</v>
+      </c>
+      <c r="H24">
+        <v>1.000787461910582</v>
+      </c>
+      <c r="I24">
+        <v>0.04893827824682729</v>
+      </c>
+      <c r="J24">
+        <v>0.04998593777418137</v>
+      </c>
+      <c r="K24">
+        <v>0.6318062543869019</v>
+      </c>
+      <c r="L24">
+        <v>0.1711157560348511</v>
+      </c>
+      <c r="M24">
+        <v>2.861012697219849</v>
+      </c>
+      <c r="N24" t="s">
+        <v>331</v>
+      </c>
+      <c r="O24" t="s">
+        <v>391</v>
+      </c>
+      <c r="P24" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
+      <c r="A25">
+        <v>0</v>
+      </c>
+      <c r="B25" t="s">
+        <v>92</v>
+      </c>
+      <c r="C25">
+        <v>0.001755440898637071</v>
+      </c>
+      <c r="D25">
+        <v>0.0009431981015950441</v>
+      </c>
+      <c r="E25">
+        <v>0.00473305769264698</v>
+      </c>
+      <c r="F25">
+        <v>0.001755410456098616</v>
+      </c>
+      <c r="G25">
+        <v>0.001511895679868758</v>
+      </c>
+      <c r="H25">
+        <v>1.001000251055299</v>
+      </c>
+      <c r="I25">
+        <v>0.04893098009260355</v>
+      </c>
+      <c r="J25">
+        <v>0.1992788165807724</v>
+      </c>
+      <c r="K25">
+        <v>20.9422550201416</v>
+      </c>
+      <c r="L25">
+        <v>0.2709029614925385</v>
+      </c>
+      <c r="M25">
+        <v>11.40599250793457</v>
+      </c>
+      <c r="N25" t="s">
+        <v>332</v>
+      </c>
+      <c r="O25" t="s">
+        <v>392</v>
+      </c>
+      <c r="P25" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="A26">
+        <v>0</v>
+      </c>
+      <c r="B26" t="s">
+        <v>93</v>
+      </c>
+      <c r="C26">
+        <v>0.003357707794388782</v>
+      </c>
+      <c r="D26">
+        <v>0.001953797647729516</v>
+      </c>
+      <c r="E26">
+        <v>0.00921082217246294</v>
+      </c>
+      <c r="F26">
+        <v>0.002310781041160226</v>
+      </c>
+      <c r="G26">
+        <v>0.001873507513664663</v>
+      </c>
+      <c r="H26">
+        <v>1.001118565316203</v>
+      </c>
+      <c r="I26">
+        <v>0.04913589307396635</v>
+      </c>
+      <c r="J26">
+        <v>0.2121197879314423</v>
+      </c>
+      <c r="K26">
+        <v>597.5653686523438</v>
+      </c>
+      <c r="L26">
+        <v>0.5271938443183899</v>
+      </c>
+      <c r="M26">
+        <v>12.14096260070801</v>
+      </c>
+      <c r="N26" t="s">
+        <v>333</v>
+      </c>
+      <c r="O26" t="s">
+        <v>393</v>
+      </c>
+      <c r="P26" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
+      <c r="A27">
+        <v>0</v>
+      </c>
+      <c r="B27" t="s">
+        <v>94</v>
+      </c>
+      <c r="C27">
+        <v>0.006437719471717263</v>
+      </c>
+      <c r="D27">
+        <v>0.003626742865890265</v>
+      </c>
+      <c r="E27">
+        <v>0.01817329786717892</v>
+      </c>
+      <c r="F27">
+        <v>0.00276570045389235</v>
+      </c>
+      <c r="G27">
+        <v>0.002141972770914435</v>
+      </c>
+      <c r="H27">
+        <v>1.000992283588457</v>
+      </c>
+      <c r="I27">
+        <v>0.04920001997447434</v>
+      </c>
+      <c r="J27">
+        <v>0.1995643824338913</v>
+      </c>
+      <c r="K27">
+        <v>141433.265625</v>
+      </c>
+      <c r="L27">
+        <v>1.040173292160034</v>
+      </c>
+      <c r="M27">
+        <v>11.42233657836914</v>
+      </c>
+      <c r="N27" t="s">
+        <v>334</v>
+      </c>
+      <c r="O27" t="s">
+        <v>394</v>
+      </c>
+      <c r="P27" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16">
+      <c r="A28">
+        <v>0</v>
+      </c>
+      <c r="B28" t="s">
+        <v>95</v>
+      </c>
+      <c r="C28">
+        <v>0.01544414299846042</v>
+      </c>
+      <c r="D28">
+        <v>0.008265847340226173</v>
+      </c>
+      <c r="E28">
+        <v>0.04483884572982788</v>
+      </c>
+      <c r="F28">
+        <v>0.002995974384248257</v>
+      </c>
+      <c r="G28">
+        <v>0.002265760209411383</v>
+      </c>
+      <c r="H28">
+        <v>1.000797712533746</v>
+      </c>
+      <c r="I28">
+        <v>0.05076091911624914</v>
+      </c>
+      <c r="J28">
+        <v>0.1843456774950027</v>
+      </c>
+      <c r="K28">
+        <v>515102572544</v>
+      </c>
+      <c r="L28">
+        <v>2.566411972045898</v>
+      </c>
+      <c r="M28">
+        <v>10.55127429962158</v>
+      </c>
+      <c r="N28" t="s">
+        <v>335</v>
+      </c>
+      <c r="O28" t="s">
+        <v>395</v>
+      </c>
+      <c r="P28" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
+      <c r="A29">
+        <v>0</v>
+      </c>
+      <c r="B29" t="s">
+        <v>96</v>
+      </c>
+      <c r="C29">
+        <v>0.03023351528529387</v>
+      </c>
+      <c r="D29">
+        <v>0.0158921480178833</v>
+      </c>
+      <c r="E29">
+        <v>0.09007486701011658</v>
+      </c>
+      <c r="F29">
+        <v>0.002953637391328812</v>
+      </c>
+      <c r="G29">
+        <v>0.002293445635586977</v>
+      </c>
+      <c r="H29">
+        <v>1.000431174627324</v>
+      </c>
+      <c r="I29">
+        <v>0.05227973425799742</v>
+      </c>
+      <c r="J29">
+        <v>0.1764326542615891</v>
+      </c>
+      <c r="K29">
+        <v>2.70862829656709E+22</v>
+      </c>
+      <c r="L29">
+        <v>5.155556678771973</v>
+      </c>
+      <c r="M29">
+        <v>10.09836101531982</v>
+      </c>
+      <c r="N29" t="s">
+        <v>336</v>
+      </c>
+      <c r="O29" t="s">
+        <v>396</v>
+      </c>
+      <c r="P29" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
+      <c r="A30">
+        <v>0</v>
+      </c>
+      <c r="B30" t="s">
+        <v>97</v>
+      </c>
+      <c r="C30">
+        <v>0.07386951888589312</v>
+      </c>
+      <c r="D30">
+        <v>0.03828170895576477</v>
+      </c>
+      <c r="E30">
+        <v>0.2214686423540115</v>
+      </c>
+      <c r="F30">
+        <v>0.002723023993894458</v>
+      </c>
+      <c r="G30">
+        <v>0.002367222448810935</v>
+      </c>
+      <c r="H30">
+        <v>1.000764839335831</v>
+      </c>
+      <c r="I30">
+        <v>0.05791969908583712</v>
+      </c>
+      <c r="J30">
+        <v>0.1728538572788239</v>
+      </c>
+      <c r="K30" t="s">
+        <v>128</v>
+      </c>
+      <c r="L30">
+        <v>12.67605686187744</v>
+      </c>
+      <c r="M30">
+        <v>9.893524169921875</v>
+      </c>
+      <c r="N30" t="s">
+        <v>337</v>
+      </c>
+      <c r="O30" t="s">
+        <v>397</v>
+      </c>
+      <c r="P30" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16">
+      <c r="A31">
+        <v>0</v>
+      </c>
+      <c r="B31" t="s">
+        <v>98</v>
+      </c>
+      <c r="C31">
+        <v>0.144332458713906</v>
+      </c>
+      <c r="D31">
+        <v>0.07500623911619186</v>
+      </c>
+      <c r="E31">
+        <v>0.4522529542446136</v>
+      </c>
+      <c r="F31">
+        <v>0.002708859508857131</v>
+      </c>
+      <c r="G31">
+        <v>0.0025695173535496</v>
+      </c>
+      <c r="H31">
+        <v>1.001897184822521</v>
+      </c>
+      <c r="I31">
+        <v>0.06814115359016776</v>
+      </c>
+      <c r="J31">
+        <v>0.1658501923084259</v>
+      </c>
+      <c r="K31" t="s">
+        <v>128</v>
+      </c>
+      <c r="L31">
+        <v>25.88530921936035</v>
+      </c>
+      <c r="M31">
+        <v>9.492659568786621</v>
+      </c>
+      <c r="N31" t="s">
+        <v>338</v>
+      </c>
+      <c r="O31" t="s">
+        <v>398</v>
+      </c>
+      <c r="P31" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16">
+      <c r="A32">
+        <v>0</v>
+      </c>
+      <c r="B32" t="s">
+        <v>99</v>
+      </c>
+      <c r="C32">
+        <v>0.0005198373226570095</v>
+      </c>
+      <c r="D32">
+        <v>-4.583394911605865E-05</v>
+      </c>
+      <c r="E32">
+        <v>0.00323661114089191</v>
+      </c>
+      <c r="F32">
+        <v>0.0009319988312199712</v>
+      </c>
+      <c r="G32">
+        <v>0.000927571440115571</v>
+      </c>
+      <c r="H32">
+        <v>1.00042277902795</v>
+      </c>
+      <c r="I32">
+        <v>0.04900064823496103</v>
+      </c>
+      <c r="J32">
+        <v>-0.01416109222918749</v>
+      </c>
+      <c r="K32">
+        <v>-0.1394315361976624</v>
+      </c>
+      <c r="L32">
+        <v>0.1852518171072006</v>
+      </c>
+      <c r="M32">
+        <v>-0.8105292320251465</v>
+      </c>
+      <c r="N32" t="s">
+        <v>339</v>
+      </c>
+      <c r="O32" t="s">
+        <v>399</v>
+      </c>
+      <c r="P32" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16">
+      <c r="A33">
+        <v>0</v>
+      </c>
+      <c r="B33" t="s">
+        <v>100</v>
+      </c>
+      <c r="C33">
+        <v>0.0006856299790317734</v>
+      </c>
+      <c r="D33">
+        <v>0.0001986356073757634</v>
+      </c>
+      <c r="E33">
+        <v>0.004187907092273235</v>
+      </c>
+      <c r="F33">
+        <v>0.001121337641961873</v>
+      </c>
+      <c r="G33">
+        <v>0.001080326735973358</v>
+      </c>
+      <c r="H33">
+        <v>1.000619843205617</v>
+      </c>
+      <c r="I33">
+        <v>0.04897699186085643</v>
+      </c>
+      <c r="J33">
+        <v>0.04743075743317604</v>
+      </c>
+      <c r="K33">
+        <v>0.916609525680542</v>
+      </c>
+      <c r="L33">
+        <v>0.2397005259990692</v>
+      </c>
+      <c r="M33">
+        <v>2.714763402938843</v>
+      </c>
+      <c r="N33" t="s">
+        <v>340</v>
+      </c>
+      <c r="O33" t="s">
+        <v>400</v>
+      </c>
+      <c r="P33" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16">
+      <c r="A34">
+        <v>0</v>
+      </c>
+      <c r="B34" t="s">
+        <v>101</v>
+      </c>
+      <c r="C34">
+        <v>0.0008473962403832146</v>
+      </c>
+      <c r="D34">
+        <v>0.0004143121477682143</v>
+      </c>
+      <c r="E34">
+        <v>0.005210643634200096</v>
+      </c>
+      <c r="F34">
+        <v>0.001297994866035879</v>
+      </c>
+      <c r="G34">
+        <v>0.001221587066538632</v>
+      </c>
+      <c r="H34">
+        <v>1.00073152923639</v>
+      </c>
+      <c r="I34">
+        <v>0.04899850407881436</v>
+      </c>
+      <c r="J34">
+        <v>0.07951266318559647</v>
+      </c>
+      <c r="K34">
+        <v>2.885298490524292</v>
+      </c>
+      <c r="L34">
+        <v>0.298238217830658</v>
+      </c>
+      <c r="M34">
+        <v>4.55101490020752</v>
+      </c>
+      <c r="N34" t="s">
+        <v>341</v>
+      </c>
+      <c r="O34" t="s">
+        <v>401</v>
+      </c>
+      <c r="P34" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16">
+      <c r="A35">
+        <v>0</v>
+      </c>
+      <c r="B35" t="s">
+        <v>102</v>
+      </c>
+      <c r="C35">
+        <v>0.001616961087417159</v>
+      </c>
+      <c r="D35">
+        <v>0.001068383571691811</v>
+      </c>
+      <c r="E35">
+        <v>0.01027038786560297</v>
+      </c>
+      <c r="F35">
+        <v>0.001831764355301857</v>
+      </c>
+      <c r="G35">
+        <v>0.001557869836688042</v>
+      </c>
+      <c r="H35">
+        <v>1.000920805488698</v>
+      </c>
+      <c r="I35">
+        <v>0.04901133650824639</v>
+      </c>
+      <c r="J35">
+        <v>0.1040256321430206</v>
+      </c>
+      <c r="K35">
+        <v>32.05121612548828</v>
+      </c>
+      <c r="L35">
+        <v>0.5878395438194275</v>
+      </c>
+      <c r="M35">
+        <v>5.954047679901123</v>
+      </c>
+      <c r="N35" t="s">
+        <v>342</v>
+      </c>
+      <c r="O35" t="s">
+        <v>402</v>
+      </c>
+      <c r="P35" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16">
+      <c r="A36">
+        <v>0</v>
+      </c>
+      <c r="B36" t="s">
+        <v>103</v>
+      </c>
+      <c r="C36">
+        <v>0.003061844881998979</v>
+      </c>
+      <c r="D36">
+        <v>0.002133800880983472</v>
+      </c>
+      <c r="E36">
+        <v>0.01997216790914536</v>
+      </c>
+      <c r="F36">
+        <v>0.002399760996922851</v>
+      </c>
+      <c r="G36">
+        <v>0.001917403656989336</v>
+      </c>
+      <c r="H36">
+        <v>1.001052301873061</v>
+      </c>
+      <c r="I36">
+        <v>0.04917112805765936</v>
+      </c>
+      <c r="J36">
+        <v>0.1068387180566788</v>
+      </c>
+      <c r="K36">
+        <v>1077.183227539062</v>
+      </c>
+      <c r="L36">
+        <v>1.143133997917175</v>
+      </c>
+      <c r="M36">
+        <v>6.115058422088623</v>
+      </c>
+      <c r="N36" t="s">
+        <v>343</v>
+      </c>
+      <c r="O36" t="s">
+        <v>403</v>
+      </c>
+      <c r="P36" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16">
+      <c r="A37">
+        <v>0</v>
+      </c>
+      <c r="B37" t="s">
+        <v>104</v>
+      </c>
+      <c r="C37">
+        <v>0.005820028954634829</v>
+      </c>
+      <c r="D37">
+        <v>0.00381851103156805</v>
+      </c>
+      <c r="E37">
+        <v>0.03852226212620735</v>
+      </c>
+      <c r="F37">
+        <v>0.002850989578291774</v>
+      </c>
+      <c r="G37">
+        <v>0.00218234583735466</v>
+      </c>
+      <c r="H37">
+        <v>1.000875087923889</v>
+      </c>
+      <c r="I37">
+        <v>0.04929294122926832</v>
+      </c>
+      <c r="J37">
+        <v>0.09912478923797607</v>
+      </c>
+      <c r="K37">
+        <v>264505.75</v>
+      </c>
+      <c r="L37">
+        <v>2.20487380027771</v>
+      </c>
+      <c r="M37">
+        <v>5.673541069030762</v>
+      </c>
+      <c r="N37" t="s">
+        <v>344</v>
+      </c>
+      <c r="O37" t="s">
+        <v>404</v>
+      </c>
+      <c r="P37" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16">
+      <c r="A38">
+        <v>0</v>
+      </c>
+      <c r="B38" t="s">
+        <v>105</v>
+      </c>
+      <c r="C38">
+        <v>0.01385791193034656</v>
+      </c>
+      <c r="D38">
+        <v>0.008154311217367649</v>
+      </c>
+      <c r="E38">
+        <v>0.08417578786611557</v>
+      </c>
+      <c r="F38">
+        <v>0.003020032774657011</v>
+      </c>
+      <c r="G38">
+        <v>0.002296480815857649</v>
+      </c>
+      <c r="H38">
+        <v>1.000752040265706</v>
+      </c>
+      <c r="I38">
+        <v>0.05075417209386936</v>
+      </c>
+      <c r="J38">
+        <v>0.09687240421772003</v>
+      </c>
+      <c r="K38">
+        <v>358456360960</v>
+      </c>
+      <c r="L38">
+        <v>4.817914962768555</v>
+      </c>
+      <c r="M38">
+        <v>5.544622898101807</v>
+      </c>
+      <c r="N38" t="s">
+        <v>345</v>
+      </c>
+      <c r="O38" t="s">
+        <v>405</v>
+      </c>
+      <c r="P38" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16">
+      <c r="A39">
+        <v>0</v>
+      </c>
+      <c r="B39" t="s">
+        <v>106</v>
+      </c>
+      <c r="C39">
+        <v>0.02704146749778153</v>
+      </c>
+      <c r="D39">
+        <v>0.01514000538736582</v>
+      </c>
+      <c r="E39">
+        <v>0.1571207493543625</v>
+      </c>
+      <c r="F39">
+        <v>0.002973963972181082</v>
+      </c>
+      <c r="G39">
+        <v>0.002314315410330892</v>
+      </c>
+      <c r="H39">
+        <v>1.000460317251326</v>
+      </c>
+      <c r="I39">
+        <v>0.05224625336010784</v>
+      </c>
+      <c r="J39">
+        <v>0.09635904431343079</v>
+      </c>
+      <c r="K39">
+        <v>2.393654194748164E+21</v>
+      </c>
+      <c r="L39">
+        <v>8.99301815032959</v>
+      </c>
+      <c r="M39">
+        <v>5.51524019241333</v>
+      </c>
+      <c r="N39" t="s">
+        <v>346</v>
+      </c>
+      <c r="O39" t="s">
+        <v>406</v>
+      </c>
+      <c r="P39" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16">
+      <c r="A40">
+        <v>0</v>
+      </c>
+      <c r="B40" t="s">
+        <v>107</v>
+      </c>
+      <c r="C40">
+        <v>0.06531791801912687</v>
+      </c>
+      <c r="D40">
+        <v>0.03855270147323608</v>
+      </c>
+      <c r="E40">
+        <v>0.4269315600395203</v>
+      </c>
+      <c r="F40">
+        <v>0.002733250148594379</v>
+      </c>
+      <c r="G40">
+        <v>0.002415689872577786</v>
+      </c>
+      <c r="H40">
+        <v>1.000637340355823</v>
+      </c>
+      <c r="I40">
+        <v>0.05830312487006046</v>
+      </c>
+      <c r="J40">
+        <v>0.09030183404684067</v>
+      </c>
+      <c r="K40" t="s">
+        <v>128</v>
+      </c>
+      <c r="L40">
+        <v>24.43600463867188</v>
+      </c>
+      <c r="M40">
+        <v>5.168547630310059</v>
+      </c>
+      <c r="N40" t="s">
+        <v>347</v>
+      </c>
+      <c r="O40" t="s">
+        <v>407</v>
+      </c>
+      <c r="P40" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16">
+      <c r="A41">
+        <v>0</v>
+      </c>
+      <c r="B41" t="s">
+        <v>108</v>
+      </c>
+      <c r="C41">
+        <v>0.1338962232336152</v>
+      </c>
+      <c r="D41">
+        <v>0.07852877676486969</v>
+      </c>
+      <c r="E41">
+        <v>0.9187746644020081</v>
+      </c>
+      <c r="F41">
+        <v>0.00272826012223959</v>
+      </c>
+      <c r="G41">
+        <v>0.002686554100364447</v>
+      </c>
+      <c r="H41">
+        <v>1.001774785801714</v>
+      </c>
+      <c r="I41">
+        <v>0.06841367929647706</v>
+      </c>
+      <c r="J41">
+        <v>0.08547120541334152</v>
+      </c>
+      <c r="K41" t="s">
+        <v>128</v>
+      </c>
+      <c r="L41">
+        <v>52.58731079101562</v>
+      </c>
+      <c r="M41">
+        <v>4.892059803009033</v>
+      </c>
+      <c r="N41" t="s">
+        <v>348</v>
+      </c>
+      <c r="O41" t="s">
+        <v>408</v>
+      </c>
+      <c r="P41" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
+      <c r="A42">
+        <v>0</v>
+      </c>
+      <c r="B42" t="s">
+        <v>109</v>
+      </c>
+      <c r="C42">
+        <v>0.0005565816731699404</v>
+      </c>
+      <c r="D42">
+        <v>-4.240326234139502E-05</v>
+      </c>
+      <c r="E42">
+        <v>0.003042072989046574</v>
+      </c>
+      <c r="F42">
+        <v>0.0009754011407494545</v>
+      </c>
+      <c r="G42">
+        <v>0.0009604969527572393</v>
+      </c>
+      <c r="H42">
+        <v>1.000268780855706</v>
+      </c>
+      <c r="I42">
+        <v>0.04913137434844447</v>
+      </c>
+      <c r="J42">
+        <v>-0.01393893640488386</v>
+      </c>
+      <c r="K42">
+        <v>-0.1296294331550598</v>
+      </c>
+      <c r="L42">
+        <v>0.1741171628236771</v>
+      </c>
+      <c r="M42">
+        <v>-0.7978138327598572</v>
+      </c>
+      <c r="N42" t="s">
+        <v>349</v>
+      </c>
+      <c r="O42" t="s">
+        <v>409</v>
+      </c>
+      <c r="P42" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
+      <c r="A43">
+        <v>0</v>
+      </c>
+      <c r="B43" t="s">
+        <v>110</v>
+      </c>
+      <c r="C43">
+        <v>0.0007307349897627513</v>
+      </c>
+      <c r="D43">
+        <v>1.962829992407933E-05</v>
+      </c>
+      <c r="E43">
+        <v>0.003928276244550943</v>
+      </c>
+      <c r="F43">
+        <v>0.001182764652185142</v>
+      </c>
+      <c r="G43">
+        <v>0.001133658108301461</v>
+      </c>
+      <c r="H43">
+        <v>1.000424823608275</v>
+      </c>
+      <c r="I43">
+        <v>0.04911012100564092</v>
+      </c>
+      <c r="J43">
+        <v>0.004996669944375753</v>
+      </c>
+      <c r="K43">
+        <v>0.0665581226348877</v>
+      </c>
+      <c r="L43">
+        <v>0.2248401939868927</v>
+      </c>
+      <c r="M43">
+        <v>0.2859911620616913</v>
+      </c>
+      <c r="N43" t="s">
+        <v>350</v>
+      </c>
+      <c r="O43" t="s">
+        <v>410</v>
+      </c>
+      <c r="P43" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
+      <c r="A44">
+        <v>0</v>
+      </c>
+      <c r="B44" t="s">
+        <v>111</v>
+      </c>
+      <c r="C44">
+        <v>0.0008997476344007086</v>
+      </c>
+      <c r="D44">
+        <v>8.404677646467462E-05</v>
+      </c>
+      <c r="E44">
+        <v>0.004798931535333395</v>
+      </c>
+      <c r="F44">
+        <v>0.001358966692350805</v>
+      </c>
+      <c r="G44">
+        <v>0.001264797057956457</v>
+      </c>
+      <c r="H44">
+        <v>1.000542504233345</v>
+      </c>
+      <c r="I44">
+        <v>0.04909850490014718</v>
+      </c>
+      <c r="J44">
+        <v>0.01751364395022392</v>
+      </c>
+      <c r="K44">
+        <v>0.3169412612915039</v>
+      </c>
+      <c r="L44">
+        <v>0.2746733427047729</v>
+      </c>
+      <c r="M44">
+        <v>1.002417087554932</v>
+      </c>
+      <c r="N44" t="s">
+        <v>351</v>
+      </c>
+      <c r="O44" t="s">
+        <v>411</v>
+      </c>
+      <c r="P44" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="A45">
+        <v>0</v>
+      </c>
+      <c r="B45" t="s">
+        <v>112</v>
+      </c>
+      <c r="C45">
+        <v>0.001696770773839241</v>
+      </c>
+      <c r="D45">
+        <v>0.0002293770376127213</v>
+      </c>
+      <c r="E45">
+        <v>0.008550711907446384</v>
+      </c>
+      <c r="F45">
+        <v>0.001934646628797054</v>
+      </c>
+      <c r="G45">
+        <v>0.001618069945834577</v>
+      </c>
+      <c r="H45">
+        <v>1.000828614303943</v>
+      </c>
+      <c r="I45">
+        <v>0.04903753492032686</v>
+      </c>
+      <c r="J45">
+        <v>0.02682548947632313</v>
+      </c>
+      <c r="K45">
+        <v>1.119738817214966</v>
+      </c>
+      <c r="L45">
+        <v>0.4894115626811981</v>
+      </c>
+      <c r="M45">
+        <v>1.535393118858337</v>
+      </c>
+      <c r="N45" t="s">
+        <v>352</v>
+      </c>
+      <c r="O45" t="s">
+        <v>412</v>
+      </c>
+      <c r="P45" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="A46">
+        <v>0</v>
+      </c>
+      <c r="B46" t="s">
+        <v>113</v>
+      </c>
+      <c r="C46">
+        <v>0.003185391873201408</v>
+      </c>
+      <c r="D46">
+        <v>0.0001630143087822944</v>
+      </c>
+      <c r="E46">
+        <v>0.01889027841389179</v>
+      </c>
+      <c r="F46">
+        <v>0.002540185349062085</v>
+      </c>
+      <c r="G46">
+        <v>0.001984454225748777</v>
+      </c>
+      <c r="H46">
+        <v>1.000919882831261</v>
+      </c>
+      <c r="I46">
+        <v>0.04924631543942031</v>
+      </c>
+      <c r="J46">
+        <v>0.008629534393548965</v>
+      </c>
+      <c r="K46">
+        <v>0.7054184675216675</v>
+      </c>
+      <c r="L46">
+        <v>1.081210613250732</v>
+      </c>
+      <c r="M46">
+        <v>0.4939230680465698</v>
+      </c>
+      <c r="N46" t="s">
+        <v>353</v>
+      </c>
+      <c r="O46" t="s">
+        <v>413</v>
+      </c>
+      <c r="P46" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="A47">
+        <v>0</v>
+      </c>
+      <c r="B47" t="s">
+        <v>114</v>
+      </c>
+      <c r="C47">
+        <v>0.006051607627709319</v>
+      </c>
+      <c r="D47">
+        <v>-3.017918606929015E-05</v>
+      </c>
+      <c r="E47">
+        <v>0.034516841173172</v>
+      </c>
+      <c r="F47">
+        <v>0.002931078895926476</v>
+      </c>
+      <c r="G47">
+        <v>0.002240018686279655</v>
+      </c>
+      <c r="H47">
+        <v>1.000798032324878</v>
+      </c>
+      <c r="I47">
+        <v>0.04935426857263497</v>
+      </c>
+      <c r="J47">
+        <v>-0.0008743322105146945</v>
+      </c>
+      <c r="K47">
+        <v>-0.09408110380172729</v>
+      </c>
+      <c r="L47">
+        <v>1.975618004798889</v>
+      </c>
+      <c r="M47">
+        <v>-0.05004358664155006</v>
+      </c>
+      <c r="N47" t="s">
+        <v>354</v>
+      </c>
+      <c r="O47" t="s">
+        <v>414</v>
+      </c>
+      <c r="P47" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16">
+      <c r="A48">
+        <v>0</v>
+      </c>
+      <c r="B48" t="s">
+        <v>115</v>
+      </c>
+      <c r="C48">
+        <v>0.01431973734368431</v>
+      </c>
+      <c r="D48">
+        <v>-0.001158385537564754</v>
+      </c>
+      <c r="E48">
+        <v>0.08770694583654404</v>
+      </c>
+      <c r="F48">
+        <v>0.003046385711058974</v>
+      </c>
+      <c r="G48">
+        <v>0.002316630678251386</v>
+      </c>
+      <c r="H48">
+        <v>1.000567710537116</v>
+      </c>
+      <c r="I48">
+        <v>0.0508882436085288</v>
+      </c>
+      <c r="J48">
+        <v>-0.01320745516568422</v>
+      </c>
+      <c r="K48">
+        <v>-0.9775614738464355</v>
+      </c>
+      <c r="L48">
+        <v>5.020025730133057</v>
+      </c>
+      <c r="M48">
+        <v>-0.7559465169906616</v>
+      </c>
+      <c r="N48" t="s">
+        <v>355</v>
+      </c>
+      <c r="O48" t="s">
+        <v>415</v>
+      </c>
+      <c r="P48" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16">
+      <c r="A49">
+        <v>0</v>
+      </c>
+      <c r="B49" t="s">
+        <v>116</v>
+      </c>
+      <c r="C49">
+        <v>0.02841782117307276</v>
+      </c>
+      <c r="D49">
+        <v>-0.003153125056996942</v>
+      </c>
+      <c r="E49">
+        <v>0.1748248636722565</v>
+      </c>
+      <c r="F49">
+        <v>0.00297164567746222</v>
+      </c>
+      <c r="G49">
+        <v>0.002368442481383681</v>
+      </c>
+      <c r="H49">
+        <v>1.000295369615515</v>
+      </c>
+      <c r="I49">
+        <v>0.05251602469116587</v>
+      </c>
+      <c r="J49">
+        <v>-0.01803590729832649</v>
+      </c>
+      <c r="K49">
+        <v>-0.9999678730964661</v>
+      </c>
+      <c r="L49">
+        <v>10.00633716583252</v>
+      </c>
+      <c r="M49">
+        <v>-1.032309532165527</v>
+      </c>
+      <c r="N49" t="s">
+        <v>356</v>
+      </c>
+      <c r="O49" t="s">
+        <v>416</v>
+      </c>
+      <c r="P49" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16">
+      <c r="A50">
+        <v>0</v>
+      </c>
+      <c r="B50" t="s">
+        <v>117</v>
+      </c>
+      <c r="C50">
+        <v>0.07105119441041917</v>
+      </c>
+      <c r="D50">
+        <v>-0.009231267496943474</v>
+      </c>
+      <c r="E50">
+        <v>0.4334238767623901</v>
+      </c>
+      <c r="F50">
+        <v>0.002747943159192801</v>
+      </c>
+      <c r="G50">
+        <v>0.002498820889741182</v>
+      </c>
+      <c r="H50">
+        <v>1.000560840967818</v>
+      </c>
+      <c r="I50">
+        <v>0.05834495019415879</v>
+      </c>
+      <c r="J50">
+        <v>-0.02129847556352615</v>
+      </c>
+      <c r="K50">
+        <v>-1</v>
+      </c>
+      <c r="L50">
+        <v>24.80760192871094</v>
+      </c>
+      <c r="M50">
+        <v>-1.219047069549561</v>
+      </c>
+      <c r="N50" t="s">
+        <v>357</v>
+      </c>
+      <c r="O50" t="s">
+        <v>417</v>
+      </c>
+      <c r="P50" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16">
+      <c r="A51">
+        <v>0</v>
+      </c>
+      <c r="B51" t="s">
+        <v>118</v>
+      </c>
+      <c r="C51">
+        <v>0.1281847725523834</v>
+      </c>
+      <c r="D51">
+        <v>-0.01932087354362011</v>
+      </c>
+      <c r="E51">
+        <v>0.8460913300514221</v>
+      </c>
+      <c r="F51">
+        <v>0.002729389118030667</v>
+      </c>
+      <c r="G51">
+        <v>0.002686996711418033</v>
+      </c>
+      <c r="H51">
+        <v>1.001499388004896</v>
+      </c>
+      <c r="I51">
+        <v>0.0686493809617631</v>
+      </c>
+      <c r="J51">
+        <v>-0.02283544652163982</v>
+      </c>
+      <c r="K51">
+        <v>-1</v>
+      </c>
+      <c r="L51">
+        <v>48.42718124389648</v>
+      </c>
+      <c r="M51">
+        <v>-1.307017683982849</v>
+      </c>
+      <c r="N51" t="s">
+        <v>358</v>
+      </c>
+      <c r="O51" t="s">
+        <v>418</v>
+      </c>
+      <c r="P51" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16">
+      <c r="A52">
+        <v>0</v>
+      </c>
+      <c r="B52" t="s">
+        <v>119</v>
+      </c>
+      <c r="C52">
+        <v>0.000219441859880586</v>
+      </c>
+      <c r="D52">
+        <v>0.0003069927042815834</v>
+      </c>
+      <c r="E52">
+        <v>0.0007134258630685508</v>
+      </c>
+      <c r="F52">
+        <v>0.001112977159209549</v>
+      </c>
+      <c r="G52">
+        <v>0.00107566243968904</v>
+      </c>
+      <c r="H52">
+        <v>0.9997034931007633</v>
+      </c>
+      <c r="I52">
+        <v>0.04967771735157368</v>
+      </c>
+      <c r="J52">
+        <v>0.4303077757358551</v>
+      </c>
+      <c r="K52">
+        <v>1.733162879943848</v>
+      </c>
+      <c r="L52">
+        <v>0.04083389416337013</v>
+      </c>
+      <c r="M52">
+        <v>24.62924766540527</v>
+      </c>
+      <c r="N52" t="s">
+        <v>359</v>
+      </c>
+      <c r="O52" t="s">
+        <v>419</v>
+      </c>
+      <c r="P52" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16">
+      <c r="A53">
+        <v>0</v>
+      </c>
+      <c r="B53" t="s">
+        <v>120</v>
+      </c>
+      <c r="C53">
+        <v>0.0002678028592947504</v>
+      </c>
+      <c r="D53">
+        <v>0.0003710400487761945</v>
+      </c>
+      <c r="E53">
+        <v>0.0007732594385743141</v>
+      </c>
+      <c r="F53">
+        <v>0.001301366370171309</v>
+      </c>
+      <c r="G53">
+        <v>0.00123192451428622</v>
+      </c>
+      <c r="H53">
+        <v>0.999967380430388</v>
+      </c>
+      <c r="I53">
+        <v>0.04951288637829883</v>
+      </c>
+      <c r="J53">
+        <v>0.479839026927948</v>
+      </c>
+      <c r="K53">
+        <v>2.371956825256348</v>
+      </c>
+      <c r="L53">
+        <v>0.04425854980945587</v>
+      </c>
+      <c r="M53">
+        <v>27.46423530578613</v>
+      </c>
+      <c r="N53" t="s">
+        <v>360</v>
+      </c>
+      <c r="O53" t="s">
+        <v>420</v>
+      </c>
+      <c r="P53" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16">
+      <c r="A54">
+        <v>0</v>
+      </c>
+      <c r="B54" t="s">
+        <v>121</v>
+      </c>
+      <c r="C54">
+        <v>0.0003077872572781045</v>
+      </c>
+      <c r="D54">
+        <v>0.0004257910186424851</v>
+      </c>
+      <c r="E54">
+        <v>0.0008173980168066919</v>
+      </c>
+      <c r="F54">
+        <v>0.001468802103772759</v>
+      </c>
+      <c r="G54">
+        <v>0.001335832639597356</v>
+      </c>
+      <c r="H54">
+        <v>1.000176527382089</v>
+      </c>
+      <c r="I54">
+        <v>0.04942062784587629</v>
+      </c>
+      <c r="J54">
+        <v>0.5209102630615234</v>
+      </c>
+      <c r="K54">
+        <v>3.033663272857666</v>
+      </c>
+      <c r="L54">
+        <v>0.04678488150238991</v>
+      </c>
+      <c r="M54">
+        <v>29.81500244140625</v>
+      </c>
+      <c r="N54" t="s">
+        <v>361</v>
+      </c>
+      <c r="O54" t="s">
+        <v>421</v>
+      </c>
+      <c r="P54" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16">
+      <c r="A55">
+        <v>0</v>
+      </c>
+      <c r="B55" t="s">
+        <v>61</v>
+      </c>
+      <c r="C55">
+        <v>0.0004451608287899583</v>
+      </c>
+      <c r="D55">
+        <v>0.0006044073961675167</v>
+      </c>
+      <c r="E55">
+        <v>0.0009689102880656719</v>
+      </c>
+      <c r="F55">
+        <v>0.002093791961669922</v>
+      </c>
+      <c r="G55">
+        <v>0.001728823641315103</v>
+      </c>
+      <c r="H55">
+        <v>1.000626713617608</v>
+      </c>
+      <c r="I55">
+        <v>0.0492428876075909</v>
+      </c>
+      <c r="J55">
+        <v>0.6238011717796326</v>
+      </c>
+      <c r="K55">
+        <v>6.238305568695068</v>
+      </c>
+      <c r="L55">
+        <v>0.05545688793063164</v>
+      </c>
+      <c r="M55">
+        <v>35.7041015625</v>
+      </c>
+      <c r="N55" t="s">
+        <v>362</v>
+      </c>
+      <c r="O55" t="s">
+        <v>422</v>
+      </c>
+      <c r="P55" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16">
+      <c r="A56">
+        <v>0</v>
+      </c>
+      <c r="B56" t="s">
+        <v>122</v>
+      </c>
+      <c r="C56">
+        <v>0.0005972541991491902</v>
+      </c>
+      <c r="D56">
+        <v>0.0007960451184771955</v>
+      </c>
+      <c r="E56">
+        <v>0.001196270110085607</v>
+      </c>
+      <c r="F56">
+        <v>0.002695040544494987</v>
+      </c>
+      <c r="G56">
+        <v>0.002090375404804945</v>
+      </c>
+      <c r="H56">
+        <v>1.00065200444487</v>
+      </c>
+      <c r="I56">
+        <v>0.04957056878525867</v>
+      </c>
+      <c r="J56">
+        <v>0.6654393076896667</v>
+      </c>
+      <c r="K56">
+        <v>12.55722141265869</v>
+      </c>
+      <c r="L56">
+        <v>0.06847013533115387</v>
+      </c>
+      <c r="M56">
+        <v>38.08731842041016</v>
+      </c>
+      <c r="N56" t="s">
+        <v>363</v>
+      </c>
+      <c r="O56" t="s">
+        <v>423</v>
+      </c>
+      <c r="P56" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16">
+      <c r="A57">
+        <v>0</v>
+      </c>
+      <c r="B57" t="s">
+        <v>123</v>
+      </c>
+      <c r="C57">
+        <v>0.0007662018442007429</v>
+      </c>
+      <c r="D57">
+        <v>0.0009704716503620148</v>
+      </c>
+      <c r="E57">
+        <v>0.001555738272145391</v>
+      </c>
+      <c r="F57">
+        <v>0.003002886427566409</v>
+      </c>
+      <c r="G57">
+        <v>0.002264394424855709</v>
+      </c>
+      <c r="H57">
+        <v>1.00066600652055</v>
+      </c>
+      <c r="I57">
+        <v>0.04957286933930903</v>
+      </c>
+      <c r="J57">
+        <v>0.6238013505935669</v>
+      </c>
+      <c r="K57">
+        <v>22.99294853210449</v>
+      </c>
+      <c r="L57">
+        <v>0.08904477953910828</v>
+      </c>
+      <c r="M57">
+        <v>35.7041130065918</v>
+      </c>
+      <c r="N57" t="s">
+        <v>364</v>
+      </c>
+      <c r="O57" t="s">
+        <v>424</v>
+      </c>
+      <c r="P57" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16">
+      <c r="A58">
+        <v>0</v>
+      </c>
+      <c r="B58" t="s">
+        <v>124</v>
+      </c>
+      <c r="C58">
+        <v>0.001031652541588571</v>
+      </c>
+      <c r="D58">
+        <v>0.001207843772135675</v>
+      </c>
+      <c r="E58">
+        <v>0.002395401941612363</v>
+      </c>
+      <c r="F58">
+        <v>0.003055923618376255</v>
+      </c>
+      <c r="G58">
+        <v>0.002438514027744532</v>
+      </c>
+      <c r="H58">
+        <v>1.000279211194718</v>
+      </c>
+      <c r="I58">
+        <v>0.05150619110461239</v>
+      </c>
+      <c r="J58">
+        <v>0.504234254360199</v>
+      </c>
+      <c r="K58">
+        <v>51.16744232177734</v>
+      </c>
+      <c r="L58">
+        <v>0.1371040642261505</v>
+      </c>
+      <c r="M58">
+        <v>28.86052894592285</v>
+      </c>
+      <c r="N58" t="s">
+        <v>365</v>
+      </c>
+      <c r="O58" t="s">
+        <v>425</v>
+      </c>
+      <c r="P58" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16">
+      <c r="A59">
+        <v>0</v>
+      </c>
+      <c r="B59" t="s">
+        <v>125</v>
+      </c>
+      <c r="C59">
+        <v>0.001267993073281982</v>
+      </c>
+      <c r="D59">
+        <v>0.00139348313678056</v>
+      </c>
+      <c r="E59">
+        <v>0.003415815997868776</v>
+      </c>
+      <c r="F59">
+        <v>0.002929516602307558</v>
+      </c>
+      <c r="G59">
+        <v>0.002443677047267556</v>
+      </c>
+      <c r="H59">
+        <v>0.9997175464661008</v>
+      </c>
+      <c r="I59">
+        <v>0.05378422186936326</v>
+      </c>
+      <c r="J59">
+        <v>0.4079502820968628</v>
+      </c>
+      <c r="K59">
+        <v>94.74834442138672</v>
+      </c>
+      <c r="L59">
+        <v>0.1955088376998901</v>
+      </c>
+      <c r="M59">
+        <v>23.34958648681641</v>
+      </c>
+      <c r="N59" t="s">
+        <v>366</v>
+      </c>
+      <c r="O59" t="s">
+        <v>426</v>
+      </c>
+      <c r="P59" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16">
+      <c r="A60">
+        <v>0</v>
+      </c>
+      <c r="B60" t="s">
+        <v>126</v>
+      </c>
+      <c r="C60">
+        <v>0.001601114152621646</v>
+      </c>
+      <c r="D60">
+        <v>0.001729910611175001</v>
+      </c>
+      <c r="E60">
+        <v>0.005662444047629833</v>
+      </c>
+      <c r="F60">
+        <v>0.002725621685385704</v>
+      </c>
+      <c r="G60">
+        <v>0.002531369449570775</v>
+      </c>
+      <c r="H60">
+        <v>1.000059344979786</v>
+      </c>
+      <c r="I60">
+        <v>0.05978789582441367</v>
+      </c>
+      <c r="J60">
+        <v>0.3055059909820557</v>
+      </c>
+      <c r="K60">
+        <v>286.858642578125</v>
+      </c>
+      <c r="L60">
+        <v>0.3240976333618164</v>
+      </c>
+      <c r="M60">
+        <v>17.48604774475098</v>
+      </c>
+      <c r="N60" t="s">
+        <v>367</v>
+      </c>
+      <c r="O60" t="s">
+        <v>427</v>
+      </c>
+      <c r="P60" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16">
+      <c r="A61">
+        <v>0</v>
+      </c>
+      <c r="B61" t="s">
+        <v>127</v>
+      </c>
+      <c r="C61">
+        <v>0.00183469786443416</v>
+      </c>
+      <c r="D61">
+        <v>0.001976096304133534</v>
+      </c>
+      <c r="E61">
+        <v>0.00762895355001092</v>
+      </c>
+      <c r="F61">
+        <v>0.002708856714889407</v>
+      </c>
+      <c r="G61">
+        <v>0.002740185242146254</v>
+      </c>
+      <c r="H61">
+        <v>1.001468788249694</v>
+      </c>
+      <c r="I61">
+        <v>0.0687002316266745</v>
+      </c>
+      <c r="J61">
+        <v>0.2590258717536926</v>
+      </c>
+      <c r="K61">
+        <v>642.821533203125</v>
+      </c>
+      <c r="L61">
+        <v>0.4366534650325775</v>
+      </c>
+      <c r="M61">
+        <v>14.82569599151611</v>
+      </c>
+      <c r="N61" t="s">
+        <v>368</v>
+      </c>
+      <c r="O61" t="s">
+        <v>428</v>
+      </c>
+      <c r="P61" t="s">
+        <v>488</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="2:2">
+      <c r="B1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="2:2">
+      <c r="B1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="2:2">
+      <c r="B1" t="s">
+        <v>489</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/gbrt_standard/performance.xlsx
+++ b/scripts/gbrt_standard/performance.xlsx
@@ -9110,12 +9110,6556 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1"/>
+  <dimension ref="A1:B819"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:2">
+    <row r="1" spans="1:2">
       <c r="B1" t="s">
         <v>489</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.001277992618270218</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>-2.508195029804483E-05</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>0.001122941612266004</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>-0.0001572353939991444</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>0.0002016595099121332</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>0.0003994885482825339</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>0.0006258646608330309</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>0.0003112081612925977</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>0.0007856199517846107</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>0.0008170852670446038</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>0.0002970512432511896</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>0.001363944378681481</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>0.002378974808380008</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <v>0.0003604341472964734</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <v>0.0006408154731616378</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17">
+        <v>6.703287363052368E-05</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>0.0003074218984693289</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19">
+        <v>0.001610864070244133</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20">
+        <v>0.0003458922728896141</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21">
+        <v>0.0007306760526262224</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22">
+        <v>0.0001128875446738675</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23">
+        <v>0.001539335935376585</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24">
+        <v>0.001757921534590423</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25">
+        <v>0.0006271600723266602</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26">
+        <v>0.00130836886819452</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27">
+        <v>0.0008326756069436669</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28">
+        <v>-0.0001305045152548701</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29">
+        <v>2.238831075374037E-05</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30">
+        <v>-0.0008049789466895163</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="B31">
+        <v>0.0004848913522437215</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="B32">
+        <v>0.0005903872079215944</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33">
+        <v>5.105936361360364E-05</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="B34">
+        <v>-0.0003069696831516922</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="B35">
+        <v>0.0003021374868694693</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>34</v>
+      </c>
+      <c r="B36">
+        <v>0.0009108203812502325</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>35</v>
+      </c>
+      <c r="B37">
+        <v>-2.065838089038152E-05</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="B38">
+        <v>0.001126233022660017</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="B39">
+        <v>-0.0008082808926701546</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="B40">
+        <v>0.001877725357189775</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="B41">
+        <v>0.0006441535078920424</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="B42">
+        <v>-0.0001130844102590345</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="B43">
+        <v>0.0009763684938661754</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="B44">
+        <v>0.000535506522282958</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="B45">
+        <v>-0.0003990635159425437</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="B46">
+        <v>0.001878294511698186</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="B47">
+        <v>-4.047237234772183E-05</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="B48">
+        <v>0.0001589877065271139</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="B49">
+        <v>0.0003821729333139956</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="B50">
+        <v>0.0001657110260566697</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51">
+        <v>49</v>
+      </c>
+      <c r="B51">
+        <v>0.0009845488239079714</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="B52">
+        <v>-0.00202628574334085</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53">
+        <v>51</v>
+      </c>
+      <c r="B53">
+        <v>-0.0001223158615175635</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54">
+        <v>52</v>
+      </c>
+      <c r="B54">
+        <v>-1.077630804502405E-05</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55">
+        <v>53</v>
+      </c>
+      <c r="B55">
+        <v>0.000143185316119343</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56">
+        <v>54</v>
+      </c>
+      <c r="B56">
+        <v>0.0005480110994540155</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57">
+        <v>55</v>
+      </c>
+      <c r="B57">
+        <v>0.0006718853255733848</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58">
+        <v>56</v>
+      </c>
+      <c r="B58">
+        <v>0.0005077302921563387</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59">
+        <v>57</v>
+      </c>
+      <c r="B59">
+        <v>0.0003469210059847683</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60">
+        <v>58</v>
+      </c>
+      <c r="B60">
+        <v>0.0009557204321026802</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61">
+        <v>59</v>
+      </c>
+      <c r="B61">
+        <v>0.0002820696390699595</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62">
+        <v>60</v>
+      </c>
+      <c r="B62">
+        <v>0.0004462776996660978</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63">
+        <v>61</v>
+      </c>
+      <c r="B63">
+        <v>0.0005978328408673406</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64">
+        <v>62</v>
+      </c>
+      <c r="B64">
+        <v>0.0007267958717420697</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65">
+        <v>63</v>
+      </c>
+      <c r="B65">
+        <v>0.002439564093947411</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66">
+        <v>64</v>
+      </c>
+      <c r="B66">
+        <v>0.0004414577852003276</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67">
+        <v>65</v>
+      </c>
+      <c r="B67">
+        <v>0.0002232550759799778</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68">
+        <v>66</v>
+      </c>
+      <c r="B68">
+        <v>0.000529139069840312</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69">
+        <v>67</v>
+      </c>
+      <c r="B69">
+        <v>0.0005017442163079977</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70">
+        <v>68</v>
+      </c>
+      <c r="B70">
+        <v>0.001558044692501426</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71">
+        <v>69</v>
+      </c>
+      <c r="B71">
+        <v>0.000851235818117857</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72">
+        <v>70</v>
+      </c>
+      <c r="B72">
+        <v>0.0006120571633800864</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73">
+        <v>71</v>
+      </c>
+      <c r="B73">
+        <v>-0.001346475910395384</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74">
+        <v>72</v>
+      </c>
+      <c r="B74">
+        <v>0.0009869850473478436</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75">
+        <v>73</v>
+      </c>
+      <c r="B75">
+        <v>0.001290445681661367</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76">
+        <v>74</v>
+      </c>
+      <c r="B76">
+        <v>0.002130476525053382</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77">
+        <v>75</v>
+      </c>
+      <c r="B77">
+        <v>-0.0008911112090572715</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78">
+        <v>76</v>
+      </c>
+      <c r="B78">
+        <v>0.003232400398701429</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79">
+        <v>77</v>
+      </c>
+      <c r="B79">
+        <v>0.0008299302426166832</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80">
+        <v>78</v>
+      </c>
+      <c r="B80">
+        <v>0.0001332364918198436</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81">
+        <v>79</v>
+      </c>
+      <c r="B81">
+        <v>-1.41805849125376E-05</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82">
+        <v>80</v>
+      </c>
+      <c r="B82">
+        <v>1.201258055516519E-05</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83">
+        <v>81</v>
+      </c>
+      <c r="B83">
+        <v>0.0001610133913345635</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84">
+        <v>82</v>
+      </c>
+      <c r="B84">
+        <v>0.0006196546019054949</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85">
+        <v>83</v>
+      </c>
+      <c r="B85">
+        <v>0.000314691656967625</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86">
+        <v>84</v>
+      </c>
+      <c r="B86">
+        <v>0.000295495119644329</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87">
+        <v>85</v>
+      </c>
+      <c r="B87">
+        <v>0.000132459303131327</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88">
+        <v>86</v>
+      </c>
+      <c r="B88">
+        <v>0.00105350324884057</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89">
+        <v>87</v>
+      </c>
+      <c r="B89">
+        <v>5.82323855269351E-06</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90">
+        <v>88</v>
+      </c>
+      <c r="B90">
+        <v>0.0009862283477559686</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91">
+        <v>89</v>
+      </c>
+      <c r="B91">
+        <v>0.0005326923565007746</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92">
+        <v>90</v>
+      </c>
+      <c r="B92">
+        <v>0.0005172613891772926</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93">
+        <v>91</v>
+      </c>
+      <c r="B93">
+        <v>0.001352335559204221</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94">
+        <v>92</v>
+      </c>
+      <c r="B94">
+        <v>0.0006564026698470116</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95">
+        <v>93</v>
+      </c>
+      <c r="B95">
+        <v>0.00186613982077688</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96">
+        <v>94</v>
+      </c>
+      <c r="B96">
+        <v>4.956755219609477E-05</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97">
+        <v>95</v>
+      </c>
+      <c r="B97">
+        <v>0.0006960232276469469</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98">
+        <v>96</v>
+      </c>
+      <c r="B98">
+        <v>0.0004157517105340958</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99">
+        <v>97</v>
+      </c>
+      <c r="B99">
+        <v>0.0004509274731390178</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100">
+        <v>98</v>
+      </c>
+      <c r="B100">
+        <v>0.0001995833008550107</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101">
+        <v>99</v>
+      </c>
+      <c r="B101">
+        <v>4.708868073066697E-05</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102">
+        <v>100</v>
+      </c>
+      <c r="B102">
+        <v>0.000388884189305827</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103">
+        <v>101</v>
+      </c>
+      <c r="B103">
+        <v>-0.0002830422599799931</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104">
+        <v>102</v>
+      </c>
+      <c r="B104">
+        <v>0.002543971175327897</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105">
+        <v>103</v>
+      </c>
+      <c r="B105">
+        <v>0.000358127465005964</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106">
+        <v>104</v>
+      </c>
+      <c r="B106">
+        <v>0.0003574415750335902</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107">
+        <v>105</v>
+      </c>
+      <c r="B107">
+        <v>0.001511647133156657</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108">
+        <v>106</v>
+      </c>
+      <c r="B108">
+        <v>0.00159357360098511</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109">
+        <v>107</v>
+      </c>
+      <c r="B109">
+        <v>0.0003502979525364935</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110">
+        <v>108</v>
+      </c>
+      <c r="B110">
+        <v>0.0004773634427692741</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111">
+        <v>109</v>
+      </c>
+      <c r="B111">
+        <v>0.001758149708621204</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112">
+        <v>110</v>
+      </c>
+      <c r="B112">
+        <v>0.0004761732998304069</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113">
+        <v>111</v>
+      </c>
+      <c r="B113">
+        <v>4.442136196303181E-05</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114">
+        <v>112</v>
+      </c>
+      <c r="B114">
+        <v>0.001038405112922192</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115">
+        <v>113</v>
+      </c>
+      <c r="B115">
+        <v>-0.0001483041851315647</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116">
+        <v>114</v>
+      </c>
+      <c r="B116">
+        <v>0.0003327181620988995</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117">
+        <v>115</v>
+      </c>
+      <c r="B117">
+        <v>-0.0008423447143286467</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118">
+        <v>116</v>
+      </c>
+      <c r="B118">
+        <v>-9.014175884658471E-05</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119">
+        <v>117</v>
+      </c>
+      <c r="B119">
+        <v>3.788301910390146E-05</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120">
+        <v>118</v>
+      </c>
+      <c r="B120">
+        <v>0.0003605876700021327</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121">
+        <v>119</v>
+      </c>
+      <c r="B121">
+        <v>4.373665433377028E-05</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122">
+        <v>120</v>
+      </c>
+      <c r="B122">
+        <v>0.001146662165410817</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123">
+        <v>121</v>
+      </c>
+      <c r="B123">
+        <v>0.0004352052637841552</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124">
+        <v>122</v>
+      </c>
+      <c r="B124">
+        <v>0.0007138209184631705</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125">
+        <v>123</v>
+      </c>
+      <c r="B125">
+        <v>0.0003075695713050663</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126">
+        <v>124</v>
+      </c>
+      <c r="B126">
+        <v>0.0005107351462356746</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127">
+        <v>125</v>
+      </c>
+      <c r="B127">
+        <v>0.00108224106952548</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128">
+        <v>126</v>
+      </c>
+      <c r="B128">
+        <v>0.0009157193708233535</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129">
+        <v>127</v>
+      </c>
+      <c r="B129">
+        <v>0.0009694906766526401</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130">
+        <v>128</v>
+      </c>
+      <c r="B130">
+        <v>-1.918927773658652E-05</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131">
+        <v>129</v>
+      </c>
+      <c r="B131">
+        <v>0.001832308014854789</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132">
+        <v>130</v>
+      </c>
+      <c r="B132">
+        <v>0.0002599950239527971</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133">
+        <v>131</v>
+      </c>
+      <c r="B133">
+        <v>4.006521703558974E-05</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134">
+        <v>132</v>
+      </c>
+      <c r="B134">
+        <v>-0.000100675672001671</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135">
+        <v>133</v>
+      </c>
+      <c r="B135">
+        <v>0.0003844242601189762</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136">
+        <v>134</v>
+      </c>
+      <c r="B136">
+        <v>0.0005062180571258068</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137">
+        <v>135</v>
+      </c>
+      <c r="B137">
+        <v>0.001483343192376196</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138">
+        <v>136</v>
+      </c>
+      <c r="B138">
+        <v>0.0002778566849883646</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139">
+        <v>137</v>
+      </c>
+      <c r="B139">
+        <v>4.287045885575935E-05</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140">
+        <v>138</v>
+      </c>
+      <c r="B140">
+        <v>0.001118277083151042</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141">
+        <v>139</v>
+      </c>
+      <c r="B141">
+        <v>0.0001275187969440594</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142">
+        <v>140</v>
+      </c>
+      <c r="B142">
+        <v>-0.0007591629982925951</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143">
+        <v>141</v>
+      </c>
+      <c r="B143">
+        <v>0.005590952467173338</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144">
+        <v>142</v>
+      </c>
+      <c r="B144">
+        <v>0.001386024756357074</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145">
+        <v>143</v>
+      </c>
+      <c r="B145">
+        <v>0.001169553492218256</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146">
+        <v>144</v>
+      </c>
+      <c r="B146">
+        <v>0.001162467640824616</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147">
+        <v>145</v>
+      </c>
+      <c r="B147">
+        <v>0.0002488931349944323</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148">
+        <v>146</v>
+      </c>
+      <c r="B148">
+        <v>0.001631995663046837</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149">
+        <v>147</v>
+      </c>
+      <c r="B149">
+        <v>0.000880714796949178</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150">
+        <v>148</v>
+      </c>
+      <c r="B150">
+        <v>0.001318695372901857</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151">
+        <v>149</v>
+      </c>
+      <c r="B151">
+        <v>0.0003873866808135062</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152">
+        <v>150</v>
+      </c>
+      <c r="B152">
+        <v>0.0005437455838546157</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153">
+        <v>151</v>
+      </c>
+      <c r="B153">
+        <v>0.001244842424057424</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154">
+        <v>152</v>
+      </c>
+      <c r="B154">
+        <v>0.0003082802577409893</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155">
+        <v>153</v>
+      </c>
+      <c r="B155">
+        <v>-0.0002143389428965747</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156">
+        <v>154</v>
+      </c>
+      <c r="B156">
+        <v>0.004083610605448484</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157">
+        <v>155</v>
+      </c>
+      <c r="B157">
+        <v>0.0009986618533730507</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158">
+        <v>156</v>
+      </c>
+      <c r="B158">
+        <v>0.0002347858244320378</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159">
+        <v>157</v>
+      </c>
+      <c r="B159">
+        <v>0.001498219673521817</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160">
+        <v>158</v>
+      </c>
+      <c r="B160">
+        <v>0.0008385743130929768</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161">
+        <v>159</v>
+      </c>
+      <c r="B161">
+        <v>0.0005863911937922239</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162">
+        <v>160</v>
+      </c>
+      <c r="B162">
+        <v>0.0004532966995611787</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163">
+        <v>161</v>
+      </c>
+      <c r="B163">
+        <v>0.0008974438533186913</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164">
+        <v>162</v>
+      </c>
+      <c r="B164">
+        <v>0.0008954884833656251</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165">
+        <v>163</v>
+      </c>
+      <c r="B165">
+        <v>0.001134091755375266</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166">
+        <v>164</v>
+      </c>
+      <c r="B166">
+        <v>0.0006234824541024864</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167">
+        <v>165</v>
+      </c>
+      <c r="B167">
+        <v>0.001092330901883543</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168">
+        <v>166</v>
+      </c>
+      <c r="B168">
+        <v>0.0001056700639310293</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169">
+        <v>167</v>
+      </c>
+      <c r="B169">
+        <v>0.002616107231006026</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170">
+        <v>168</v>
+      </c>
+      <c r="B170">
+        <v>0.0009691611048765481</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171">
+        <v>169</v>
+      </c>
+      <c r="B171">
+        <v>1.440468713553855E-05</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172">
+        <v>170</v>
+      </c>
+      <c r="B172">
+        <v>3.46403758157976E-05</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173">
+        <v>171</v>
+      </c>
+      <c r="B173">
+        <v>0.0006284313858486712</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174">
+        <v>172</v>
+      </c>
+      <c r="B174">
+        <v>0.0001158789091277868</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175">
+        <v>173</v>
+      </c>
+      <c r="B175">
+        <v>-4.399782483233139E-05</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176">
+        <v>174</v>
+      </c>
+      <c r="B176">
+        <v>0.0005935442168265581</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177">
+        <v>175</v>
+      </c>
+      <c r="B177">
+        <v>0.0008592708618380129</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178">
+        <v>176</v>
+      </c>
+      <c r="B178">
+        <v>0.0004914276651106775</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179">
+        <v>177</v>
+      </c>
+      <c r="B179">
+        <v>0.0005019609234295785</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180">
+        <v>178</v>
+      </c>
+      <c r="B180">
+        <v>0.0006393311778083444</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181">
+        <v>179</v>
+      </c>
+      <c r="B181">
+        <v>0.0007146518910303712</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182">
+        <v>180</v>
+      </c>
+      <c r="B182">
+        <v>-0.00230642594397068</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183">
+        <v>181</v>
+      </c>
+      <c r="B183">
+        <v>-0.0004543898685369641</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184">
+        <v>182</v>
+      </c>
+      <c r="B184">
+        <v>-3.895430199918337E-05</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185">
+        <v>183</v>
+      </c>
+      <c r="B185">
+        <v>0.0006770092877559364</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186">
+        <v>184</v>
+      </c>
+      <c r="B186">
+        <v>0.0005719457985833287</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187">
+        <v>185</v>
+      </c>
+      <c r="B187">
+        <v>0.0003855047689285129</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188">
+        <v>186</v>
+      </c>
+      <c r="B188">
+        <v>0.001358954003080726</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189">
+        <v>187</v>
+      </c>
+      <c r="B189">
+        <v>0.00146674842108041</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190">
+        <v>188</v>
+      </c>
+      <c r="B190">
+        <v>0.0006392389768734574</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191">
+        <v>189</v>
+      </c>
+      <c r="B191">
+        <v>0.0005417967331595719</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192">
+        <v>190</v>
+      </c>
+      <c r="B192">
+        <v>0.001327999751083553</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193">
+        <v>191</v>
+      </c>
+      <c r="B193">
+        <v>0.0004021570784971118</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2">
+      <c r="A194">
+        <v>192</v>
+      </c>
+      <c r="B194">
+        <v>-0.0009517223224975169</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2">
+      <c r="A195">
+        <v>193</v>
+      </c>
+      <c r="B195">
+        <v>-0.003622724208980799</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
+      <c r="A196">
+        <v>194</v>
+      </c>
+      <c r="B196">
+        <v>0.00221006409265101</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2">
+      <c r="A197">
+        <v>195</v>
+      </c>
+      <c r="B197">
+        <v>0.000407328741857782</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198">
+        <v>196</v>
+      </c>
+      <c r="B198">
+        <v>0.0008306113304570317</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
+      <c r="A199">
+        <v>197</v>
+      </c>
+      <c r="B199">
+        <v>0.0005074578803032637</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2">
+      <c r="A200">
+        <v>198</v>
+      </c>
+      <c r="B200">
+        <v>7.108999125193805E-05</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201">
+        <v>199</v>
+      </c>
+      <c r="B201">
+        <v>0.0008330538985319436</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2">
+      <c r="A202">
+        <v>200</v>
+      </c>
+      <c r="B202">
+        <v>0.0002630340459290892</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2">
+      <c r="A203">
+        <v>201</v>
+      </c>
+      <c r="B203">
+        <v>0.0002354920870857313</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2">
+      <c r="A204">
+        <v>202</v>
+      </c>
+      <c r="B204">
+        <v>0.00119940482545644</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2">
+      <c r="A205">
+        <v>203</v>
+      </c>
+      <c r="B205">
+        <v>0.0005521968705579638</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2">
+      <c r="A206">
+        <v>204</v>
+      </c>
+      <c r="B206">
+        <v>3.749500319827348E-05</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2">
+      <c r="A207">
+        <v>205</v>
+      </c>
+      <c r="B207">
+        <v>0.0003574857255443931</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2">
+      <c r="A208">
+        <v>206</v>
+      </c>
+      <c r="B208">
+        <v>-0.003619681810960174</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2">
+      <c r="A209">
+        <v>207</v>
+      </c>
+      <c r="B209">
+        <v>-7.838116289349273E-05</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2">
+      <c r="A210">
+        <v>208</v>
+      </c>
+      <c r="B210">
+        <v>0.0005814493051730096</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2">
+      <c r="A211">
+        <v>209</v>
+      </c>
+      <c r="B211">
+        <v>0.0001371006510453299</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2">
+      <c r="A212">
+        <v>210</v>
+      </c>
+      <c r="B212">
+        <v>0.000882911728695035</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2">
+      <c r="A213">
+        <v>211</v>
+      </c>
+      <c r="B213">
+        <v>0.000357690587406978</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2">
+      <c r="A214">
+        <v>212</v>
+      </c>
+      <c r="B214">
+        <v>0.0005481686675921082</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2">
+      <c r="A215">
+        <v>213</v>
+      </c>
+      <c r="B215">
+        <v>0.0004005972004961222</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2">
+      <c r="A216">
+        <v>214</v>
+      </c>
+      <c r="B216">
+        <v>0.0004192084597889334</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2">
+      <c r="A217">
+        <v>215</v>
+      </c>
+      <c r="B217">
+        <v>0.0007674673106521368</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2">
+      <c r="A218">
+        <v>216</v>
+      </c>
+      <c r="B218">
+        <v>0.0007240034756250679</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2">
+      <c r="A219">
+        <v>217</v>
+      </c>
+      <c r="B219">
+        <v>0.0001686651667114347</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2">
+      <c r="A220">
+        <v>218</v>
+      </c>
+      <c r="B220">
+        <v>0.0006542635383084416</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2">
+      <c r="A221">
+        <v>219</v>
+      </c>
+      <c r="B221">
+        <v>-0.002672711620107293</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2">
+      <c r="A222">
+        <v>220</v>
+      </c>
+      <c r="B222">
+        <v>0.001047156401909888</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2">
+      <c r="A223">
+        <v>221</v>
+      </c>
+      <c r="B223">
+        <v>-0.0003452724777162075</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2">
+      <c r="A224">
+        <v>222</v>
+      </c>
+      <c r="B224">
+        <v>0.001447466784156859</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2">
+      <c r="A225">
+        <v>223</v>
+      </c>
+      <c r="B225">
+        <v>0.0003933015686925501</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2">
+      <c r="A226">
+        <v>224</v>
+      </c>
+      <c r="B226">
+        <v>0.0006579948822036386</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2">
+      <c r="A227">
+        <v>225</v>
+      </c>
+      <c r="B227">
+        <v>0.001048595877364278</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2">
+      <c r="A228">
+        <v>226</v>
+      </c>
+      <c r="B228">
+        <v>-4.54325600003358E-05</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2">
+      <c r="A229">
+        <v>227</v>
+      </c>
+      <c r="B229">
+        <v>0.0008667081128805876</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2">
+      <c r="A230">
+        <v>228</v>
+      </c>
+      <c r="B230">
+        <v>0.001423383713699877</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2">
+      <c r="A231">
+        <v>229</v>
+      </c>
+      <c r="B231">
+        <v>0.0006472666864283383</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2">
+      <c r="A232">
+        <v>230</v>
+      </c>
+      <c r="B232">
+        <v>0.0002259174070786685</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2">
+      <c r="A233">
+        <v>231</v>
+      </c>
+      <c r="B233">
+        <v>-0.0004814382118638605</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2">
+      <c r="A234">
+        <v>232</v>
+      </c>
+      <c r="B234">
+        <v>0.0003031131054740399</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2">
+      <c r="A235">
+        <v>233</v>
+      </c>
+      <c r="B235">
+        <v>0.001004068879410625</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2">
+      <c r="A236">
+        <v>234</v>
+      </c>
+      <c r="B236">
+        <v>5.075095396023244E-05</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2">
+      <c r="A237">
+        <v>235</v>
+      </c>
+      <c r="B237">
+        <v>0.0007209800533019006</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2">
+      <c r="A238">
+        <v>236</v>
+      </c>
+      <c r="B238">
+        <v>0.000870610645506531</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2">
+      <c r="A239">
+        <v>237</v>
+      </c>
+      <c r="B239">
+        <v>0.0001137690705945715</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2">
+      <c r="A240">
+        <v>238</v>
+      </c>
+      <c r="B240">
+        <v>-0.0005310655105859041</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2">
+      <c r="A241">
+        <v>239</v>
+      </c>
+      <c r="B241">
+        <v>0.002242539077997208</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2">
+      <c r="A242">
+        <v>240</v>
+      </c>
+      <c r="B242">
+        <v>0.0001286389015149325</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2">
+      <c r="A243">
+        <v>241</v>
+      </c>
+      <c r="B243">
+        <v>3.808581095654517E-05</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2">
+      <c r="A244">
+        <v>242</v>
+      </c>
+      <c r="B244">
+        <v>0.0005092910723760724</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2">
+      <c r="A245">
+        <v>243</v>
+      </c>
+      <c r="B245">
+        <v>0.0001574613415868953</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2">
+      <c r="A246">
+        <v>244</v>
+      </c>
+      <c r="B246">
+        <v>0.0004609577590599656</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2">
+      <c r="A247">
+        <v>245</v>
+      </c>
+      <c r="B247">
+        <v>0.003246605629101396</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2">
+      <c r="A248">
+        <v>246</v>
+      </c>
+      <c r="B248">
+        <v>0.0005380198126658797</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2">
+      <c r="A249">
+        <v>247</v>
+      </c>
+      <c r="B249">
+        <v>-0.0001896110916277394</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2">
+      <c r="A250">
+        <v>248</v>
+      </c>
+      <c r="B250">
+        <v>0.0005488136084750295</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2">
+      <c r="A251">
+        <v>249</v>
+      </c>
+      <c r="B251">
+        <v>0.000130251981317997</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2">
+      <c r="A252">
+        <v>250</v>
+      </c>
+      <c r="B252">
+        <v>0.0004830518446397036</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2">
+      <c r="A253">
+        <v>251</v>
+      </c>
+      <c r="B253">
+        <v>0.0008583904127590358</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2">
+      <c r="A254">
+        <v>252</v>
+      </c>
+      <c r="B254">
+        <v>7.745342736598104E-05</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2">
+      <c r="A255">
+        <v>253</v>
+      </c>
+      <c r="B255">
+        <v>-1.801987309590913E-05</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2">
+      <c r="A256">
+        <v>254</v>
+      </c>
+      <c r="B256">
+        <v>0.0005075972876511514</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2">
+      <c r="A257">
+        <v>255</v>
+      </c>
+      <c r="B257">
+        <v>0.0001387249067192897</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2">
+      <c r="A258">
+        <v>256</v>
+      </c>
+      <c r="B258">
+        <v>0.0005946754245087504</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2">
+      <c r="A259">
+        <v>257</v>
+      </c>
+      <c r="B259">
+        <v>0.0001342709438176826</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2">
+      <c r="A260">
+        <v>258</v>
+      </c>
+      <c r="B260">
+        <v>0.001861375058069825</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2">
+      <c r="A261">
+        <v>259</v>
+      </c>
+      <c r="B261">
+        <v>-0.0003286482242401689</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2">
+      <c r="A262">
+        <v>260</v>
+      </c>
+      <c r="B262">
+        <v>0.001379734021611512</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2">
+      <c r="A263">
+        <v>261</v>
+      </c>
+      <c r="B263">
+        <v>0.0002959602570626885</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2">
+      <c r="A264">
+        <v>262</v>
+      </c>
+      <c r="B264">
+        <v>-0.0001000959382508881</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2">
+      <c r="A265">
+        <v>263</v>
+      </c>
+      <c r="B265">
+        <v>0.000396899733459577</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2">
+      <c r="A266">
+        <v>264</v>
+      </c>
+      <c r="B266">
+        <v>0.0008808724815025926</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2">
+      <c r="A267">
+        <v>265</v>
+      </c>
+      <c r="B267">
+        <v>0.0005246790242381394</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2">
+      <c r="A268">
+        <v>266</v>
+      </c>
+      <c r="B268">
+        <v>0.0002107730397256091</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2">
+      <c r="A269">
+        <v>267</v>
+      </c>
+      <c r="B269">
+        <v>0.00139214051887393</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2">
+      <c r="A270">
+        <v>268</v>
+      </c>
+      <c r="B270">
+        <v>0.0002022000116994604</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2">
+      <c r="A271">
+        <v>269</v>
+      </c>
+      <c r="B271">
+        <v>0.0006770858308300376</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2">
+      <c r="A272">
+        <v>270</v>
+      </c>
+      <c r="B272">
+        <v>-0.0006844675517641008</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2">
+      <c r="A273">
+        <v>271</v>
+      </c>
+      <c r="B273">
+        <v>0.002930752700194716</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2">
+      <c r="A274">
+        <v>272</v>
+      </c>
+      <c r="B274">
+        <v>0.0007610806496813893</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2">
+      <c r="A275">
+        <v>273</v>
+      </c>
+      <c r="B275">
+        <v>0.0006461164448410273</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2">
+      <c r="A276">
+        <v>274</v>
+      </c>
+      <c r="B276">
+        <v>0.0005761385546065867</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2">
+      <c r="A277">
+        <v>275</v>
+      </c>
+      <c r="B277">
+        <v>0.0007512037409469485</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2">
+      <c r="A278">
+        <v>276</v>
+      </c>
+      <c r="B278">
+        <v>0.0002821536327246577</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2">
+      <c r="A279">
+        <v>277</v>
+      </c>
+      <c r="B279">
+        <v>0.0005426065181382</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2">
+      <c r="A280">
+        <v>278</v>
+      </c>
+      <c r="B280">
+        <v>0.0001314670953433961</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2">
+      <c r="A281">
+        <v>279</v>
+      </c>
+      <c r="B281">
+        <v>0.0006605704547837377</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2">
+      <c r="A282">
+        <v>280</v>
+      </c>
+      <c r="B282">
+        <v>0.0001019988412735984</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2">
+      <c r="A283">
+        <v>281</v>
+      </c>
+      <c r="B283">
+        <v>0.0006631422438658774</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2">
+      <c r="A284">
+        <v>282</v>
+      </c>
+      <c r="B284">
+        <v>0.0002213749976363033</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2">
+      <c r="A285">
+        <v>283</v>
+      </c>
+      <c r="B285">
+        <v>-0.0001027771504595876</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2">
+      <c r="A286">
+        <v>284</v>
+      </c>
+      <c r="B286">
+        <v>0.001445482019335032</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2">
+      <c r="A287">
+        <v>285</v>
+      </c>
+      <c r="B287">
+        <v>0.0005389252328313887</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2">
+      <c r="A288">
+        <v>286</v>
+      </c>
+      <c r="B288">
+        <v>0.001095182029530406</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2">
+      <c r="A289">
+        <v>287</v>
+      </c>
+      <c r="B289">
+        <v>0.0003652181185316294</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2">
+      <c r="A290">
+        <v>288</v>
+      </c>
+      <c r="B290">
+        <v>0.0001202271596412174</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2">
+      <c r="A291">
+        <v>289</v>
+      </c>
+      <c r="B291">
+        <v>9.678213245933875E-05</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2">
+      <c r="A292">
+        <v>290</v>
+      </c>
+      <c r="B292">
+        <v>0.001025799312628806</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2">
+      <c r="A293">
+        <v>291</v>
+      </c>
+      <c r="B293">
+        <v>0.0003149005060549825</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2">
+      <c r="A294">
+        <v>292</v>
+      </c>
+      <c r="B294">
+        <v>8.663920743856579E-05</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2">
+      <c r="A295">
+        <v>293</v>
+      </c>
+      <c r="B295">
+        <v>0.0006777814705856144</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2">
+      <c r="A296">
+        <v>294</v>
+      </c>
+      <c r="B296">
+        <v>0.0003025136538781226</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2">
+      <c r="A297">
+        <v>295</v>
+      </c>
+      <c r="B297">
+        <v>0.0002533898805268109</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2">
+      <c r="A298">
+        <v>296</v>
+      </c>
+      <c r="B298">
+        <v>0.0003514240961521864</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2">
+      <c r="A299">
+        <v>297</v>
+      </c>
+      <c r="B299">
+        <v>-0.001685321447439492</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2">
+      <c r="A300">
+        <v>298</v>
+      </c>
+      <c r="B300">
+        <v>0.0001980591769097373</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2">
+      <c r="A301">
+        <v>299</v>
+      </c>
+      <c r="B301">
+        <v>0.000569764175452292</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2">
+      <c r="A302">
+        <v>300</v>
+      </c>
+      <c r="B302">
+        <v>0.0001152203039964661</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2">
+      <c r="A303">
+        <v>301</v>
+      </c>
+      <c r="B303">
+        <v>0.0001892213331302628</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2">
+      <c r="A304">
+        <v>302</v>
+      </c>
+      <c r="B304">
+        <v>0.0004151610191911459</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2">
+      <c r="A305">
+        <v>303</v>
+      </c>
+      <c r="B305">
+        <v>0.0008099984843283892</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2">
+      <c r="A306">
+        <v>304</v>
+      </c>
+      <c r="B306">
+        <v>0.0003354485670570284</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2">
+      <c r="A307">
+        <v>305</v>
+      </c>
+      <c r="B307">
+        <v>0.0002789972932077944</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2">
+      <c r="A308">
+        <v>306</v>
+      </c>
+      <c r="B308">
+        <v>-0.0004640787374228239</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2">
+      <c r="A309">
+        <v>307</v>
+      </c>
+      <c r="B309">
+        <v>0.0008681442704983056</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2">
+      <c r="A310">
+        <v>308</v>
+      </c>
+      <c r="B310">
+        <v>0.0003615253954194486</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2">
+      <c r="A311">
+        <v>309</v>
+      </c>
+      <c r="B311">
+        <v>-0.0001452729775337502</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2">
+      <c r="A312">
+        <v>310</v>
+      </c>
+      <c r="B312">
+        <v>0.0008696326403878629</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2">
+      <c r="A313">
+        <v>311</v>
+      </c>
+      <c r="B313">
+        <v>-5.392930324887857E-05</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2">
+      <c r="A314">
+        <v>312</v>
+      </c>
+      <c r="B314">
+        <v>0.001389632350765169</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2">
+      <c r="A315">
+        <v>313</v>
+      </c>
+      <c r="B315">
+        <v>0.0007268073968589306</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2">
+      <c r="A316">
+        <v>314</v>
+      </c>
+      <c r="B316">
+        <v>0.000601581356022507</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2">
+      <c r="A317">
+        <v>315</v>
+      </c>
+      <c r="B317">
+        <v>0.0004111512389499694</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2">
+      <c r="A318">
+        <v>316</v>
+      </c>
+      <c r="B318">
+        <v>0.001449806964956224</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2">
+      <c r="A319">
+        <v>317</v>
+      </c>
+      <c r="B319">
+        <v>-0.0002288533869432285</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2">
+      <c r="A320">
+        <v>318</v>
+      </c>
+      <c r="B320">
+        <v>0.0002380251971771941</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2">
+      <c r="A321">
+        <v>319</v>
+      </c>
+      <c r="B321">
+        <v>0.0009976306464523077</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2">
+      <c r="A322">
+        <v>320</v>
+      </c>
+      <c r="B322">
+        <v>0.0003398661501705647</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2">
+      <c r="A323">
+        <v>321</v>
+      </c>
+      <c r="B323">
+        <v>-4.689135676017031E-05</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2">
+      <c r="A324">
+        <v>322</v>
+      </c>
+      <c r="B324">
+        <v>-0.0005197206046432257</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2">
+      <c r="A325">
+        <v>323</v>
+      </c>
+      <c r="B325">
+        <v>-0.00103889754973352</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2">
+      <c r="A326">
+        <v>324</v>
+      </c>
+      <c r="B326">
+        <v>-0.0001334117550868541</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2">
+      <c r="A327">
+        <v>325</v>
+      </c>
+      <c r="B327">
+        <v>0.001380150439217687</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2">
+      <c r="A328">
+        <v>326</v>
+      </c>
+      <c r="B328">
+        <v>0.0004406249499879777</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2">
+      <c r="A329">
+        <v>327</v>
+      </c>
+      <c r="B329">
+        <v>0.0005340558709576726</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2">
+      <c r="A330">
+        <v>328</v>
+      </c>
+      <c r="B330">
+        <v>0.0001339440495939925</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2">
+      <c r="A331">
+        <v>329</v>
+      </c>
+      <c r="B331">
+        <v>0.0002408444270258769</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2">
+      <c r="A332">
+        <v>330</v>
+      </c>
+      <c r="B332">
+        <v>0.001289153704419732</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2">
+      <c r="A333">
+        <v>331</v>
+      </c>
+      <c r="B333">
+        <v>0.001342110335826874</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2">
+      <c r="A334">
+        <v>332</v>
+      </c>
+      <c r="B334">
+        <v>0.0009335227077826858</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2">
+      <c r="A335">
+        <v>333</v>
+      </c>
+      <c r="B335">
+        <v>0.00102547905407846</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2">
+      <c r="A336">
+        <v>334</v>
+      </c>
+      <c r="B336">
+        <v>0.0004692562797572464</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2">
+      <c r="A337">
+        <v>335</v>
+      </c>
+      <c r="B337">
+        <v>0.001910770894028246</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2">
+      <c r="A338">
+        <v>336</v>
+      </c>
+      <c r="B338">
+        <v>0.001075800624676049</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2">
+      <c r="A339">
+        <v>337</v>
+      </c>
+      <c r="B339">
+        <v>0.0002642267209012061</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2">
+      <c r="A340">
+        <v>338</v>
+      </c>
+      <c r="B340">
+        <v>0.001043873839080334</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2">
+      <c r="A341">
+        <v>339</v>
+      </c>
+      <c r="B341">
+        <v>-4.525798794929869E-05</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2">
+      <c r="A342">
+        <v>340</v>
+      </c>
+      <c r="B342">
+        <v>0.001074030064046383</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2">
+      <c r="A343">
+        <v>341</v>
+      </c>
+      <c r="B343">
+        <v>0.0007983858231455088</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2">
+      <c r="A344">
+        <v>342</v>
+      </c>
+      <c r="B344">
+        <v>0.0003936956054531038</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2">
+      <c r="A345">
+        <v>343</v>
+      </c>
+      <c r="B345">
+        <v>0.001073887920938432</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2">
+      <c r="A346">
+        <v>344</v>
+      </c>
+      <c r="B346">
+        <v>0.0002225048665422946</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2">
+      <c r="A347">
+        <v>345</v>
+      </c>
+      <c r="B347">
+        <v>0.0004629987524822354</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2">
+      <c r="A348">
+        <v>346</v>
+      </c>
+      <c r="B348">
+        <v>0.000417607108829543</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2">
+      <c r="A349">
+        <v>347</v>
+      </c>
+      <c r="B349">
+        <v>0.0004440407210495323</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2">
+      <c r="A350">
+        <v>348</v>
+      </c>
+      <c r="B350">
+        <v>0.0008048453601077199</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2">
+      <c r="A351">
+        <v>349</v>
+      </c>
+      <c r="B351">
+        <v>0.0006229458376765251</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2">
+      <c r="A352">
+        <v>350</v>
+      </c>
+      <c r="B352">
+        <v>0.001189168193377554</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2">
+      <c r="A353">
+        <v>351</v>
+      </c>
+      <c r="B353">
+        <v>0.0006134375580586493</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2">
+      <c r="A354">
+        <v>352</v>
+      </c>
+      <c r="B354">
+        <v>0.0005705207004211843</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2">
+      <c r="A355">
+        <v>353</v>
+      </c>
+      <c r="B355">
+        <v>0.0009519836166873574</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2">
+      <c r="A356">
+        <v>354</v>
+      </c>
+      <c r="B356">
+        <v>0.0008589830831624568</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2">
+      <c r="A357">
+        <v>355</v>
+      </c>
+      <c r="B357">
+        <v>0.0006982036866247654</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2">
+      <c r="A358">
+        <v>356</v>
+      </c>
+      <c r="B358">
+        <v>0.0001698279811535031</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2">
+      <c r="A359">
+        <v>357</v>
+      </c>
+      <c r="B359">
+        <v>0.0001846458908403292</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2">
+      <c r="A360">
+        <v>358</v>
+      </c>
+      <c r="B360">
+        <v>0.0005281943595036864</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2">
+      <c r="A361">
+        <v>359</v>
+      </c>
+      <c r="B361">
+        <v>-5.251209222478792E-05</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2">
+      <c r="A362">
+        <v>360</v>
+      </c>
+      <c r="B362">
+        <v>9.917072748066857E-05</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2">
+      <c r="A363">
+        <v>361</v>
+      </c>
+      <c r="B363">
+        <v>0.002527666976675391</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2">
+      <c r="A364">
+        <v>362</v>
+      </c>
+      <c r="B364">
+        <v>-0.0002944400766864419</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2">
+      <c r="A365">
+        <v>363</v>
+      </c>
+      <c r="B365">
+        <v>-0.0009038542630150914</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2">
+      <c r="A366">
+        <v>364</v>
+      </c>
+      <c r="B366">
+        <v>0.0008899974636733532</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2">
+      <c r="A367">
+        <v>365</v>
+      </c>
+      <c r="B367">
+        <v>0.0009906357154250145</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2">
+      <c r="A368">
+        <v>366</v>
+      </c>
+      <c r="B368">
+        <v>0.0003990139521192759</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2">
+      <c r="A369">
+        <v>367</v>
+      </c>
+      <c r="B369">
+        <v>0.0008517677779309452</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2">
+      <c r="A370">
+        <v>368</v>
+      </c>
+      <c r="B370">
+        <v>0.0001677826658124104</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2">
+      <c r="A371">
+        <v>369</v>
+      </c>
+      <c r="B371">
+        <v>0.000109343760414049</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2">
+      <c r="A372">
+        <v>370</v>
+      </c>
+      <c r="B372">
+        <v>0.0005990737117826939</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2">
+      <c r="A373">
+        <v>371</v>
+      </c>
+      <c r="B373">
+        <v>0.0005025455029681325</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2">
+      <c r="A374">
+        <v>372</v>
+      </c>
+      <c r="B374">
+        <v>0.0005146587500348687</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2">
+      <c r="A375">
+        <v>373</v>
+      </c>
+      <c r="B375">
+        <v>0.0002923837746493518</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2">
+      <c r="A376">
+        <v>374</v>
+      </c>
+      <c r="B376">
+        <v>0.001398473861627281</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2">
+      <c r="A377">
+        <v>375</v>
+      </c>
+      <c r="B377">
+        <v>0.003347755642607808</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2">
+      <c r="A378">
+        <v>376</v>
+      </c>
+      <c r="B378">
+        <v>0.0001696615508990362</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2">
+      <c r="A379">
+        <v>377</v>
+      </c>
+      <c r="B379">
+        <v>2.615089397295378E-05</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2">
+      <c r="A380">
+        <v>378</v>
+      </c>
+      <c r="B380">
+        <v>0.0004191840416751802</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2">
+      <c r="A381">
+        <v>379</v>
+      </c>
+      <c r="B381">
+        <v>0.0004056530306115746</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2">
+      <c r="A382">
+        <v>380</v>
+      </c>
+      <c r="B382">
+        <v>0.0007361869793385267</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2">
+      <c r="A383">
+        <v>381</v>
+      </c>
+      <c r="B383">
+        <v>0.0001348947844235227</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2">
+      <c r="A384">
+        <v>382</v>
+      </c>
+      <c r="B384">
+        <v>0.0005872236215509474</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2">
+      <c r="A385">
+        <v>383</v>
+      </c>
+      <c r="B385">
+        <v>0.0004892763681709766</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2">
+      <c r="A386">
+        <v>384</v>
+      </c>
+      <c r="B386">
+        <v>0.000801829737611115</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2">
+      <c r="A387">
+        <v>385</v>
+      </c>
+      <c r="B387">
+        <v>0.001283071702346206</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2">
+      <c r="A388">
+        <v>386</v>
+      </c>
+      <c r="B388">
+        <v>0.001678303931839764</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2">
+      <c r="A389">
+        <v>387</v>
+      </c>
+      <c r="B389">
+        <v>0.001412252546288073</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2">
+      <c r="A390">
+        <v>388</v>
+      </c>
+      <c r="B390">
+        <v>0.0007008450920693576</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2">
+      <c r="A391">
+        <v>389</v>
+      </c>
+      <c r="B391">
+        <v>0.000849552801810205</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2">
+      <c r="A392">
+        <v>390</v>
+      </c>
+      <c r="B392">
+        <v>0.0007722604204900563</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2">
+      <c r="A393">
+        <v>391</v>
+      </c>
+      <c r="B393">
+        <v>0.001173489377833903</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2">
+      <c r="A394">
+        <v>392</v>
+      </c>
+      <c r="B394">
+        <v>0.001157061429694295</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2">
+      <c r="A395">
+        <v>393</v>
+      </c>
+      <c r="B395">
+        <v>0.0001186570079880767</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2">
+      <c r="A396">
+        <v>394</v>
+      </c>
+      <c r="B396">
+        <v>0.0004621690895874053</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2">
+      <c r="A397">
+        <v>395</v>
+      </c>
+      <c r="B397">
+        <v>0.0002260568435303867</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2">
+      <c r="A398">
+        <v>396</v>
+      </c>
+      <c r="B398">
+        <v>0.0002744598605204374</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2">
+      <c r="A399">
+        <v>397</v>
+      </c>
+      <c r="B399">
+        <v>9.258429054170847E-05</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2">
+      <c r="A400">
+        <v>398</v>
+      </c>
+      <c r="B400">
+        <v>0.0001605121215106919</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2">
+      <c r="A401">
+        <v>399</v>
+      </c>
+      <c r="B401">
+        <v>0.0003811471397057176</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2">
+      <c r="A402">
+        <v>400</v>
+      </c>
+      <c r="B402">
+        <v>1.371199778077425E-05</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2">
+      <c r="A403">
+        <v>401</v>
+      </c>
+      <c r="B403">
+        <v>0.0007498286431655288</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2">
+      <c r="A404">
+        <v>402</v>
+      </c>
+      <c r="B404">
+        <v>0.001259426004253328</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2">
+      <c r="A405">
+        <v>403</v>
+      </c>
+      <c r="B405">
+        <v>0.0006197122856974602</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2">
+      <c r="A406">
+        <v>404</v>
+      </c>
+      <c r="B406">
+        <v>-0.0001196565499412827</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2">
+      <c r="A407">
+        <v>405</v>
+      </c>
+      <c r="B407">
+        <v>0.001964299939572811</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2">
+      <c r="A408">
+        <v>406</v>
+      </c>
+      <c r="B408">
+        <v>0.001659814384765923</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2">
+      <c r="A409">
+        <v>407</v>
+      </c>
+      <c r="B409">
+        <v>-4.176827496849E-05</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2">
+      <c r="A410">
+        <v>408</v>
+      </c>
+      <c r="B410">
+        <v>2.98204777209321E-05</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2">
+      <c r="A411">
+        <v>409</v>
+      </c>
+      <c r="B411">
+        <v>0.0001351663086097687</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2">
+      <c r="A412">
+        <v>410</v>
+      </c>
+      <c r="B412">
+        <v>0.002008306561037898</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2">
+      <c r="A413">
+        <v>411</v>
+      </c>
+      <c r="B413">
+        <v>0.0005271355621516705</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2">
+      <c r="A414">
+        <v>412</v>
+      </c>
+      <c r="B414">
+        <v>-6.914213008712977E-05</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2">
+      <c r="A415">
+        <v>413</v>
+      </c>
+      <c r="B415">
+        <v>-0.0002715489536058158</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2">
+      <c r="A416">
+        <v>414</v>
+      </c>
+      <c r="B416">
+        <v>0.0005669989623129368</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2">
+      <c r="A417">
+        <v>415</v>
+      </c>
+      <c r="B417">
+        <v>0.0004145090933889151</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2">
+      <c r="A418">
+        <v>416</v>
+      </c>
+      <c r="B418">
+        <v>0.0007426898810081184</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2">
+      <c r="A419">
+        <v>417</v>
+      </c>
+      <c r="B419">
+        <v>0.0008678142912685871</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2">
+      <c r="A420">
+        <v>418</v>
+      </c>
+      <c r="B420">
+        <v>0.0007371266256086528</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2">
+      <c r="A421">
+        <v>419</v>
+      </c>
+      <c r="B421">
+        <v>0.0004138055664952844</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2">
+      <c r="A422">
+        <v>420</v>
+      </c>
+      <c r="B422">
+        <v>0.001376316766254604</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2">
+      <c r="A423">
+        <v>421</v>
+      </c>
+      <c r="B423">
+        <v>5.499287362908944E-05</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2">
+      <c r="A424">
+        <v>422</v>
+      </c>
+      <c r="B424">
+        <v>0.000935391872189939</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2">
+      <c r="A425">
+        <v>423</v>
+      </c>
+      <c r="B425">
+        <v>0.000255077495239675</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2">
+      <c r="A426">
+        <v>424</v>
+      </c>
+      <c r="B426">
+        <v>0.001479333965107799</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2">
+      <c r="A427">
+        <v>425</v>
+      </c>
+      <c r="B427">
+        <v>-0.0001987968571484089</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2">
+      <c r="A428">
+        <v>426</v>
+      </c>
+      <c r="B428">
+        <v>0.001728787552565336</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2">
+      <c r="A429">
+        <v>427</v>
+      </c>
+      <c r="B429">
+        <v>0.0006361561245284975</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2">
+      <c r="A430">
+        <v>428</v>
+      </c>
+      <c r="B430">
+        <v>0.0007923946832306683</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2">
+      <c r="A431">
+        <v>429</v>
+      </c>
+      <c r="B431">
+        <v>0.0002671696711331606</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2">
+      <c r="A432">
+        <v>430</v>
+      </c>
+      <c r="B432">
+        <v>0.0005574533133767545</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2">
+      <c r="A433">
+        <v>431</v>
+      </c>
+      <c r="B433">
+        <v>0.0004256995453033596</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2">
+      <c r="A434">
+        <v>432</v>
+      </c>
+      <c r="B434">
+        <v>0.001191360410302877</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2">
+      <c r="A435">
+        <v>433</v>
+      </c>
+      <c r="B435">
+        <v>0.0007802707841619849</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2">
+      <c r="A436">
+        <v>434</v>
+      </c>
+      <c r="B436">
+        <v>0.0004395237192511559</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2">
+      <c r="A437">
+        <v>435</v>
+      </c>
+      <c r="B437">
+        <v>0.0009907428175210953</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2">
+      <c r="A438">
+        <v>436</v>
+      </c>
+      <c r="B438">
+        <v>0.002193504711613059</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2">
+      <c r="A439">
+        <v>437</v>
+      </c>
+      <c r="B439">
+        <v>0.0001407715026289225</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2">
+      <c r="A440">
+        <v>438</v>
+      </c>
+      <c r="B440">
+        <v>0.00204218877479434</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2">
+      <c r="A441">
+        <v>439</v>
+      </c>
+      <c r="B441">
+        <v>0.003514196258038282</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2">
+      <c r="A442">
+        <v>440</v>
+      </c>
+      <c r="B442">
+        <v>0.0002108344488078728</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2">
+      <c r="A443">
+        <v>441</v>
+      </c>
+      <c r="B443">
+        <v>0.0006251154118217528</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2">
+      <c r="A444">
+        <v>442</v>
+      </c>
+      <c r="B444">
+        <v>0.0004392594273667783</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2">
+      <c r="A445">
+        <v>443</v>
+      </c>
+      <c r="B445">
+        <v>0.0006863088929094374</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2">
+      <c r="A446">
+        <v>444</v>
+      </c>
+      <c r="B446">
+        <v>0.0002071427734335884</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2">
+      <c r="A447">
+        <v>445</v>
+      </c>
+      <c r="B447">
+        <v>0.0003428620693739504</v>
+      </c>
+    </row>
+    <row r="448" spans="1:2">
+      <c r="A448">
+        <v>446</v>
+      </c>
+      <c r="B448">
+        <v>0.0003219846112187952</v>
+      </c>
+    </row>
+    <row r="449" spans="1:2">
+      <c r="A449">
+        <v>447</v>
+      </c>
+      <c r="B449">
+        <v>0.0005539043340831995</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2">
+      <c r="A450">
+        <v>448</v>
+      </c>
+      <c r="B450">
+        <v>0.000513346865773201</v>
+      </c>
+    </row>
+    <row r="451" spans="1:2">
+      <c r="A451">
+        <v>449</v>
+      </c>
+      <c r="B451">
+        <v>-0.0003431354416534305</v>
+      </c>
+    </row>
+    <row r="452" spans="1:2">
+      <c r="A452">
+        <v>450</v>
+      </c>
+      <c r="B452">
+        <v>-4.624894791049883E-05</v>
+      </c>
+    </row>
+    <row r="453" spans="1:2">
+      <c r="A453">
+        <v>451</v>
+      </c>
+      <c r="B453">
+        <v>0.0005034100613556802</v>
+      </c>
+    </row>
+    <row r="454" spans="1:2">
+      <c r="A454">
+        <v>452</v>
+      </c>
+      <c r="B454">
+        <v>-0.001317897229455411</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2">
+      <c r="A455">
+        <v>453</v>
+      </c>
+      <c r="B455">
+        <v>-0.0004165616119280457</v>
+      </c>
+    </row>
+    <row r="456" spans="1:2">
+      <c r="A456">
+        <v>454</v>
+      </c>
+      <c r="B456">
+        <v>0.0008284003706648946</v>
+      </c>
+    </row>
+    <row r="457" spans="1:2">
+      <c r="A457">
+        <v>455</v>
+      </c>
+      <c r="B457">
+        <v>0.0006967498338781297</v>
+      </c>
+    </row>
+    <row r="458" spans="1:2">
+      <c r="A458">
+        <v>456</v>
+      </c>
+      <c r="B458">
+        <v>0.0007510032155551016</v>
+      </c>
+    </row>
+    <row r="459" spans="1:2">
+      <c r="A459">
+        <v>457</v>
+      </c>
+      <c r="B459">
+        <v>0.0006899087456986308</v>
+      </c>
+    </row>
+    <row r="460" spans="1:2">
+      <c r="A460">
+        <v>458</v>
+      </c>
+      <c r="B460">
+        <v>0.0002043679269263521</v>
+      </c>
+    </row>
+    <row r="461" spans="1:2">
+      <c r="A461">
+        <v>459</v>
+      </c>
+      <c r="B461">
+        <v>0.001101438188925385</v>
+      </c>
+    </row>
+    <row r="462" spans="1:2">
+      <c r="A462">
+        <v>460</v>
+      </c>
+      <c r="B462">
+        <v>0.0002711537235882133</v>
+      </c>
+    </row>
+    <row r="463" spans="1:2">
+      <c r="A463">
+        <v>461</v>
+      </c>
+      <c r="B463">
+        <v>0.001956445164978504</v>
+      </c>
+    </row>
+    <row r="464" spans="1:2">
+      <c r="A464">
+        <v>462</v>
+      </c>
+      <c r="B464">
+        <v>0.0001734734105411917</v>
+      </c>
+    </row>
+    <row r="465" spans="1:2">
+      <c r="A465">
+        <v>463</v>
+      </c>
+      <c r="B465">
+        <v>-0.0001858066098066047</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2">
+      <c r="A466">
+        <v>464</v>
+      </c>
+      <c r="B466">
+        <v>0.001171782962046564</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2">
+      <c r="A467">
+        <v>465</v>
+      </c>
+      <c r="B467">
+        <v>0.0007210492040030658</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2">
+      <c r="A468">
+        <v>466</v>
+      </c>
+      <c r="B468">
+        <v>0.001223949366249144</v>
+      </c>
+    </row>
+    <row r="469" spans="1:2">
+      <c r="A469">
+        <v>467</v>
+      </c>
+      <c r="B469">
+        <v>0.0005957132671028376</v>
+      </c>
+    </row>
+    <row r="470" spans="1:2">
+      <c r="A470">
+        <v>468</v>
+      </c>
+      <c r="B470">
+        <v>0.001491583418101072</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2">
+      <c r="A471">
+        <v>469</v>
+      </c>
+      <c r="B471">
+        <v>0.000520958099514246</v>
+      </c>
+    </row>
+    <row r="472" spans="1:2">
+      <c r="A472">
+        <v>470</v>
+      </c>
+      <c r="B472">
+        <v>0.000441478710854426</v>
+      </c>
+    </row>
+    <row r="473" spans="1:2">
+      <c r="A473">
+        <v>471</v>
+      </c>
+      <c r="B473">
+        <v>0.0004637552774511278</v>
+      </c>
+    </row>
+    <row r="474" spans="1:2">
+      <c r="A474">
+        <v>472</v>
+      </c>
+      <c r="B474">
+        <v>0.0001192563868244179</v>
+      </c>
+    </row>
+    <row r="475" spans="1:2">
+      <c r="A475">
+        <v>473</v>
+      </c>
+      <c r="B475">
+        <v>0.0003071905812248588</v>
+      </c>
+    </row>
+    <row r="476" spans="1:2">
+      <c r="A476">
+        <v>474</v>
+      </c>
+      <c r="B476">
+        <v>0.0002780136710498482</v>
+      </c>
+    </row>
+    <row r="477" spans="1:2">
+      <c r="A477">
+        <v>475</v>
+      </c>
+      <c r="B477">
+        <v>0.0003623652446549386</v>
+      </c>
+    </row>
+    <row r="478" spans="1:2">
+      <c r="A478">
+        <v>476</v>
+      </c>
+      <c r="B478">
+        <v>0.001365863136015832</v>
+      </c>
+    </row>
+    <row r="479" spans="1:2">
+      <c r="A479">
+        <v>477</v>
+      </c>
+      <c r="B479">
+        <v>0.001049229642376304</v>
+      </c>
+    </row>
+    <row r="480" spans="1:2">
+      <c r="A480">
+        <v>478</v>
+      </c>
+      <c r="B480">
+        <v>0.005852012429386377</v>
+      </c>
+    </row>
+    <row r="481" spans="1:2">
+      <c r="A481">
+        <v>479</v>
+      </c>
+      <c r="B481">
+        <v>0.0010880206245929</v>
+      </c>
+    </row>
+    <row r="482" spans="1:2">
+      <c r="A482">
+        <v>480</v>
+      </c>
+      <c r="B482">
+        <v>0.0003183942753821611</v>
+      </c>
+    </row>
+    <row r="483" spans="1:2">
+      <c r="A483">
+        <v>481</v>
+      </c>
+      <c r="B483">
+        <v>0.0009151604026556015</v>
+      </c>
+    </row>
+    <row r="484" spans="1:2">
+      <c r="A484">
+        <v>482</v>
+      </c>
+      <c r="B484">
+        <v>0.0004748026258312166</v>
+      </c>
+    </row>
+    <row r="485" spans="1:2">
+      <c r="A485">
+        <v>483</v>
+      </c>
+      <c r="B485">
+        <v>0.0005804283428005874</v>
+      </c>
+    </row>
+    <row r="486" spans="1:2">
+      <c r="A486">
+        <v>484</v>
+      </c>
+      <c r="B486">
+        <v>-7.038611511234194E-05</v>
+      </c>
+    </row>
+    <row r="487" spans="1:2">
+      <c r="A487">
+        <v>485</v>
+      </c>
+      <c r="B487">
+        <v>0.0002800083020702004</v>
+      </c>
+    </row>
+    <row r="488" spans="1:2">
+      <c r="A488">
+        <v>486</v>
+      </c>
+      <c r="B488">
+        <v>0.0001371900289086625</v>
+      </c>
+    </row>
+    <row r="489" spans="1:2">
+      <c r="A489">
+        <v>487</v>
+      </c>
+      <c r="B489">
+        <v>0.001444582245312631</v>
+      </c>
+    </row>
+    <row r="490" spans="1:2">
+      <c r="A490">
+        <v>488</v>
+      </c>
+      <c r="B490">
+        <v>0.000556289975065738</v>
+      </c>
+    </row>
+    <row r="491" spans="1:2">
+      <c r="A491">
+        <v>489</v>
+      </c>
+      <c r="B491">
+        <v>0.0004217277746647596</v>
+      </c>
+    </row>
+    <row r="492" spans="1:2">
+      <c r="A492">
+        <v>490</v>
+      </c>
+      <c r="B492">
+        <v>0.0004971611779183149</v>
+      </c>
+    </row>
+    <row r="493" spans="1:2">
+      <c r="A493">
+        <v>491</v>
+      </c>
+      <c r="B493">
+        <v>0.001553411362692714</v>
+      </c>
+    </row>
+    <row r="494" spans="1:2">
+      <c r="A494">
+        <v>492</v>
+      </c>
+      <c r="B494">
+        <v>0.0007579423254355788</v>
+      </c>
+    </row>
+    <row r="495" spans="1:2">
+      <c r="A495">
+        <v>493</v>
+      </c>
+      <c r="B495">
+        <v>0.0008471919572912157</v>
+      </c>
+    </row>
+    <row r="496" spans="1:2">
+      <c r="A496">
+        <v>494</v>
+      </c>
+      <c r="B496">
+        <v>0.0007710499339736998</v>
+      </c>
+    </row>
+    <row r="497" spans="1:2">
+      <c r="A497">
+        <v>495</v>
+      </c>
+      <c r="B497">
+        <v>0.0006445078179240227</v>
+      </c>
+    </row>
+    <row r="498" spans="1:2">
+      <c r="A498">
+        <v>496</v>
+      </c>
+      <c r="B498">
+        <v>0.0003258861252106726</v>
+      </c>
+    </row>
+    <row r="499" spans="1:2">
+      <c r="A499">
+        <v>497</v>
+      </c>
+      <c r="B499">
+        <v>0.0001962435781024396</v>
+      </c>
+    </row>
+    <row r="500" spans="1:2">
+      <c r="A500">
+        <v>498</v>
+      </c>
+      <c r="B500">
+        <v>0.0005462449626065791</v>
+      </c>
+    </row>
+    <row r="501" spans="1:2">
+      <c r="A501">
+        <v>499</v>
+      </c>
+      <c r="B501">
+        <v>0.0004918001941405237</v>
+      </c>
+    </row>
+    <row r="502" spans="1:2">
+      <c r="A502">
+        <v>500</v>
+      </c>
+      <c r="B502">
+        <v>0.0006834067753516138</v>
+      </c>
+    </row>
+    <row r="503" spans="1:2">
+      <c r="A503">
+        <v>501</v>
+      </c>
+      <c r="B503">
+        <v>0.0008033631020225585</v>
+      </c>
+    </row>
+    <row r="504" spans="1:2">
+      <c r="A504">
+        <v>502</v>
+      </c>
+      <c r="B504">
+        <v>0.001366710173897445</v>
+      </c>
+    </row>
+    <row r="505" spans="1:2">
+      <c r="A505">
+        <v>503</v>
+      </c>
+      <c r="B505">
+        <v>0.00143153069075197</v>
+      </c>
+    </row>
+    <row r="506" spans="1:2">
+      <c r="A506">
+        <v>504</v>
+      </c>
+      <c r="B506">
+        <v>-0.0009500614833086729</v>
+      </c>
+    </row>
+    <row r="507" spans="1:2">
+      <c r="A507">
+        <v>505</v>
+      </c>
+      <c r="B507">
+        <v>0.001442288397811353</v>
+      </c>
+    </row>
+    <row r="508" spans="1:2">
+      <c r="A508">
+        <v>506</v>
+      </c>
+      <c r="B508">
+        <v>0.0009185887174680829</v>
+      </c>
+    </row>
+    <row r="509" spans="1:2">
+      <c r="A509">
+        <v>507</v>
+      </c>
+      <c r="B509">
+        <v>0.000529491575434804</v>
+      </c>
+    </row>
+    <row r="510" spans="1:2">
+      <c r="A510">
+        <v>508</v>
+      </c>
+      <c r="B510">
+        <v>0.001080235815607011</v>
+      </c>
+    </row>
+    <row r="511" spans="1:2">
+      <c r="A511">
+        <v>509</v>
+      </c>
+      <c r="B511">
+        <v>7.808829104760662E-05</v>
+      </c>
+    </row>
+    <row r="512" spans="1:2">
+      <c r="A512">
+        <v>510</v>
+      </c>
+      <c r="B512">
+        <v>0.000415477086789906</v>
+      </c>
+    </row>
+    <row r="513" spans="1:2">
+      <c r="A513">
+        <v>511</v>
+      </c>
+      <c r="B513">
+        <v>0.0005155969993211329</v>
+      </c>
+    </row>
+    <row r="514" spans="1:2">
+      <c r="A514">
+        <v>512</v>
+      </c>
+      <c r="B514">
+        <v>0.0002499075490050018</v>
+      </c>
+    </row>
+    <row r="515" spans="1:2">
+      <c r="A515">
+        <v>513</v>
+      </c>
+      <c r="B515">
+        <v>6.141974881757051E-05</v>
+      </c>
+    </row>
+    <row r="516" spans="1:2">
+      <c r="A516">
+        <v>514</v>
+      </c>
+      <c r="B516">
+        <v>-1.11240879050456E-05</v>
+      </c>
+    </row>
+    <row r="517" spans="1:2">
+      <c r="A517">
+        <v>515</v>
+      </c>
+      <c r="B517">
+        <v>-0.0001300513395108283</v>
+      </c>
+    </row>
+    <row r="518" spans="1:2">
+      <c r="A518">
+        <v>516</v>
+      </c>
+      <c r="B518">
+        <v>0.001054939581081271</v>
+      </c>
+    </row>
+    <row r="519" spans="1:2">
+      <c r="A519">
+        <v>517</v>
+      </c>
+      <c r="B519">
+        <v>0.002297563245519996</v>
+      </c>
+    </row>
+    <row r="520" spans="1:2">
+      <c r="A520">
+        <v>518</v>
+      </c>
+      <c r="B520">
+        <v>0.0007246860186569393</v>
+      </c>
+    </row>
+    <row r="521" spans="1:2">
+      <c r="A521">
+        <v>519</v>
+      </c>
+      <c r="B521">
+        <v>0.0001880021882243454</v>
+      </c>
+    </row>
+    <row r="522" spans="1:2">
+      <c r="A522">
+        <v>520</v>
+      </c>
+      <c r="B522">
+        <v>0.0006072262185625732</v>
+      </c>
+    </row>
+    <row r="523" spans="1:2">
+      <c r="A523">
+        <v>521</v>
+      </c>
+      <c r="B523">
+        <v>0.0003626709512900561</v>
+      </c>
+    </row>
+    <row r="524" spans="1:2">
+      <c r="A524">
+        <v>522</v>
+      </c>
+      <c r="B524">
+        <v>0.001116373925469816</v>
+      </c>
+    </row>
+    <row r="525" spans="1:2">
+      <c r="A525">
+        <v>523</v>
+      </c>
+      <c r="B525">
+        <v>0.001318742521107197</v>
+      </c>
+    </row>
+    <row r="526" spans="1:2">
+      <c r="A526">
+        <v>524</v>
+      </c>
+      <c r="B526">
+        <v>0.0008373867021873593</v>
+      </c>
+    </row>
+    <row r="527" spans="1:2">
+      <c r="A527">
+        <v>525</v>
+      </c>
+      <c r="B527">
+        <v>0.001399801461957395</v>
+      </c>
+    </row>
+    <row r="528" spans="1:2">
+      <c r="A528">
+        <v>526</v>
+      </c>
+      <c r="B528">
+        <v>0.0001846449740696698</v>
+      </c>
+    </row>
+    <row r="529" spans="1:2">
+      <c r="A529">
+        <v>527</v>
+      </c>
+      <c r="B529">
+        <v>7.818955782568082E-05</v>
+      </c>
+    </row>
+    <row r="530" spans="1:2">
+      <c r="A530">
+        <v>528</v>
+      </c>
+      <c r="B530">
+        <v>0.0005689164972864091</v>
+      </c>
+    </row>
+    <row r="531" spans="1:2">
+      <c r="A531">
+        <v>529</v>
+      </c>
+      <c r="B531">
+        <v>0.000600684667006135</v>
+      </c>
+    </row>
+    <row r="532" spans="1:2">
+      <c r="A532">
+        <v>530</v>
+      </c>
+      <c r="B532">
+        <v>0.0005031010950915515</v>
+      </c>
+    </row>
+    <row r="533" spans="1:2">
+      <c r="A533">
+        <v>531</v>
+      </c>
+      <c r="B533">
+        <v>0.0003829031193163246</v>
+      </c>
+    </row>
+    <row r="534" spans="1:2">
+      <c r="A534">
+        <v>532</v>
+      </c>
+      <c r="B534">
+        <v>0.0006584067596122622</v>
+      </c>
+    </row>
+    <row r="535" spans="1:2">
+      <c r="A535">
+        <v>533</v>
+      </c>
+      <c r="B535">
+        <v>0.0006332991761155427</v>
+      </c>
+    </row>
+    <row r="536" spans="1:2">
+      <c r="A536">
+        <v>534</v>
+      </c>
+      <c r="B536">
+        <v>5.946364763076417E-05</v>
+      </c>
+    </row>
+    <row r="537" spans="1:2">
+      <c r="A537">
+        <v>535</v>
+      </c>
+      <c r="B537">
+        <v>0.001391154597513378</v>
+      </c>
+    </row>
+    <row r="538" spans="1:2">
+      <c r="A538">
+        <v>536</v>
+      </c>
+      <c r="B538">
+        <v>0.0008386051049456</v>
+      </c>
+    </row>
+    <row r="539" spans="1:2">
+      <c r="A539">
+        <v>537</v>
+      </c>
+      <c r="B539">
+        <v>0.002911597955971956</v>
+      </c>
+    </row>
+    <row r="540" spans="1:2">
+      <c r="A540">
+        <v>538</v>
+      </c>
+      <c r="B540">
+        <v>0.0001064643874997273</v>
+      </c>
+    </row>
+    <row r="541" spans="1:2">
+      <c r="A541">
+        <v>539</v>
+      </c>
+      <c r="B541">
+        <v>0.0002383893297519535</v>
+      </c>
+    </row>
+    <row r="542" spans="1:2">
+      <c r="A542">
+        <v>540</v>
+      </c>
+      <c r="B542">
+        <v>0.0006042063469067216</v>
+      </c>
+    </row>
+    <row r="543" spans="1:2">
+      <c r="A543">
+        <v>541</v>
+      </c>
+      <c r="B543">
+        <v>0.0003712762554641813</v>
+      </c>
+    </row>
+    <row r="544" spans="1:2">
+      <c r="A544">
+        <v>542</v>
+      </c>
+      <c r="B544">
+        <v>0.00037090849946253</v>
+      </c>
+    </row>
+    <row r="545" spans="1:2">
+      <c r="A545">
+        <v>543</v>
+      </c>
+      <c r="B545">
+        <v>6.877981650177389E-05</v>
+      </c>
+    </row>
+    <row r="546" spans="1:2">
+      <c r="A546">
+        <v>544</v>
+      </c>
+      <c r="B546">
+        <v>0.0009522692416794598</v>
+      </c>
+    </row>
+    <row r="547" spans="1:2">
+      <c r="A547">
+        <v>545</v>
+      </c>
+      <c r="B547">
+        <v>0.0004402768681757152</v>
+      </c>
+    </row>
+    <row r="548" spans="1:2">
+      <c r="A548">
+        <v>546</v>
+      </c>
+      <c r="B548">
+        <v>0.001062584924511611</v>
+      </c>
+    </row>
+    <row r="549" spans="1:2">
+      <c r="A549">
+        <v>547</v>
+      </c>
+      <c r="B549">
+        <v>0.0007685890304856002</v>
+      </c>
+    </row>
+    <row r="550" spans="1:2">
+      <c r="A550">
+        <v>548</v>
+      </c>
+      <c r="B550">
+        <v>0.0007418345776386559</v>
+      </c>
+    </row>
+    <row r="551" spans="1:2">
+      <c r="A551">
+        <v>549</v>
+      </c>
+      <c r="B551">
+        <v>0.0006330183823592961</v>
+      </c>
+    </row>
+    <row r="552" spans="1:2">
+      <c r="A552">
+        <v>550</v>
+      </c>
+      <c r="B552">
+        <v>0.001792849041521549</v>
+      </c>
+    </row>
+    <row r="553" spans="1:2">
+      <c r="A553">
+        <v>551</v>
+      </c>
+      <c r="B553">
+        <v>0.001609535538591444</v>
+      </c>
+    </row>
+    <row r="554" spans="1:2">
+      <c r="A554">
+        <v>552</v>
+      </c>
+      <c r="B554">
+        <v>0.000546553113963455</v>
+      </c>
+    </row>
+    <row r="555" spans="1:2">
+      <c r="A555">
+        <v>553</v>
+      </c>
+      <c r="B555">
+        <v>0.0007147965370677412</v>
+      </c>
+    </row>
+    <row r="556" spans="1:2">
+      <c r="A556">
+        <v>554</v>
+      </c>
+      <c r="B556">
+        <v>0.0009509979281574488</v>
+      </c>
+    </row>
+    <row r="557" spans="1:2">
+      <c r="A557">
+        <v>555</v>
+      </c>
+      <c r="B557">
+        <v>0.0008167434716597199</v>
+      </c>
+    </row>
+    <row r="558" spans="1:2">
+      <c r="A558">
+        <v>556</v>
+      </c>
+      <c r="B558">
+        <v>0.00109622220043093</v>
+      </c>
+    </row>
+    <row r="559" spans="1:2">
+      <c r="A559">
+        <v>557</v>
+      </c>
+      <c r="B559">
+        <v>0.001361457165330648</v>
+      </c>
+    </row>
+    <row r="560" spans="1:2">
+      <c r="A560">
+        <v>558</v>
+      </c>
+      <c r="B560">
+        <v>0.001259938231669366</v>
+      </c>
+    </row>
+    <row r="561" spans="1:2">
+      <c r="A561">
+        <v>559</v>
+      </c>
+      <c r="B561">
+        <v>0.002168920356780291</v>
+      </c>
+    </row>
+    <row r="562" spans="1:2">
+      <c r="A562">
+        <v>560</v>
+      </c>
+      <c r="B562">
+        <v>0.0009989335667341948</v>
+      </c>
+    </row>
+    <row r="563" spans="1:2">
+      <c r="A563">
+        <v>561</v>
+      </c>
+      <c r="B563">
+        <v>3.985069270129316E-05</v>
+      </c>
+    </row>
+    <row r="564" spans="1:2">
+      <c r="A564">
+        <v>562</v>
+      </c>
+      <c r="B564">
+        <v>0.0009264987893402576</v>
+      </c>
+    </row>
+    <row r="565" spans="1:2">
+      <c r="A565">
+        <v>563</v>
+      </c>
+      <c r="B565">
+        <v>-0.003636159468442202</v>
+      </c>
+    </row>
+    <row r="566" spans="1:2">
+      <c r="A566">
+        <v>564</v>
+      </c>
+      <c r="B566">
+        <v>0.001232246402651072</v>
+      </c>
+    </row>
+    <row r="567" spans="1:2">
+      <c r="A567">
+        <v>565</v>
+      </c>
+      <c r="B567">
+        <v>-0.0002894398348871619</v>
+      </c>
+    </row>
+    <row r="568" spans="1:2">
+      <c r="A568">
+        <v>566</v>
+      </c>
+      <c r="B568">
+        <v>0.0005560193676501513</v>
+      </c>
+    </row>
+    <row r="569" spans="1:2">
+      <c r="A569">
+        <v>567</v>
+      </c>
+      <c r="B569">
+        <v>0.0007054692250676453</v>
+      </c>
+    </row>
+    <row r="570" spans="1:2">
+      <c r="A570">
+        <v>568</v>
+      </c>
+      <c r="B570">
+        <v>0.0005481175612658262</v>
+      </c>
+    </row>
+    <row r="571" spans="1:2">
+      <c r="A571">
+        <v>569</v>
+      </c>
+      <c r="B571">
+        <v>-0.0004677595279645175</v>
+      </c>
+    </row>
+    <row r="572" spans="1:2">
+      <c r="A572">
+        <v>570</v>
+      </c>
+      <c r="B572">
+        <v>0.0008293353603221476</v>
+      </c>
+    </row>
+    <row r="573" spans="1:2">
+      <c r="A573">
+        <v>571</v>
+      </c>
+      <c r="B573">
+        <v>0.000714459631126374</v>
+      </c>
+    </row>
+    <row r="574" spans="1:2">
+      <c r="A574">
+        <v>572</v>
+      </c>
+      <c r="B574">
+        <v>0.001113854348659515</v>
+      </c>
+    </row>
+    <row r="575" spans="1:2">
+      <c r="A575">
+        <v>573</v>
+      </c>
+      <c r="B575">
+        <v>0.002337561454623938</v>
+      </c>
+    </row>
+    <row r="576" spans="1:2">
+      <c r="A576">
+        <v>574</v>
+      </c>
+      <c r="B576">
+        <v>0.0006990436231717467</v>
+      </c>
+    </row>
+    <row r="577" spans="1:2">
+      <c r="A577">
+        <v>575</v>
+      </c>
+      <c r="B577">
+        <v>0.000806046708021313</v>
+      </c>
+    </row>
+    <row r="578" spans="1:2">
+      <c r="A578">
+        <v>576</v>
+      </c>
+      <c r="B578">
+        <v>0.002014789963141084</v>
+      </c>
+    </row>
+    <row r="579" spans="1:2">
+      <c r="A579">
+        <v>577</v>
+      </c>
+      <c r="B579">
+        <v>0.0009587326785549521</v>
+      </c>
+    </row>
+    <row r="580" spans="1:2">
+      <c r="A580">
+        <v>578</v>
+      </c>
+      <c r="B580">
+        <v>0.0006306672585196793</v>
+      </c>
+    </row>
+    <row r="581" spans="1:2">
+      <c r="A581">
+        <v>579</v>
+      </c>
+      <c r="B581">
+        <v>0.001423329231329262</v>
+      </c>
+    </row>
+    <row r="582" spans="1:2">
+      <c r="A582">
+        <v>580</v>
+      </c>
+      <c r="B582">
+        <v>0.001633565756492317</v>
+      </c>
+    </row>
+    <row r="583" spans="1:2">
+      <c r="A583">
+        <v>581</v>
+      </c>
+      <c r="B583">
+        <v>0.0005160295986570418</v>
+      </c>
+    </row>
+    <row r="584" spans="1:2">
+      <c r="A584">
+        <v>582</v>
+      </c>
+      <c r="B584">
+        <v>0.0006922326283529401</v>
+      </c>
+    </row>
+    <row r="585" spans="1:2">
+      <c r="A585">
+        <v>583</v>
+      </c>
+      <c r="B585">
+        <v>0.0003674546605907381</v>
+      </c>
+    </row>
+    <row r="586" spans="1:2">
+      <c r="A586">
+        <v>584</v>
+      </c>
+      <c r="B586">
+        <v>0.0004891721764579415</v>
+      </c>
+    </row>
+    <row r="587" spans="1:2">
+      <c r="A587">
+        <v>585</v>
+      </c>
+      <c r="B587">
+        <v>4.450483174878173E-05</v>
+      </c>
+    </row>
+    <row r="588" spans="1:2">
+      <c r="A588">
+        <v>586</v>
+      </c>
+      <c r="B588">
+        <v>-0.0001979932276299223</v>
+      </c>
+    </row>
+    <row r="589" spans="1:2">
+      <c r="A589">
+        <v>587</v>
+      </c>
+      <c r="B589">
+        <v>0.0003772070340346545</v>
+      </c>
+    </row>
+    <row r="590" spans="1:2">
+      <c r="A590">
+        <v>588</v>
+      </c>
+      <c r="B590">
+        <v>0.0002950670605059713</v>
+      </c>
+    </row>
+    <row r="591" spans="1:2">
+      <c r="A591">
+        <v>589</v>
+      </c>
+      <c r="B591">
+        <v>0.002019705483689904</v>
+      </c>
+    </row>
+    <row r="592" spans="1:2">
+      <c r="A592">
+        <v>590</v>
+      </c>
+      <c r="B592">
+        <v>0.0006334116915240884</v>
+      </c>
+    </row>
+    <row r="593" spans="1:2">
+      <c r="A593">
+        <v>591</v>
+      </c>
+      <c r="B593">
+        <v>0.001601714524440467</v>
+      </c>
+    </row>
+    <row r="594" spans="1:2">
+      <c r="A594">
+        <v>592</v>
+      </c>
+      <c r="B594">
+        <v>0.0004997043870389462</v>
+      </c>
+    </row>
+    <row r="595" spans="1:2">
+      <c r="A595">
+        <v>593</v>
+      </c>
+      <c r="B595">
+        <v>0.0007163776317611337</v>
+      </c>
+    </row>
+    <row r="596" spans="1:2">
+      <c r="A596">
+        <v>594</v>
+      </c>
+      <c r="B596">
+        <v>0.0005900797550566494</v>
+      </c>
+    </row>
+    <row r="597" spans="1:2">
+      <c r="A597">
+        <v>595</v>
+      </c>
+      <c r="B597">
+        <v>0.00082113326061517</v>
+      </c>
+    </row>
+    <row r="598" spans="1:2">
+      <c r="A598">
+        <v>596</v>
+      </c>
+      <c r="B598">
+        <v>0.0005304656224325299</v>
+      </c>
+    </row>
+    <row r="599" spans="1:2">
+      <c r="A599">
+        <v>597</v>
+      </c>
+      <c r="B599">
+        <v>-9.143846546066925E-05</v>
+      </c>
+    </row>
+    <row r="600" spans="1:2">
+      <c r="A600">
+        <v>598</v>
+      </c>
+      <c r="B600">
+        <v>0.0005476374644786119</v>
+      </c>
+    </row>
+    <row r="601" spans="1:2">
+      <c r="A601">
+        <v>599</v>
+      </c>
+      <c r="B601">
+        <v>0.001638325396925211</v>
+      </c>
+    </row>
+    <row r="602" spans="1:2">
+      <c r="A602">
+        <v>600</v>
+      </c>
+      <c r="B602">
+        <v>0.002862801076844335</v>
+      </c>
+    </row>
+    <row r="603" spans="1:2">
+      <c r="A603">
+        <v>601</v>
+      </c>
+      <c r="B603">
+        <v>0.001809594104997814</v>
+      </c>
+    </row>
+    <row r="604" spans="1:2">
+      <c r="A604">
+        <v>602</v>
+      </c>
+      <c r="B604">
+        <v>0.008888553828001022</v>
+      </c>
+    </row>
+    <row r="605" spans="1:2">
+      <c r="A605">
+        <v>603</v>
+      </c>
+      <c r="B605">
+        <v>0.001179619575850666</v>
+      </c>
+    </row>
+    <row r="606" spans="1:2">
+      <c r="A606">
+        <v>604</v>
+      </c>
+      <c r="B606">
+        <v>-0.0004877809842582792</v>
+      </c>
+    </row>
+    <row r="607" spans="1:2">
+      <c r="A607">
+        <v>605</v>
+      </c>
+      <c r="B607">
+        <v>0.001514949952252209</v>
+      </c>
+    </row>
+    <row r="608" spans="1:2">
+      <c r="A608">
+        <v>606</v>
+      </c>
+      <c r="B608">
+        <v>0.001834606868214905</v>
+      </c>
+    </row>
+    <row r="609" spans="1:2">
+      <c r="A609">
+        <v>607</v>
+      </c>
+      <c r="B609">
+        <v>0.0003691569436341524</v>
+      </c>
+    </row>
+    <row r="610" spans="1:2">
+      <c r="A610">
+        <v>608</v>
+      </c>
+      <c r="B610">
+        <v>0.0002662544138729572</v>
+      </c>
+    </row>
+    <row r="611" spans="1:2">
+      <c r="A611">
+        <v>609</v>
+      </c>
+      <c r="B611">
+        <v>0.0003138045722153038</v>
+      </c>
+    </row>
+    <row r="612" spans="1:2">
+      <c r="A612">
+        <v>610</v>
+      </c>
+      <c r="B612">
+        <v>0.0002910360635723919</v>
+      </c>
+    </row>
+    <row r="613" spans="1:2">
+      <c r="A613">
+        <v>611</v>
+      </c>
+      <c r="B613">
+        <v>0.001010521198622882</v>
+      </c>
+    </row>
+    <row r="614" spans="1:2">
+      <c r="A614">
+        <v>612</v>
+      </c>
+      <c r="B614">
+        <v>8.749480912229046E-05</v>
+      </c>
+    </row>
+    <row r="615" spans="1:2">
+      <c r="A615">
+        <v>613</v>
+      </c>
+      <c r="B615">
+        <v>0.0008995282696560025</v>
+      </c>
+    </row>
+    <row r="616" spans="1:2">
+      <c r="A616">
+        <v>614</v>
+      </c>
+      <c r="B616">
+        <v>0.0009094896377064288</v>
+      </c>
+    </row>
+    <row r="617" spans="1:2">
+      <c r="A617">
+        <v>615</v>
+      </c>
+      <c r="B617">
+        <v>-0.0006138048483990133</v>
+      </c>
+    </row>
+    <row r="618" spans="1:2">
+      <c r="A618">
+        <v>616</v>
+      </c>
+      <c r="B618">
+        <v>0.0009557588491588831</v>
+      </c>
+    </row>
+    <row r="619" spans="1:2">
+      <c r="A619">
+        <v>617</v>
+      </c>
+      <c r="B619">
+        <v>2.696613410080317E-05</v>
+      </c>
+    </row>
+    <row r="620" spans="1:2">
+      <c r="A620">
+        <v>618</v>
+      </c>
+      <c r="B620">
+        <v>0.0001721645094221458</v>
+      </c>
+    </row>
+    <row r="621" spans="1:2">
+      <c r="A621">
+        <v>619</v>
+      </c>
+      <c r="B621">
+        <v>0.002283061156049371</v>
+      </c>
+    </row>
+    <row r="622" spans="1:2">
+      <c r="A622">
+        <v>620</v>
+      </c>
+      <c r="B622">
+        <v>0.0002327115653315559</v>
+      </c>
+    </row>
+    <row r="623" spans="1:2">
+      <c r="A623">
+        <v>621</v>
+      </c>
+      <c r="B623">
+        <v>0.001330015016719699</v>
+      </c>
+    </row>
+    <row r="624" spans="1:2">
+      <c r="A624">
+        <v>622</v>
+      </c>
+      <c r="B624">
+        <v>0.0005832561291754246</v>
+      </c>
+    </row>
+    <row r="625" spans="1:2">
+      <c r="A625">
+        <v>623</v>
+      </c>
+      <c r="B625">
+        <v>0.00097254867432639</v>
+      </c>
+    </row>
+    <row r="626" spans="1:2">
+      <c r="A626">
+        <v>624</v>
+      </c>
+      <c r="B626">
+        <v>0.000699843221809715</v>
+      </c>
+    </row>
+    <row r="627" spans="1:2">
+      <c r="A627">
+        <v>625</v>
+      </c>
+      <c r="B627">
+        <v>0.000366073043551296</v>
+      </c>
+    </row>
+    <row r="628" spans="1:2">
+      <c r="A628">
+        <v>626</v>
+      </c>
+      <c r="B628">
+        <v>0.001189332688227296</v>
+      </c>
+    </row>
+    <row r="629" spans="1:2">
+      <c r="A629">
+        <v>627</v>
+      </c>
+      <c r="B629">
+        <v>0.0007224389701150358</v>
+      </c>
+    </row>
+    <row r="630" spans="1:2">
+      <c r="A630">
+        <v>628</v>
+      </c>
+      <c r="B630">
+        <v>-0.005188690964132547</v>
+      </c>
+    </row>
+    <row r="631" spans="1:2">
+      <c r="A631">
+        <v>629</v>
+      </c>
+      <c r="B631">
+        <v>0.0006557678570970893</v>
+      </c>
+    </row>
+    <row r="632" spans="1:2">
+      <c r="A632">
+        <v>630</v>
+      </c>
+      <c r="B632">
+        <v>0.001264328835532069</v>
+      </c>
+    </row>
+    <row r="633" spans="1:2">
+      <c r="A633">
+        <v>631</v>
+      </c>
+      <c r="B633">
+        <v>0.0004189889878034592</v>
+      </c>
+    </row>
+    <row r="634" spans="1:2">
+      <c r="A634">
+        <v>632</v>
+      </c>
+      <c r="B634">
+        <v>0.001307575381360948</v>
+      </c>
+    </row>
+    <row r="635" spans="1:2">
+      <c r="A635">
+        <v>633</v>
+      </c>
+      <c r="B635">
+        <v>0.0004881065397057682</v>
+      </c>
+    </row>
+    <row r="636" spans="1:2">
+      <c r="A636">
+        <v>634</v>
+      </c>
+      <c r="B636">
+        <v>0.0002738109033089131</v>
+      </c>
+    </row>
+    <row r="637" spans="1:2">
+      <c r="A637">
+        <v>635</v>
+      </c>
+      <c r="B637">
+        <v>0.0005704596405848861</v>
+      </c>
+    </row>
+    <row r="638" spans="1:2">
+      <c r="A638">
+        <v>636</v>
+      </c>
+      <c r="B638">
+        <v>0.0005207770736888051</v>
+      </c>
+    </row>
+    <row r="639" spans="1:2">
+      <c r="A639">
+        <v>637</v>
+      </c>
+      <c r="B639">
+        <v>0.0006538493908010423</v>
+      </c>
+    </row>
+    <row r="640" spans="1:2">
+      <c r="A640">
+        <v>638</v>
+      </c>
+      <c r="B640">
+        <v>0.001271814573556185</v>
+      </c>
+    </row>
+    <row r="641" spans="1:2">
+      <c r="A641">
+        <v>639</v>
+      </c>
+      <c r="B641">
+        <v>0.001909699756652117</v>
+      </c>
+    </row>
+    <row r="642" spans="1:2">
+      <c r="A642">
+        <v>640</v>
+      </c>
+      <c r="B642">
+        <v>0.0006188576808199286</v>
+      </c>
+    </row>
+    <row r="643" spans="1:2">
+      <c r="A643">
+        <v>641</v>
+      </c>
+      <c r="B643">
+        <v>-0.001002541743218899</v>
+      </c>
+    </row>
+    <row r="644" spans="1:2">
+      <c r="A644">
+        <v>642</v>
+      </c>
+      <c r="B644">
+        <v>0.0003338152600917965</v>
+      </c>
+    </row>
+    <row r="645" spans="1:2">
+      <c r="A645">
+        <v>643</v>
+      </c>
+      <c r="B645">
+        <v>0.002099594799801707</v>
+      </c>
+    </row>
+    <row r="646" spans="1:2">
+      <c r="A646">
+        <v>644</v>
+      </c>
+      <c r="B646">
+        <v>0.0008788398117758334</v>
+      </c>
+    </row>
+    <row r="647" spans="1:2">
+      <c r="A647">
+        <v>645</v>
+      </c>
+      <c r="B647">
+        <v>0.0001041097639244981</v>
+      </c>
+    </row>
+    <row r="648" spans="1:2">
+      <c r="A648">
+        <v>646</v>
+      </c>
+      <c r="B648">
+        <v>0.001273107482120395</v>
+      </c>
+    </row>
+    <row r="649" spans="1:2">
+      <c r="A649">
+        <v>647</v>
+      </c>
+      <c r="B649">
+        <v>-0.0004478510527405888</v>
+      </c>
+    </row>
+    <row r="650" spans="1:2">
+      <c r="A650">
+        <v>648</v>
+      </c>
+      <c r="B650">
+        <v>0.001239167875610292</v>
+      </c>
+    </row>
+    <row r="651" spans="1:2">
+      <c r="A651">
+        <v>649</v>
+      </c>
+      <c r="B651">
+        <v>0.0001137976651079953</v>
+      </c>
+    </row>
+    <row r="652" spans="1:2">
+      <c r="A652">
+        <v>650</v>
+      </c>
+      <c r="B652">
+        <v>0.0003305719001218677</v>
+      </c>
+    </row>
+    <row r="653" spans="1:2">
+      <c r="A653">
+        <v>651</v>
+      </c>
+      <c r="B653">
+        <v>0.0004381981561891735</v>
+      </c>
+    </row>
+    <row r="654" spans="1:2">
+      <c r="A654">
+        <v>652</v>
+      </c>
+      <c r="B654">
+        <v>0.0006194309098646045</v>
+      </c>
+    </row>
+    <row r="655" spans="1:2">
+      <c r="A655">
+        <v>653</v>
+      </c>
+      <c r="B655">
+        <v>-1.952052116394043E-05</v>
+      </c>
+    </row>
+    <row r="656" spans="1:2">
+      <c r="A656">
+        <v>654</v>
+      </c>
+      <c r="B656">
+        <v>-0.001919671427458525</v>
+      </c>
+    </row>
+    <row r="657" spans="1:2">
+      <c r="A657">
+        <v>655</v>
+      </c>
+      <c r="B657">
+        <v>-0.000773854146245867</v>
+      </c>
+    </row>
+    <row r="658" spans="1:2">
+      <c r="A658">
+        <v>656</v>
+      </c>
+      <c r="B658">
+        <v>0.0007551548769697547</v>
+      </c>
+    </row>
+    <row r="659" spans="1:2">
+      <c r="A659">
+        <v>657</v>
+      </c>
+      <c r="B659">
+        <v>0.0004779012233484536</v>
+      </c>
+    </row>
+    <row r="660" spans="1:2">
+      <c r="A660">
+        <v>658</v>
+      </c>
+      <c r="B660">
+        <v>-0.0006324753048829734</v>
+      </c>
+    </row>
+    <row r="661" spans="1:2">
+      <c r="A661">
+        <v>659</v>
+      </c>
+      <c r="B661">
+        <v>0.003925127908587456</v>
+      </c>
+    </row>
+    <row r="662" spans="1:2">
+      <c r="A662">
+        <v>660</v>
+      </c>
+      <c r="B662">
+        <v>0.0005901006516069174</v>
+      </c>
+    </row>
+    <row r="663" spans="1:2">
+      <c r="A663">
+        <v>661</v>
+      </c>
+      <c r="B663">
+        <v>0.0004337364807724953</v>
+      </c>
+    </row>
+    <row r="664" spans="1:2">
+      <c r="A664">
+        <v>662</v>
+      </c>
+      <c r="B664">
+        <v>0.0001013506771414541</v>
+      </c>
+    </row>
+    <row r="665" spans="1:2">
+      <c r="A665">
+        <v>663</v>
+      </c>
+      <c r="B665">
+        <v>0.001248822896741331</v>
+      </c>
+    </row>
+    <row r="666" spans="1:2">
+      <c r="A666">
+        <v>664</v>
+      </c>
+      <c r="B666">
+        <v>0.0006367422174662352</v>
+      </c>
+    </row>
+    <row r="667" spans="1:2">
+      <c r="A667">
+        <v>665</v>
+      </c>
+      <c r="B667">
+        <v>0.0008385536493733525</v>
+      </c>
+    </row>
+    <row r="668" spans="1:2">
+      <c r="A668">
+        <v>666</v>
+      </c>
+      <c r="B668">
+        <v>0.002739078132435679</v>
+      </c>
+    </row>
+    <row r="669" spans="1:2">
+      <c r="A669">
+        <v>667</v>
+      </c>
+      <c r="B669">
+        <v>-0.00522537948563695</v>
+      </c>
+    </row>
+    <row r="670" spans="1:2">
+      <c r="A670">
+        <v>668</v>
+      </c>
+      <c r="B670">
+        <v>0.0009022696758620441</v>
+      </c>
+    </row>
+    <row r="671" spans="1:2">
+      <c r="A671">
+        <v>669</v>
+      </c>
+      <c r="B671">
+        <v>0.000415295478887856</v>
+      </c>
+    </row>
+    <row r="672" spans="1:2">
+      <c r="A672">
+        <v>670</v>
+      </c>
+      <c r="B672">
+        <v>0.0004158844822086394</v>
+      </c>
+    </row>
+    <row r="673" spans="1:2">
+      <c r="A673">
+        <v>671</v>
+      </c>
+      <c r="B673">
+        <v>0.0001212513816426508</v>
+      </c>
+    </row>
+    <row r="674" spans="1:2">
+      <c r="A674">
+        <v>672</v>
+      </c>
+      <c r="B674">
+        <v>0.0006435331306420267</v>
+      </c>
+    </row>
+    <row r="675" spans="1:2">
+      <c r="A675">
+        <v>673</v>
+      </c>
+      <c r="B675">
+        <v>0.001108358614146709</v>
+      </c>
+    </row>
+    <row r="676" spans="1:2">
+      <c r="A676">
+        <v>674</v>
+      </c>
+      <c r="B676">
+        <v>0.0009757940424606204</v>
+      </c>
+    </row>
+    <row r="677" spans="1:2">
+      <c r="A677">
+        <v>675</v>
+      </c>
+      <c r="B677">
+        <v>0.001105362549424171</v>
+      </c>
+    </row>
+    <row r="678" spans="1:2">
+      <c r="A678">
+        <v>676</v>
+      </c>
+      <c r="B678">
+        <v>0.0001794103882275522</v>
+      </c>
+    </row>
+    <row r="679" spans="1:2">
+      <c r="A679">
+        <v>677</v>
+      </c>
+      <c r="B679">
+        <v>0.0003849053173325956</v>
+      </c>
+    </row>
+    <row r="680" spans="1:2">
+      <c r="A680">
+        <v>678</v>
+      </c>
+      <c r="B680">
+        <v>0.0003229363064747304</v>
+      </c>
+    </row>
+    <row r="681" spans="1:2">
+      <c r="A681">
+        <v>679</v>
+      </c>
+      <c r="B681">
+        <v>0.0003759672690648586</v>
+      </c>
+    </row>
+    <row r="682" spans="1:2">
+      <c r="A682">
+        <v>680</v>
+      </c>
+      <c r="B682">
+        <v>0.006855547893792391</v>
+      </c>
+    </row>
+    <row r="683" spans="1:2">
+      <c r="A683">
+        <v>681</v>
+      </c>
+      <c r="B683">
+        <v>0.001144069130532444</v>
+      </c>
+    </row>
+    <row r="684" spans="1:2">
+      <c r="A684">
+        <v>682</v>
+      </c>
+      <c r="B684">
+        <v>-0.0006877238629385829</v>
+      </c>
+    </row>
+    <row r="685" spans="1:2">
+      <c r="A685">
+        <v>683</v>
+      </c>
+      <c r="B685">
+        <v>0.000206245225854218</v>
+      </c>
+    </row>
+    <row r="686" spans="1:2">
+      <c r="A686">
+        <v>684</v>
+      </c>
+      <c r="B686">
+        <v>0.0005924910074099898</v>
+      </c>
+    </row>
+    <row r="687" spans="1:2">
+      <c r="A687">
+        <v>685</v>
+      </c>
+      <c r="B687">
+        <v>0.0006792920758016407</v>
+      </c>
+    </row>
+    <row r="688" spans="1:2">
+      <c r="A688">
+        <v>686</v>
+      </c>
+      <c r="B688">
+        <v>0.000728543964214623</v>
+      </c>
+    </row>
+    <row r="689" spans="1:2">
+      <c r="A689">
+        <v>687</v>
+      </c>
+      <c r="B689">
+        <v>0.0004793301923200488</v>
+      </c>
+    </row>
+    <row r="690" spans="1:2">
+      <c r="A690">
+        <v>688</v>
+      </c>
+      <c r="B690">
+        <v>3.721809207490878E-06</v>
+      </c>
+    </row>
+    <row r="691" spans="1:2">
+      <c r="A691">
+        <v>689</v>
+      </c>
+      <c r="B691">
+        <v>0.001985042821615934</v>
+      </c>
+    </row>
+    <row r="692" spans="1:2">
+      <c r="A692">
+        <v>690</v>
+      </c>
+      <c r="B692">
+        <v>-0.0002001486282097176</v>
+      </c>
+    </row>
+    <row r="693" spans="1:2">
+      <c r="A693">
+        <v>691</v>
+      </c>
+      <c r="B693">
+        <v>0.001111530116759241</v>
+      </c>
+    </row>
+    <row r="694" spans="1:2">
+      <c r="A694">
+        <v>692</v>
+      </c>
+      <c r="B694">
+        <v>0.001256805844604969</v>
+      </c>
+    </row>
+    <row r="695" spans="1:2">
+      <c r="A695">
+        <v>693</v>
+      </c>
+      <c r="B695">
+        <v>0.001391272409819067</v>
+      </c>
+    </row>
+    <row r="696" spans="1:2">
+      <c r="A696">
+        <v>694</v>
+      </c>
+      <c r="B696">
+        <v>-0.0002424094855086878</v>
+      </c>
+    </row>
+    <row r="697" spans="1:2">
+      <c r="A697">
+        <v>695</v>
+      </c>
+      <c r="B697">
+        <v>0.0002163940080208704</v>
+      </c>
+    </row>
+    <row r="698" spans="1:2">
+      <c r="A698">
+        <v>696</v>
+      </c>
+      <c r="B698">
+        <v>0.0006894309772178531</v>
+      </c>
+    </row>
+    <row r="699" spans="1:2">
+      <c r="A699">
+        <v>697</v>
+      </c>
+      <c r="B699">
+        <v>-0.0008797051850706339</v>
+      </c>
+    </row>
+    <row r="700" spans="1:2">
+      <c r="A700">
+        <v>698</v>
+      </c>
+      <c r="B700">
+        <v>0.0007168794400058687</v>
+      </c>
+    </row>
+    <row r="701" spans="1:2">
+      <c r="A701">
+        <v>699</v>
+      </c>
+      <c r="B701">
+        <v>-6.657624180661514E-05</v>
+      </c>
+    </row>
+    <row r="702" spans="1:2">
+      <c r="A702">
+        <v>700</v>
+      </c>
+      <c r="B702">
+        <v>-0.0001858067262219265</v>
+      </c>
+    </row>
+    <row r="703" spans="1:2">
+      <c r="A703">
+        <v>701</v>
+      </c>
+      <c r="B703">
+        <v>0.001477726036682725</v>
+      </c>
+    </row>
+    <row r="704" spans="1:2">
+      <c r="A704">
+        <v>702</v>
+      </c>
+      <c r="B704">
+        <v>0.0003877721901517361</v>
+      </c>
+    </row>
+    <row r="705" spans="1:2">
+      <c r="A705">
+        <v>703</v>
+      </c>
+      <c r="B705">
+        <v>0.0005918855313211679</v>
+      </c>
+    </row>
+    <row r="706" spans="1:2">
+      <c r="A706">
+        <v>704</v>
+      </c>
+      <c r="B706">
+        <v>0.0006468825740739703</v>
+      </c>
+    </row>
+    <row r="707" spans="1:2">
+      <c r="A707">
+        <v>705</v>
+      </c>
+      <c r="B707">
+        <v>0.0001721966254990548</v>
+      </c>
+    </row>
+    <row r="708" spans="1:2">
+      <c r="A708">
+        <v>706</v>
+      </c>
+      <c r="B708">
+        <v>0.004172360524535179</v>
+      </c>
+    </row>
+    <row r="709" spans="1:2">
+      <c r="A709">
+        <v>707</v>
+      </c>
+      <c r="B709">
+        <v>-0.0005249378154985607</v>
+      </c>
+    </row>
+    <row r="710" spans="1:2">
+      <c r="A710">
+        <v>708</v>
+      </c>
+      <c r="B710">
+        <v>0.0009258442441932857</v>
+      </c>
+    </row>
+    <row r="711" spans="1:2">
+      <c r="A711">
+        <v>709</v>
+      </c>
+      <c r="B711">
+        <v>0.0004588024748954922</v>
+      </c>
+    </row>
+    <row r="712" spans="1:2">
+      <c r="A712">
+        <v>710</v>
+      </c>
+      <c r="B712">
+        <v>-0.0002484455762896687</v>
+      </c>
+    </row>
+    <row r="713" spans="1:2">
+      <c r="A713">
+        <v>711</v>
+      </c>
+      <c r="B713">
+        <v>-0.0002273625286761671</v>
+      </c>
+    </row>
+    <row r="714" spans="1:2">
+      <c r="A714">
+        <v>712</v>
+      </c>
+      <c r="B714">
+        <v>-0.0001852683199103922</v>
+      </c>
+    </row>
+    <row r="715" spans="1:2">
+      <c r="A715">
+        <v>713</v>
+      </c>
+      <c r="B715">
+        <v>0.0007174805505201221</v>
+      </c>
+    </row>
+    <row r="716" spans="1:2">
+      <c r="A716">
+        <v>714</v>
+      </c>
+      <c r="B716">
+        <v>0.0004211788182146847</v>
+      </c>
+    </row>
+    <row r="717" spans="1:2">
+      <c r="A717">
+        <v>715</v>
+      </c>
+      <c r="B717">
+        <v>0.0005643869517371058</v>
+      </c>
+    </row>
+    <row r="718" spans="1:2">
+      <c r="A718">
+        <v>716</v>
+      </c>
+      <c r="B718">
+        <v>0.0003025332407560199</v>
+      </c>
+    </row>
+    <row r="719" spans="1:2">
+      <c r="A719">
+        <v>717</v>
+      </c>
+      <c r="B719">
+        <v>0.0002854776685126126</v>
+      </c>
+    </row>
+    <row r="720" spans="1:2">
+      <c r="A720">
+        <v>718</v>
+      </c>
+      <c r="B720">
+        <v>-7.352907414315268E-05</v>
+      </c>
+    </row>
+    <row r="721" spans="1:2">
+      <c r="A721">
+        <v>719</v>
+      </c>
+      <c r="B721">
+        <v>0.005232835654169321</v>
+      </c>
+    </row>
+    <row r="722" spans="1:2">
+      <c r="A722">
+        <v>720</v>
+      </c>
+      <c r="B722">
+        <v>-7.594261114718392E-05</v>
+      </c>
+    </row>
+    <row r="723" spans="1:2">
+      <c r="A723">
+        <v>721</v>
+      </c>
+      <c r="B723">
+        <v>0.0003646860423032194</v>
+      </c>
+    </row>
+    <row r="724" spans="1:2">
+      <c r="A724">
+        <v>722</v>
+      </c>
+      <c r="B724">
+        <v>0.0007981398375704885</v>
+      </c>
+    </row>
+    <row r="725" spans="1:2">
+      <c r="A725">
+        <v>723</v>
+      </c>
+      <c r="B725">
+        <v>0.0008907559094950557</v>
+      </c>
+    </row>
+    <row r="726" spans="1:2">
+      <c r="A726">
+        <v>724</v>
+      </c>
+      <c r="B726">
+        <v>0.0002411191526334733</v>
+      </c>
+    </row>
+    <row r="727" spans="1:2">
+      <c r="A727">
+        <v>725</v>
+      </c>
+      <c r="B727">
+        <v>0.0009965470526367426</v>
+      </c>
+    </row>
+    <row r="728" spans="1:2">
+      <c r="A728">
+        <v>726</v>
+      </c>
+      <c r="B728">
+        <v>0.000474575295811519</v>
+      </c>
+    </row>
+    <row r="729" spans="1:2">
+      <c r="A729">
+        <v>727</v>
+      </c>
+      <c r="B729">
+        <v>0.0008458244265057147</v>
+      </c>
+    </row>
+    <row r="730" spans="1:2">
+      <c r="A730">
+        <v>728</v>
+      </c>
+      <c r="B730">
+        <v>0.0001839898031903431</v>
+      </c>
+    </row>
+    <row r="731" spans="1:2">
+      <c r="A731">
+        <v>729</v>
+      </c>
+      <c r="B731">
+        <v>0.0006474390393123031</v>
+      </c>
+    </row>
+    <row r="732" spans="1:2">
+      <c r="A732">
+        <v>730</v>
+      </c>
+      <c r="B732">
+        <v>0.0004249861522112042</v>
+      </c>
+    </row>
+    <row r="733" spans="1:2">
+      <c r="A733">
+        <v>731</v>
+      </c>
+      <c r="B733">
+        <v>-0.000642248138319701</v>
+      </c>
+    </row>
+    <row r="734" spans="1:2">
+      <c r="A734">
+        <v>732</v>
+      </c>
+      <c r="B734">
+        <v>0.005266309250146151</v>
+      </c>
+    </row>
+    <row r="735" spans="1:2">
+      <c r="A735">
+        <v>733</v>
+      </c>
+      <c r="B735">
+        <v>0.001037294045090675</v>
+      </c>
+    </row>
+    <row r="736" spans="1:2">
+      <c r="A736">
+        <v>734</v>
+      </c>
+      <c r="B736">
+        <v>0.0003523464256431907</v>
+      </c>
+    </row>
+    <row r="737" spans="1:2">
+      <c r="A737">
+        <v>735</v>
+      </c>
+      <c r="B737">
+        <v>0.0003467290953267366</v>
+      </c>
+    </row>
+    <row r="738" spans="1:2">
+      <c r="A738">
+        <v>736</v>
+      </c>
+      <c r="B738">
+        <v>9.477307321503758E-05</v>
+      </c>
+    </row>
+    <row r="739" spans="1:2">
+      <c r="A739">
+        <v>737</v>
+      </c>
+      <c r="B739">
+        <v>0.0004187815939076245</v>
+      </c>
+    </row>
+    <row r="740" spans="1:2">
+      <c r="A740">
+        <v>738</v>
+      </c>
+      <c r="B740">
+        <v>-0.0001138447332778014</v>
+      </c>
+    </row>
+    <row r="741" spans="1:2">
+      <c r="A741">
+        <v>739</v>
+      </c>
+      <c r="B741">
+        <v>0.0001227252505486831</v>
+      </c>
+    </row>
+    <row r="742" spans="1:2">
+      <c r="A742">
+        <v>740</v>
+      </c>
+      <c r="B742">
+        <v>0.0001326442579738796</v>
+      </c>
+    </row>
+    <row r="743" spans="1:2">
+      <c r="A743">
+        <v>741</v>
+      </c>
+      <c r="B743">
+        <v>0.000531620520632714</v>
+      </c>
+    </row>
+    <row r="744" spans="1:2">
+      <c r="A744">
+        <v>742</v>
+      </c>
+      <c r="B744">
+        <v>-1.293753484787885E-05</v>
+      </c>
+    </row>
+    <row r="745" spans="1:2">
+      <c r="A745">
+        <v>743</v>
+      </c>
+      <c r="B745">
+        <v>0.0009687485289759934</v>
+      </c>
+    </row>
+    <row r="746" spans="1:2">
+      <c r="A746">
+        <v>744</v>
+      </c>
+      <c r="B746">
+        <v>-3.065801865886897E-05</v>
+      </c>
+    </row>
+    <row r="747" spans="1:2">
+      <c r="A747">
+        <v>745</v>
+      </c>
+      <c r="B747">
+        <v>0.004384623374789953</v>
+      </c>
+    </row>
+    <row r="748" spans="1:2">
+      <c r="A748">
+        <v>746</v>
+      </c>
+      <c r="B748">
+        <v>0.002203639596700668</v>
+      </c>
+    </row>
+    <row r="749" spans="1:2">
+      <c r="A749">
+        <v>747</v>
+      </c>
+      <c r="B749">
+        <v>0.001967806136235595</v>
+      </c>
+    </row>
+    <row r="750" spans="1:2">
+      <c r="A750">
+        <v>748</v>
+      </c>
+      <c r="B750">
+        <v>0.0007646604208275676</v>
+      </c>
+    </row>
+    <row r="751" spans="1:2">
+      <c r="A751">
+        <v>749</v>
+      </c>
+      <c r="B751">
+        <v>0.0003875707916449755</v>
+      </c>
+    </row>
+    <row r="752" spans="1:2">
+      <c r="A752">
+        <v>750</v>
+      </c>
+      <c r="B752">
+        <v>0.0001386845106026158</v>
+      </c>
+    </row>
+    <row r="753" spans="1:2">
+      <c r="A753">
+        <v>751</v>
+      </c>
+      <c r="B753">
+        <v>0.0004461316857486963</v>
+      </c>
+    </row>
+    <row r="754" spans="1:2">
+      <c r="A754">
+        <v>752</v>
+      </c>
+      <c r="B754">
+        <v>0.000958693097345531</v>
+      </c>
+    </row>
+    <row r="755" spans="1:2">
+      <c r="A755">
+        <v>753</v>
+      </c>
+      <c r="B755">
+        <v>0.0002221168979303911</v>
+      </c>
+    </row>
+    <row r="756" spans="1:2">
+      <c r="A756">
+        <v>754</v>
+      </c>
+      <c r="B756">
+        <v>0.0005259606405161321</v>
+      </c>
+    </row>
+    <row r="757" spans="1:2">
+      <c r="A757">
+        <v>755</v>
+      </c>
+      <c r="B757">
+        <v>0.0007988882716745138</v>
+      </c>
+    </row>
+    <row r="758" spans="1:2">
+      <c r="A758">
+        <v>756</v>
+      </c>
+      <c r="B758">
+        <v>0.0002983998274430633</v>
+      </c>
+    </row>
+    <row r="759" spans="1:2">
+      <c r="A759">
+        <v>757</v>
+      </c>
+      <c r="B759">
+        <v>0.0008455229690298438</v>
+      </c>
+    </row>
+    <row r="760" spans="1:2">
+      <c r="A760">
+        <v>758</v>
+      </c>
+      <c r="B760">
+        <v>-0.003145378781482577</v>
+      </c>
+    </row>
+    <row r="761" spans="1:2">
+      <c r="A761">
+        <v>759</v>
+      </c>
+      <c r="B761">
+        <v>0.00047320342855528</v>
+      </c>
+    </row>
+    <row r="762" spans="1:2">
+      <c r="A762">
+        <v>760</v>
+      </c>
+      <c r="B762">
+        <v>0.0001466067624278367</v>
+      </c>
+    </row>
+    <row r="763" spans="1:2">
+      <c r="A763">
+        <v>761</v>
+      </c>
+      <c r="B763">
+        <v>-2.636802310007624E-05</v>
+      </c>
+    </row>
+    <row r="764" spans="1:2">
+      <c r="A764">
+        <v>762</v>
+      </c>
+      <c r="B764">
+        <v>0.0002555048849899322</v>
+      </c>
+    </row>
+    <row r="765" spans="1:2">
+      <c r="A765">
+        <v>763</v>
+      </c>
+      <c r="B765">
+        <v>-0.00010511413711356</v>
+      </c>
+    </row>
+    <row r="766" spans="1:2">
+      <c r="A766">
+        <v>764</v>
+      </c>
+      <c r="B766">
+        <v>0.0006596026942133904</v>
+      </c>
+    </row>
+    <row r="767" spans="1:2">
+      <c r="A767">
+        <v>765</v>
+      </c>
+      <c r="B767">
+        <v>0.002392158610746264</v>
+      </c>
+    </row>
+    <row r="768" spans="1:2">
+      <c r="A768">
+        <v>766</v>
+      </c>
+      <c r="B768">
+        <v>0.0002914736396633089</v>
+      </c>
+    </row>
+    <row r="769" spans="1:2">
+      <c r="A769">
+        <v>767</v>
+      </c>
+      <c r="B769">
+        <v>-6.243796815397218E-05</v>
+      </c>
+    </row>
+    <row r="770" spans="1:2">
+      <c r="A770">
+        <v>768</v>
+      </c>
+      <c r="B770">
+        <v>0.0003443561145104468</v>
+      </c>
+    </row>
+    <row r="771" spans="1:2">
+      <c r="A771">
+        <v>769</v>
+      </c>
+      <c r="B771">
+        <v>0.0005123033188283443</v>
+      </c>
+    </row>
+    <row r="772" spans="1:2">
+      <c r="A772">
+        <v>770</v>
+      </c>
+      <c r="B772">
+        <v>0.0002008980518439785</v>
+      </c>
+    </row>
+    <row r="773" spans="1:2">
+      <c r="A773">
+        <v>771</v>
+      </c>
+      <c r="B773">
+        <v>0.0005929293110966682</v>
+      </c>
+    </row>
+    <row r="774" spans="1:2">
+      <c r="A774">
+        <v>772</v>
+      </c>
+      <c r="B774">
+        <v>0.0008209245861507952</v>
+      </c>
+    </row>
+    <row r="775" spans="1:2">
+      <c r="A775">
+        <v>773</v>
+      </c>
+      <c r="B775">
+        <v>0.001673003425821662</v>
+      </c>
+    </row>
+    <row r="776" spans="1:2">
+      <c r="A776">
+        <v>774</v>
+      </c>
+      <c r="B776">
+        <v>0.0002740327327046543</v>
+      </c>
+    </row>
+    <row r="777" spans="1:2">
+      <c r="A777">
+        <v>775</v>
+      </c>
+      <c r="B777">
+        <v>-8.085718582151458E-05</v>
+      </c>
+    </row>
+    <row r="778" spans="1:2">
+      <c r="A778">
+        <v>776</v>
+      </c>
+      <c r="B778">
+        <v>0.0002043857093667611</v>
+      </c>
+    </row>
+    <row r="779" spans="1:2">
+      <c r="A779">
+        <v>777</v>
+      </c>
+      <c r="B779">
+        <v>0.000175549037521705</v>
+      </c>
+    </row>
+    <row r="780" spans="1:2">
+      <c r="A780">
+        <v>778</v>
+      </c>
+      <c r="B780">
+        <v>0.002358575817197561</v>
+      </c>
+    </row>
+    <row r="781" spans="1:2">
+      <c r="A781">
+        <v>779</v>
+      </c>
+      <c r="B781">
+        <v>0.0005734608275815845</v>
+      </c>
+    </row>
+    <row r="782" spans="1:2">
+      <c r="A782">
+        <v>780</v>
+      </c>
+      <c r="B782">
+        <v>0.0006455801776610315</v>
+      </c>
+    </row>
+    <row r="783" spans="1:2">
+      <c r="A783">
+        <v>781</v>
+      </c>
+      <c r="B783">
+        <v>0.0009994953870773315</v>
+      </c>
+    </row>
+    <row r="784" spans="1:2">
+      <c r="A784">
+        <v>782</v>
+      </c>
+      <c r="B784">
+        <v>0.0005802114610560238</v>
+      </c>
+    </row>
+    <row r="785" spans="1:2">
+      <c r="A785">
+        <v>783</v>
+      </c>
+      <c r="B785">
+        <v>-1.024843095365213E-05</v>
+      </c>
+    </row>
+    <row r="786" spans="1:2">
+      <c r="A786">
+        <v>784</v>
+      </c>
+      <c r="B786">
+        <v>0.0003189500712323934</v>
+      </c>
+    </row>
+    <row r="787" spans="1:2">
+      <c r="A787">
+        <v>785</v>
+      </c>
+      <c r="B787">
+        <v>0.0003478691214695573</v>
+      </c>
+    </row>
+    <row r="788" spans="1:2">
+      <c r="A788">
+        <v>786</v>
+      </c>
+      <c r="B788">
+        <v>0.0005161336739547551</v>
+      </c>
+    </row>
+    <row r="789" spans="1:2">
+      <c r="A789">
+        <v>787</v>
+      </c>
+      <c r="B789">
+        <v>0.0002410849119769409</v>
+      </c>
+    </row>
+    <row r="790" spans="1:2">
+      <c r="A790">
+        <v>788</v>
+      </c>
+      <c r="B790">
+        <v>9.37861914280802E-05</v>
+      </c>
+    </row>
+    <row r="791" spans="1:2">
+      <c r="A791">
+        <v>789</v>
+      </c>
+      <c r="B791">
+        <v>0.0007923675584606826</v>
+      </c>
+    </row>
+    <row r="792" spans="1:2">
+      <c r="A792">
+        <v>790</v>
+      </c>
+      <c r="B792">
+        <v>0.0003559231699910015</v>
+      </c>
+    </row>
+    <row r="793" spans="1:2">
+      <c r="A793">
+        <v>791</v>
+      </c>
+      <c r="B793">
+        <v>0.004360867198556662</v>
+      </c>
+    </row>
+    <row r="794" spans="1:2">
+      <c r="A794">
+        <v>792</v>
+      </c>
+      <c r="B794">
+        <v>0.0001732274249661714</v>
+      </c>
+    </row>
+    <row r="795" spans="1:2">
+      <c r="A795">
+        <v>793</v>
+      </c>
+      <c r="B795">
+        <v>0.0004987479187548161</v>
+      </c>
+    </row>
+    <row r="796" spans="1:2">
+      <c r="A796">
+        <v>794</v>
+      </c>
+      <c r="B796">
+        <v>9.005601896205917E-05</v>
+      </c>
+    </row>
+    <row r="797" spans="1:2">
+      <c r="A797">
+        <v>795</v>
+      </c>
+      <c r="B797">
+        <v>-3.488273068796843E-05</v>
+      </c>
+    </row>
+    <row r="798" spans="1:2">
+      <c r="A798">
+        <v>796</v>
+      </c>
+      <c r="B798">
+        <v>0.0001092878374038264</v>
+      </c>
+    </row>
+    <row r="799" spans="1:2">
+      <c r="A799">
+        <v>797</v>
+      </c>
+      <c r="B799">
+        <v>9.54508941504173E-05</v>
+      </c>
+    </row>
+    <row r="800" spans="1:2">
+      <c r="A800">
+        <v>798</v>
+      </c>
+      <c r="B800">
+        <v>-0.0001888758561108261</v>
+      </c>
+    </row>
+    <row r="801" spans="1:2">
+      <c r="A801">
+        <v>799</v>
+      </c>
+      <c r="B801">
+        <v>0.0006496802670881152</v>
+      </c>
+    </row>
+    <row r="802" spans="1:2">
+      <c r="A802">
+        <v>800</v>
+      </c>
+      <c r="B802">
+        <v>0.000104148784885183</v>
+      </c>
+    </row>
+    <row r="803" spans="1:2">
+      <c r="A803">
+        <v>801</v>
+      </c>
+      <c r="B803">
+        <v>-0.0001717340928735211</v>
+      </c>
+    </row>
+    <row r="804" spans="1:2">
+      <c r="A804">
+        <v>802</v>
+      </c>
+      <c r="B804">
+        <v>-0.0002099098928738385</v>
+      </c>
+    </row>
+    <row r="805" spans="1:2">
+      <c r="A805">
+        <v>803</v>
+      </c>
+      <c r="B805">
+        <v>0.00100406538695097</v>
+      </c>
+    </row>
+    <row r="806" spans="1:2">
+      <c r="A806">
+        <v>804</v>
+      </c>
+      <c r="B806">
+        <v>0.0006629042909480631</v>
+      </c>
+    </row>
+    <row r="807" spans="1:2">
+      <c r="A807">
+        <v>805</v>
+      </c>
+      <c r="B807">
+        <v>-0.000182239236892201</v>
+      </c>
+    </row>
+    <row r="808" spans="1:2">
+      <c r="A808">
+        <v>806</v>
+      </c>
+      <c r="B808">
+        <v>0.0002978369011543691</v>
+      </c>
+    </row>
+    <row r="809" spans="1:2">
+      <c r="A809">
+        <v>807</v>
+      </c>
+      <c r="B809">
+        <v>0.0007515894249081612</v>
+      </c>
+    </row>
+    <row r="810" spans="1:2">
+      <c r="A810">
+        <v>808</v>
+      </c>
+      <c r="B810">
+        <v>0.0006322126719169319</v>
+      </c>
+    </row>
+    <row r="811" spans="1:2">
+      <c r="A811">
+        <v>809</v>
+      </c>
+      <c r="B811">
+        <v>0.0003774976648855954</v>
+      </c>
+    </row>
+    <row r="812" spans="1:2">
+      <c r="A812">
+        <v>810</v>
+      </c>
+      <c r="B812">
+        <v>0.001356442109681666</v>
+      </c>
+    </row>
+    <row r="813" spans="1:2">
+      <c r="A813">
+        <v>811</v>
+      </c>
+      <c r="B813">
+        <v>0.0006292287725955248</v>
+      </c>
+    </row>
+    <row r="814" spans="1:2">
+      <c r="A814">
+        <v>812</v>
+      </c>
+      <c r="B814">
+        <v>0.0002937153331004083</v>
+      </c>
+    </row>
+    <row r="815" spans="1:2">
+      <c r="A815">
+        <v>813</v>
+      </c>
+      <c r="B815">
+        <v>0.001246001222170889</v>
+      </c>
+    </row>
+    <row r="816" spans="1:2">
+      <c r="A816">
+        <v>814</v>
+      </c>
+      <c r="B816">
+        <v>0.0006003216840326786</v>
+      </c>
+    </row>
+    <row r="817" spans="1:2">
+      <c r="A817">
+        <v>815</v>
+      </c>
+      <c r="B817">
+        <v>0.0005496646626852453</v>
+      </c>
+    </row>
+    <row r="818" spans="1:2">
+      <c r="A818">
+        <v>816</v>
+      </c>
+      <c r="B818">
+        <v>-0.0001329821971012279</v>
+      </c>
+    </row>
+    <row r="819" spans="1:2">
+      <c r="A819">
+        <v>817</v>
+      </c>
+      <c r="B819">
+        <v>0.001276113442145288</v>
       </c>
     </row>
   </sheetData>
@@ -9125,12 +15669,508 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1"/>
+  <dimension ref="A1:B63"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:2">
+    <row r="1" spans="1:2">
       <c r="B1" t="s">
         <v>489</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.009437680244445801</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>0.01028811931610107</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>0.0032958984375</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>0.003023982048034668</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>0.008124709129333496</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>0.010550856590271</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>0.004759669303894043</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>0.008773088455200195</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>0.006877660751342773</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>0.008367180824279785</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>0.01039254665374756</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>0.01384544372558594</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>0.01200854778289795</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <v>0.001786231994628906</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <v>0.004967093467712402</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17">
+        <v>0.001589417457580566</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>0.004017949104309082</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19">
+        <v>0.00716710090637207</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20">
+        <v>0.008574247360229492</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21">
+        <v>0.004807233810424805</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22">
+        <v>0.008899211883544922</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23">
+        <v>0.006476998329162598</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24">
+        <v>0.003204822540283203</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25">
+        <v>0.004156947135925293</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26">
+        <v>0.00419151782989502</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27">
+        <v>0.01109433174133301</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28">
+        <v>0.008535385131835938</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29">
+        <v>0.005964398384094238</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30">
+        <v>0.01027679443359375</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="B31">
+        <v>0.009564995765686035</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="B32">
+        <v>0.006861686706542969</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33">
+        <v>0.007445335388183594</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="B34">
+        <v>0.009863734245300293</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="B35">
+        <v>0.01345551013946533</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>34</v>
+      </c>
+      <c r="B36">
+        <v>0.002273082733154297</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>35</v>
+      </c>
+      <c r="B37">
+        <v>0.00941002368927002</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="B38">
+        <v>0.01373076438903809</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="B39">
+        <v>0.008426785469055176</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="B40">
+        <v>0.008704185485839844</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="B41">
+        <v>0.007074356079101562</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="B42">
+        <v>0.008652329444885254</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="B43">
+        <v>0.009020090103149414</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="B44">
+        <v>0.01343703269958496</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="B45">
+        <v>0.004323720932006836</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="B46">
+        <v>0.01376676559448242</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="B47">
+        <v>0.007866024971008301</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="B48">
+        <v>0.02119994163513184</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="B49">
+        <v>0.008882641792297363</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="B50">
+        <v>0.003277182579040527</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51">
+        <v>49</v>
+      </c>
+      <c r="B51">
+        <v>0.009079456329345703</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="B52">
+        <v>0.00432431697845459</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53">
+        <v>51</v>
+      </c>
+      <c r="B53">
+        <v>0.005921840667724609</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54">
+        <v>52</v>
+      </c>
+      <c r="B54">
+        <v>0.01130294799804688</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55">
+        <v>53</v>
+      </c>
+      <c r="B55">
+        <v>0.00729072093963623</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56">
+        <v>54</v>
+      </c>
+      <c r="B56">
+        <v>0.007324695587158203</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57">
+        <v>55</v>
+      </c>
+      <c r="B57">
+        <v>0.01089024543762207</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58">
+        <v>56</v>
+      </c>
+      <c r="B58">
+        <v>0.008290767669677734</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59">
+        <v>57</v>
+      </c>
+      <c r="B59">
+        <v>0.01299858093261719</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60">
+        <v>58</v>
+      </c>
+      <c r="B60">
+        <v>0.00340723991394043</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61">
+        <v>59</v>
+      </c>
+      <c r="B61">
+        <v>0.007610917091369629</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62">
+        <v>60</v>
+      </c>
+      <c r="B62">
+        <v>0.009448647499084473</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63">
+        <v>61</v>
+      </c>
+      <c r="B63">
+        <v>0.002428770065307617</v>
       </c>
     </row>
   </sheetData>
@@ -9140,12 +16180,108 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:2">
+    <row r="1" spans="1:2">
       <c r="B1" t="s">
         <v>489</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.03461647033691406</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>0.03994250297546387</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>0.04369354248046875</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>0.02641534805297852</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>0.02721083164215088</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>0.04626119136810303</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>0.04050683975219727</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>0.04823768138885498</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>0.05014622211456299</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>0.05123674869537354</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>0.03667747974395752</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>0.04392397403717041</v>
       </c>
     </row>
   </sheetData>
